--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_precious_metals.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kas_alms" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.536</v>
+        <v>0.212</v>
       </c>
       <c r="E2">
-        <v>1.62</v>
+        <v>0.655</v>
       </c>
       <c r="G2">
-        <v>-0.2479057591623037</v>
+        <v>0.3886337308775377</v>
       </c>
       <c r="H2">
-        <v>-0.2479057591623037</v>
+        <v>0.3886337308775377</v>
       </c>
       <c r="I2">
-        <v>-0.1840314136125654</v>
+        <v>0.353813295493906</v>
       </c>
       <c r="J2">
-        <v>-0.1840314136125654</v>
+        <v>0.3423449456565869</v>
       </c>
       <c r="K2">
-        <v>0.184</v>
+        <v>278.66</v>
       </c>
       <c r="L2">
-        <v>0.04816753926701571</v>
+        <v>0.2916021795342694</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.03</v>
+        <v>245.847</v>
       </c>
       <c r="V2">
-        <v>0.0003397508493771234</v>
+        <v>0.3990374939133258</v>
       </c>
       <c r="W2">
-        <v>-0.02206235011990408</v>
+        <v>0.530039291962267</v>
       </c>
       <c r="X2">
-        <v>0.0783754766721128</v>
+        <v>0.2345926233075705</v>
       </c>
       <c r="Y2">
-        <v>-0.1004378267920169</v>
+        <v>0.2954466686546965</v>
       </c>
       <c r="Z2">
-        <v>0.8816062774059544</v>
+        <v>0.8168783765301237</v>
       </c>
       <c r="AA2">
-        <v>-0.1622432494807293</v>
+        <v>-0.2774086880317832</v>
       </c>
       <c r="AB2">
-        <v>0.07433356339108702</v>
+        <v>0.1502812339163005</v>
       </c>
       <c r="AC2">
-        <v>-0.2365768128718163</v>
+        <v>-0.4276899219480838</v>
       </c>
       <c r="AD2">
-        <v>9.76</v>
+        <v>824.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.76</v>
+        <v>824.5</v>
       </c>
       <c r="AG2">
-        <v>9.73</v>
+        <v>578.653</v>
       </c>
       <c r="AH2">
-        <v>0.09953089944931674</v>
+        <v>0.5723309732056088</v>
       </c>
       <c r="AI2">
-        <v>6.550335570469797</v>
+        <v>0.5762671587128519</v>
       </c>
       <c r="AJ2">
-        <v>0.0992553300010201</v>
+        <v>0.4843285599617661</v>
       </c>
       <c r="AK2">
-        <v>6.664383561643832</v>
+        <v>0.488350621522424</v>
       </c>
       <c r="AL2">
-        <v>0.388</v>
+        <v>42.075</v>
       </c>
       <c r="AM2">
-        <v>0.388</v>
+        <v>35.675</v>
       </c>
       <c r="AN2">
-        <v>-20.16528925619835</v>
+        <v>1.749097342729737</v>
       </c>
       <c r="AO2">
-        <v>-1.811855670103093</v>
+        <v>8.035888294711825</v>
       </c>
       <c r="AP2">
-        <v>-20.10330578512397</v>
+        <v>1.227556609657478</v>
       </c>
       <c r="AQ2">
-        <v>-1.811855670103093</v>
+        <v>9.477505255781361</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Joint Stock Company KM GOLD (KAS:KMGD)</t>
+          <t>AK Altynalmas JSC (KAS:ALMS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.536</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="E3">
-        <v>1.62</v>
+        <v>0.655</v>
       </c>
       <c r="G3">
-        <v>-0.2479057591623037</v>
+        <v>0.3894880117265208</v>
       </c>
       <c r="H3">
-        <v>-0.2479057591623037</v>
+        <v>0.3894880117265208</v>
       </c>
       <c r="I3">
-        <v>-0.1840314136125654</v>
+        <v>0.3552507590828186</v>
       </c>
       <c r="J3">
-        <v>-0.1840314136125654</v>
+        <v>0.3322208727725959</v>
       </c>
       <c r="K3">
-        <v>0.184</v>
+        <v>281.2</v>
       </c>
       <c r="L3">
-        <v>0.04816753926701571</v>
+        <v>0.294419432520155</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +766,8913 @@
         <v>0</v>
       </c>
       <c r="U3">
+        <v>245.8</v>
+      </c>
+      <c r="V3">
+        <v>0.406953642384106</v>
+      </c>
+      <c r="W3">
+        <v>0.7536853390511926</v>
+      </c>
+      <c r="X3">
+        <v>0.2496331778169746</v>
+      </c>
+      <c r="Y3">
+        <v>0.504052161234218</v>
+      </c>
+      <c r="Z3">
+        <v>0.8174426566244436</v>
+      </c>
+      <c r="AA3">
+        <v>0.2715715128253221</v>
+      </c>
+      <c r="AB3">
+        <v>0.144105659442174</v>
+      </c>
+      <c r="AC3">
+        <v>0.1274658533831481</v>
+      </c>
+      <c r="AD3">
+        <v>812.7</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>812.7</v>
+      </c>
+      <c r="AG3">
+        <v>566.9000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>0.5736570904214019</v>
+      </c>
+      <c r="AI3">
+        <v>0.5687591853873609</v>
+      </c>
+      <c r="AJ3">
+        <v>0.4841574856947647</v>
+      </c>
+      <c r="AK3">
+        <v>0.4791649057560646</v>
+      </c>
+      <c r="AL3">
+        <v>41.4</v>
+      </c>
+      <c r="AM3">
+        <v>35</v>
+      </c>
+      <c r="AN3">
+        <v>1.720728350624603</v>
+      </c>
+      <c r="AO3">
+        <v>8.195652173913045</v>
+      </c>
+      <c r="AP3">
+        <v>1.200296421765827</v>
+      </c>
+      <c r="AQ3">
+        <v>9.694285714285714</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joint Stock Company KM GOLD (KAS:KMGD)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.135</v>
+      </c>
+      <c r="G4">
+        <v>-1.189555125725339</v>
+      </c>
+      <c r="H4">
+        <v>-1.189555125725339</v>
+      </c>
+      <c r="I4">
+        <v>-2.30174081237911</v>
+      </c>
+      <c r="J4">
+        <v>-2.30174081237911</v>
+      </c>
+      <c r="K4">
+        <v>-2.54</v>
+      </c>
+      <c r="L4">
+        <v>-4.912959381044487</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.047</v>
+      </c>
+      <c r="V4">
+        <v>0.003884297520661157</v>
+      </c>
+      <c r="W4">
+        <v>0.3063932448733414</v>
+      </c>
+      <c r="X4">
+        <v>0.2195520687981664</v>
+      </c>
+      <c r="Y4">
+        <v>0.08684117607517505</v>
+      </c>
+      <c r="Z4">
+        <v>0.3590277777777776</v>
+      </c>
+      <c r="AA4">
+        <v>-0.8263888888888885</v>
+      </c>
+      <c r="AB4">
+        <v>0.1564568083904271</v>
+      </c>
+      <c r="AC4">
+        <v>-0.9828456972793156</v>
+      </c>
+      <c r="AD4">
+        <v>11.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>11.8</v>
+      </c>
+      <c r="AG4">
+        <v>11.753</v>
+      </c>
+      <c r="AH4">
+        <v>0.493723849372385</v>
+      </c>
+      <c r="AI4">
+        <v>6.344086021505372</v>
+      </c>
+      <c r="AJ4">
+        <v>0.492726281809416</v>
+      </c>
+      <c r="AK4">
+        <v>6.482625482625481</v>
+      </c>
+      <c r="AL4">
+        <v>0.675</v>
+      </c>
+      <c r="AM4">
+        <v>0.675</v>
+      </c>
+      <c r="AN4">
+        <v>-12.91028446389497</v>
+      </c>
+      <c r="AO4">
+        <v>-1.762962962962963</v>
+      </c>
+      <c r="AP4">
+        <v>-12.85886214442013</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.762962962962963</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AK Altynalmas JSC (KAS:ALMS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KAS:ALMS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.573657090421402</v>
+      </c>
+      <c r="F2">
+        <v>0.98</v>
+      </c>
+      <c r="G2">
+        <v>604</v>
+      </c>
+      <c r="H2">
+        <v>238.817804513471</v>
+      </c>
+      <c r="I2">
+        <v>1170.9</v>
+      </c>
+      <c r="J2">
+        <v>1381.38380451347</v>
+      </c>
+      <c r="K2">
+        <v>812.7</v>
+      </c>
+      <c r="L2">
+        <v>1388.366</v>
+      </c>
+      <c r="M2">
+        <v>0.144105659442174</v>
+      </c>
+      <c r="N2">
+        <v>0.123963488676698</v>
+      </c>
+      <c r="O2">
+        <v>0.06567743119266049</v>
+      </c>
+      <c r="P2">
+        <v>0.0424</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.249633177816975</v>
+      </c>
+      <c r="T2">
+        <v>4.12057443383491</v>
+      </c>
+      <c r="U2">
+        <v>2.2915298073507</v>
+      </c>
+      <c r="V2">
+        <v>44.3644965126626</v>
+      </c>
+      <c r="W2">
+        <v>6.267718161099328</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>604</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.08209678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>472.3</v>
+      </c>
+      <c r="AH2">
+        <v>11.1</v>
+      </c>
+      <c r="AI2">
+        <v>227.1</v>
+      </c>
+      <c r="AJ2">
+        <v>812.7</v>
+      </c>
+      <c r="AK2">
+        <v>812.7</v>
+      </c>
+      <c r="AL2">
+        <v>41.4</v>
+      </c>
+      <c r="AM2">
+        <v>812.7</v>
+      </c>
+      <c r="AN2">
+        <v>245.8</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.14033667745858</v>
+      </c>
+      <c r="C2">
+        <v>1451.064047841465</v>
+      </c>
+      <c r="D2">
+        <v>1205.264047841465</v>
+      </c>
+      <c r="E2">
+        <v>-812.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>245.8</v>
+      </c>
+      <c r="H2">
+        <v>604</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>472.3</v>
+      </c>
+      <c r="K2">
+        <v>11.1</v>
+      </c>
+      <c r="L2">
+        <v>461.2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>461.2</v>
+      </c>
+      <c r="O2">
+        <v>92.24000000000002</v>
+      </c>
+      <c r="P2">
+        <v>368.96</v>
+      </c>
+      <c r="Q2">
+        <v>380.06</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.14033667745858</v>
+      </c>
+      <c r="T2">
+        <v>1.103594440613497</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1401112041036628</v>
+      </c>
+      <c r="C3">
+        <v>1439.016877904449</v>
+      </c>
+      <c r="D3">
+        <v>1207.383877904449</v>
+      </c>
+      <c r="E3">
+        <v>-798.533</v>
+      </c>
+      <c r="F3">
+        <v>14.167</v>
+      </c>
+      <c r="G3">
+        <v>245.8</v>
+      </c>
+      <c r="H3">
+        <v>604</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>472.3</v>
+      </c>
+      <c r="K3">
+        <v>11.1</v>
+      </c>
+      <c r="L3">
+        <v>461.2</v>
+      </c>
+      <c r="M3">
+        <v>0.6474319000000002</v>
+      </c>
+      <c r="N3">
+        <v>460.5525681</v>
+      </c>
+      <c r="O3">
+        <v>92.11051362000002</v>
+      </c>
+      <c r="P3">
+        <v>368.44205448</v>
+      </c>
+      <c r="Q3">
+        <v>379.54205448</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1411571758622857</v>
+      </c>
+      <c r="T3">
+        <v>1.112512375487142</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>712.3529131017484</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1398857307487456</v>
+      </c>
+      <c r="C4">
+        <v>1426.977177860784</v>
+      </c>
+      <c r="D4">
+        <v>1209.511177860784</v>
+      </c>
+      <c r="E4">
+        <v>-784.366</v>
+      </c>
+      <c r="F4">
+        <v>28.334</v>
+      </c>
+      <c r="G4">
+        <v>245.8</v>
+      </c>
+      <c r="H4">
+        <v>604</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>472.3</v>
+      </c>
+      <c r="K4">
+        <v>11.1</v>
+      </c>
+      <c r="L4">
+        <v>461.2</v>
+      </c>
+      <c r="M4">
+        <v>1.2948638</v>
+      </c>
+      <c r="N4">
+        <v>459.9051362</v>
+      </c>
+      <c r="O4">
+        <v>91.98102724000003</v>
+      </c>
+      <c r="P4">
+        <v>367.92410896</v>
+      </c>
+      <c r="Q4">
+        <v>379.02410896</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1419944191313731</v>
+      </c>
+      <c r="T4">
+        <v>1.121612309031677</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>356.1764565508742</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
         <v>0.03</v>
       </c>
-      <c r="V3">
-        <v>0.0003397508493771234</v>
-      </c>
-      <c r="W3">
-        <v>-0.02206235011990408</v>
-      </c>
-      <c r="X3">
-        <v>0.0783754766721128</v>
-      </c>
-      <c r="Y3">
-        <v>-0.1004378267920169</v>
-      </c>
-      <c r="Z3">
-        <v>0.8816062774059544</v>
-      </c>
-      <c r="AA3">
-        <v>-0.1622432494807293</v>
-      </c>
-      <c r="AB3">
-        <v>0.07433356339108702</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2365768128718163</v>
-      </c>
-      <c r="AD3">
-        <v>9.76</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>9.76</v>
-      </c>
-      <c r="AG3">
-        <v>9.73</v>
-      </c>
-      <c r="AH3">
-        <v>0.09953089944931674</v>
-      </c>
-      <c r="AI3">
-        <v>6.550335570469797</v>
-      </c>
-      <c r="AJ3">
-        <v>0.0992553300010201</v>
-      </c>
-      <c r="AK3">
-        <v>6.664383561643832</v>
-      </c>
-      <c r="AL3">
-        <v>0.388</v>
-      </c>
-      <c r="AM3">
-        <v>0.388</v>
-      </c>
-      <c r="AN3">
-        <v>-20.16528925619835</v>
-      </c>
-      <c r="AO3">
-        <v>-1.811855670103093</v>
-      </c>
-      <c r="AP3">
-        <v>-20.10330578512397</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.811855670103093</v>
+      <c r="B5">
+        <v>0.1396602573938285</v>
+      </c>
+      <c r="C5">
+        <v>1414.944987263965</v>
+      </c>
+      <c r="D5">
+        <v>1211.645987263965</v>
+      </c>
+      <c r="E5">
+        <v>-770.1990000000001</v>
+      </c>
+      <c r="F5">
+        <v>42.501</v>
+      </c>
+      <c r="G5">
+        <v>245.8</v>
+      </c>
+      <c r="H5">
+        <v>604</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>472.3</v>
+      </c>
+      <c r="K5">
+        <v>11.1</v>
+      </c>
+      <c r="L5">
+        <v>461.2</v>
+      </c>
+      <c r="M5">
+        <v>1.9422957</v>
+      </c>
+      <c r="N5">
+        <v>459.2577043</v>
+      </c>
+      <c r="O5">
+        <v>91.85154086000003</v>
+      </c>
+      <c r="P5">
+        <v>367.40616344</v>
+      </c>
+      <c r="Q5">
+        <v>378.50616344</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1428489251482768</v>
+      </c>
+      <c r="T5">
+        <v>1.130899870071976</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>237.4509710339162</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1394347840389114</v>
+      </c>
+      <c r="C6">
+        <v>1402.920345947233</v>
+      </c>
+      <c r="D6">
+        <v>1213.788345947233</v>
+      </c>
+      <c r="E6">
+        <v>-756.032</v>
+      </c>
+      <c r="F6">
+        <v>56.66800000000001</v>
+      </c>
+      <c r="G6">
+        <v>245.8</v>
+      </c>
+      <c r="H6">
+        <v>604</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>472.3</v>
+      </c>
+      <c r="K6">
+        <v>11.1</v>
+      </c>
+      <c r="L6">
+        <v>461.2</v>
+      </c>
+      <c r="M6">
+        <v>2.589727600000001</v>
+      </c>
+      <c r="N6">
+        <v>458.6102724</v>
+      </c>
+      <c r="O6">
+        <v>91.72205448000003</v>
+      </c>
+      <c r="P6">
+        <v>366.88821792</v>
+      </c>
+      <c r="Q6">
+        <v>377.98821792</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.143721233373866</v>
+      </c>
+      <c r="T6">
+        <v>1.140380921967281</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>178.0882282754371</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1392093106839942</v>
+      </c>
+      <c r="C7">
+        <v>1390.90329402605</v>
+      </c>
+      <c r="D7">
+        <v>1215.93829402605</v>
+      </c>
+      <c r="E7">
+        <v>-741.865</v>
+      </c>
+      <c r="F7">
+        <v>70.83500000000001</v>
+      </c>
+      <c r="G7">
+        <v>245.8</v>
+      </c>
+      <c r="H7">
+        <v>604</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>472.3</v>
+      </c>
+      <c r="K7">
+        <v>11.1</v>
+      </c>
+      <c r="L7">
+        <v>461.2</v>
+      </c>
+      <c r="M7">
+        <v>3.237159500000001</v>
+      </c>
+      <c r="N7">
+        <v>457.9628405</v>
+      </c>
+      <c r="O7">
+        <v>91.59256810000002</v>
+      </c>
+      <c r="P7">
+        <v>366.3702724</v>
+      </c>
+      <c r="Q7">
+        <v>377.4702724</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1446119059831518</v>
+      </c>
+      <c r="T7">
+        <v>1.150061574955118</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>142.4705826203497</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.138983837329077</v>
+      </c>
+      <c r="C8">
+        <v>1378.893871900604</v>
+      </c>
+      <c r="D8">
+        <v>1218.095871900604</v>
+      </c>
+      <c r="E8">
+        <v>-727.6980000000001</v>
+      </c>
+      <c r="F8">
+        <v>85.002</v>
+      </c>
+      <c r="G8">
+        <v>245.8</v>
+      </c>
+      <c r="H8">
+        <v>604</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>472.3</v>
+      </c>
+      <c r="K8">
+        <v>11.1</v>
+      </c>
+      <c r="L8">
+        <v>461.2</v>
+      </c>
+      <c r="M8">
+        <v>3.8845914</v>
+      </c>
+      <c r="N8">
+        <v>457.3154086</v>
+      </c>
+      <c r="O8">
+        <v>91.46308172000003</v>
+      </c>
+      <c r="P8">
+        <v>365.85232688</v>
+      </c>
+      <c r="Q8">
+        <v>376.95232688</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1455215290734862</v>
+      </c>
+      <c r="T8">
+        <v>1.159948199283123</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>118.7254855169581</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1387583639741599</v>
+      </c>
+      <c r="C9">
+        <v>1366.89212025834</v>
+      </c>
+      <c r="D9">
+        <v>1220.26112025834</v>
+      </c>
+      <c r="E9">
+        <v>-713.5310000000001</v>
+      </c>
+      <c r="F9">
+        <v>99.16900000000001</v>
+      </c>
+      <c r="G9">
+        <v>245.8</v>
+      </c>
+      <c r="H9">
+        <v>604</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>472.3</v>
+      </c>
+      <c r="K9">
+        <v>11.1</v>
+      </c>
+      <c r="L9">
+        <v>461.2</v>
+      </c>
+      <c r="M9">
+        <v>4.532023300000001</v>
+      </c>
+      <c r="N9">
+        <v>456.6679767</v>
+      </c>
+      <c r="O9">
+        <v>91.33359534000003</v>
+      </c>
+      <c r="P9">
+        <v>365.33438136</v>
+      </c>
+      <c r="Q9">
+        <v>376.43438136</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1464507139507095</v>
+      </c>
+      <c r="T9">
+        <v>1.170047439188074</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>101.7647018716784</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1385328906192427</v>
+      </c>
+      <c r="C10">
+        <v>1354.898080076517</v>
+      </c>
+      <c r="D10">
+        <v>1222.434080076517</v>
+      </c>
+      <c r="E10">
+        <v>-699.364</v>
+      </c>
+      <c r="F10">
+        <v>113.336</v>
+      </c>
+      <c r="G10">
+        <v>245.8</v>
+      </c>
+      <c r="H10">
+        <v>604</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>472.3</v>
+      </c>
+      <c r="K10">
+        <v>11.1</v>
+      </c>
+      <c r="L10">
+        <v>461.2</v>
+      </c>
+      <c r="M10">
+        <v>5.179455200000001</v>
+      </c>
+      <c r="N10">
+        <v>456.0205448</v>
+      </c>
+      <c r="O10">
+        <v>91.20410896000003</v>
+      </c>
+      <c r="P10">
+        <v>364.8164358399999</v>
+      </c>
+      <c r="Q10">
+        <v>375.91643584</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1474000984991768</v>
+      </c>
+      <c r="T10">
+        <v>1.18036622778661</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.03656</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>89.04411413771855</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1383074172643255</v>
+      </c>
+      <c r="C11">
+        <v>1342.91179262479</v>
+      </c>
+      <c r="D11">
+        <v>1224.61479262479</v>
+      </c>
+      <c r="E11">
+        <v>-685.197</v>
+      </c>
+      <c r="F11">
+        <v>127.503</v>
+      </c>
+      <c r="G11">
+        <v>245.8</v>
+      </c>
+      <c r="H11">
+        <v>604</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>472.3</v>
+      </c>
+      <c r="K11">
+        <v>11.1</v>
+      </c>
+      <c r="L11">
+        <v>461.2</v>
+      </c>
+      <c r="M11">
+        <v>5.8268871</v>
+      </c>
+      <c r="N11">
+        <v>455.3731129</v>
+      </c>
+      <c r="O11">
+        <v>91.07462258000002</v>
+      </c>
+      <c r="P11">
+        <v>364.2984903199999</v>
+      </c>
+      <c r="Q11">
+        <v>375.39849032</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.148370348642116</v>
+      </c>
+      <c r="T11">
+        <v>1.190911802947752</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.03656</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>79.15032367797205</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1380819439094084</v>
+      </c>
+      <c r="C12">
+        <v>1330.93329946783</v>
+      </c>
+      <c r="D12">
+        <v>1226.803299467831</v>
+      </c>
+      <c r="E12">
+        <v>-671.03</v>
+      </c>
+      <c r="F12">
+        <v>141.67</v>
+      </c>
+      <c r="G12">
+        <v>245.8</v>
+      </c>
+      <c r="H12">
+        <v>604</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>472.3</v>
+      </c>
+      <c r="K12">
+        <v>11.1</v>
+      </c>
+      <c r="L12">
+        <v>461.2</v>
+      </c>
+      <c r="M12">
+        <v>6.474319000000001</v>
+      </c>
+      <c r="N12">
+        <v>454.725681</v>
+      </c>
+      <c r="O12">
+        <v>90.94513620000004</v>
+      </c>
+      <c r="P12">
+        <v>363.7805448</v>
+      </c>
+      <c r="Q12">
+        <v>374.8805448</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1493621598993427</v>
+      </c>
+      <c r="T12">
+        <v>1.201691724223586</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.03656</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>71.23529131017484</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1378564705544912</v>
+      </c>
+      <c r="C13">
+        <v>1318.962642467959</v>
+      </c>
+      <c r="D13">
+        <v>1228.999642467959</v>
+      </c>
+      <c r="E13">
+        <v>-656.8630000000001</v>
+      </c>
+      <c r="F13">
+        <v>155.837</v>
+      </c>
+      <c r="G13">
+        <v>245.8</v>
+      </c>
+      <c r="H13">
+        <v>604</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>472.3</v>
+      </c>
+      <c r="K13">
+        <v>11.1</v>
+      </c>
+      <c r="L13">
+        <v>461.2</v>
+      </c>
+      <c r="M13">
+        <v>7.121750900000001</v>
+      </c>
+      <c r="N13">
+        <v>454.0782491</v>
+      </c>
+      <c r="O13">
+        <v>90.81564982000003</v>
+      </c>
+      <c r="P13">
+        <v>363.26259928</v>
+      </c>
+      <c r="Q13">
+        <v>374.36259928</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1503762590499901</v>
+      </c>
+      <c r="T13">
+        <v>1.212713890921349</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.03656</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>64.75935573652259</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1376309971995741</v>
+      </c>
+      <c r="C14">
+        <v>1306.999863787819</v>
+      </c>
+      <c r="D14">
+        <v>1231.203863787819</v>
+      </c>
+      <c r="E14">
+        <v>-642.696</v>
+      </c>
+      <c r="F14">
+        <v>170.004</v>
+      </c>
+      <c r="G14">
+        <v>245.8</v>
+      </c>
+      <c r="H14">
+        <v>604</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>472.3</v>
+      </c>
+      <c r="K14">
+        <v>11.1</v>
+      </c>
+      <c r="L14">
+        <v>461.2</v>
+      </c>
+      <c r="M14">
+        <v>7.7691828</v>
+      </c>
+      <c r="N14">
+        <v>453.4308172</v>
+      </c>
+      <c r="O14">
+        <v>90.68616344000003</v>
+      </c>
+      <c r="P14">
+        <v>362.7446537599999</v>
+      </c>
+      <c r="Q14">
+        <v>373.84465376</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1514134059086069</v>
+      </c>
+      <c r="T14">
+        <v>1.223986561407697</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.03656</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>59.36274275847904</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1374055238446569</v>
+      </c>
+      <c r="C15">
+        <v>1295.045005893073</v>
+      </c>
+      <c r="D15">
+        <v>1233.416005893073</v>
+      </c>
+      <c r="E15">
+        <v>-628.529</v>
+      </c>
+      <c r="F15">
+        <v>184.171</v>
+      </c>
+      <c r="G15">
+        <v>245.8</v>
+      </c>
+      <c r="H15">
+        <v>604</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>472.3</v>
+      </c>
+      <c r="K15">
+        <v>11.1</v>
+      </c>
+      <c r="L15">
+        <v>461.2</v>
+      </c>
+      <c r="M15">
+        <v>8.416614700000002</v>
+      </c>
+      <c r="N15">
+        <v>452.7833853</v>
+      </c>
+      <c r="O15">
+        <v>90.55667706000003</v>
+      </c>
+      <c r="P15">
+        <v>362.2267082399999</v>
+      </c>
+      <c r="Q15">
+        <v>373.32670824</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1524743952237436</v>
+      </c>
+      <c r="T15">
+        <v>1.235518373744306</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.03656</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>54.79637793090372</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1371800504897397</v>
+      </c>
+      <c r="C16">
+        <v>1283.098111555132</v>
+      </c>
+      <c r="D16">
+        <v>1235.636111555132</v>
+      </c>
+      <c r="E16">
+        <v>-614.3620000000001</v>
+      </c>
+      <c r="F16">
+        <v>198.338</v>
+      </c>
+      <c r="G16">
+        <v>245.8</v>
+      </c>
+      <c r="H16">
+        <v>604</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>472.3</v>
+      </c>
+      <c r="K16">
+        <v>11.1</v>
+      </c>
+      <c r="L16">
+        <v>461.2</v>
+      </c>
+      <c r="M16">
+        <v>9.064046600000001</v>
+      </c>
+      <c r="N16">
+        <v>452.1359534</v>
+      </c>
+      <c r="O16">
+        <v>90.42719068000004</v>
+      </c>
+      <c r="P16">
+        <v>361.70876272</v>
+      </c>
+      <c r="Q16">
+        <v>372.80876272</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1535600587089997</v>
+      </c>
+      <c r="T16">
+        <v>1.247318367763162</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.03656</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>50.88235093583918</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1369545771348226</v>
+      </c>
+      <c r="C17">
+        <v>1271.159223853908</v>
+      </c>
+      <c r="D17">
+        <v>1237.864223853908</v>
+      </c>
+      <c r="E17">
+        <v>-600.1950000000001</v>
+      </c>
+      <c r="F17">
+        <v>212.505</v>
+      </c>
+      <c r="G17">
+        <v>245.8</v>
+      </c>
+      <c r="H17">
+        <v>604</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>472.3</v>
+      </c>
+      <c r="K17">
+        <v>11.1</v>
+      </c>
+      <c r="L17">
+        <v>461.2</v>
+      </c>
+      <c r="M17">
+        <v>9.7114785</v>
+      </c>
+      <c r="N17">
+        <v>451.4885215</v>
+      </c>
+      <c r="O17">
+        <v>90.29770430000004</v>
+      </c>
+      <c r="P17">
+        <v>361.1908172</v>
+      </c>
+      <c r="Q17">
+        <v>372.2908172</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1546712672174383</v>
+      </c>
+      <c r="T17">
+        <v>1.259396008700109</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.03656</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>47.49019420678324</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1367291037799054</v>
+      </c>
+      <c r="C18">
+        <v>1259.228386180605</v>
+      </c>
+      <c r="D18">
+        <v>1240.100386180605</v>
+      </c>
+      <c r="E18">
+        <v>-586.028</v>
+      </c>
+      <c r="F18">
+        <v>226.672</v>
+      </c>
+      <c r="G18">
+        <v>245.8</v>
+      </c>
+      <c r="H18">
+        <v>604</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>472.3</v>
+      </c>
+      <c r="K18">
+        <v>11.1</v>
+      </c>
+      <c r="L18">
+        <v>461.2</v>
+      </c>
+      <c r="M18">
+        <v>10.3589104</v>
+      </c>
+      <c r="N18">
+        <v>450.8410896</v>
+      </c>
+      <c r="O18">
+        <v>90.16821792000003</v>
+      </c>
+      <c r="P18">
+        <v>360.67287168</v>
+      </c>
+      <c r="Q18">
+        <v>371.77287168</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.155808933071316</v>
+      </c>
+      <c r="T18">
+        <v>1.271761212516507</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.03656</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>44.52205706885928</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1365036304249883</v>
+      </c>
+      <c r="C19">
+        <v>1247.305642240534</v>
+      </c>
+      <c r="D19">
+        <v>1242.344642240534</v>
+      </c>
+      <c r="E19">
+        <v>-571.861</v>
+      </c>
+      <c r="F19">
+        <v>240.839</v>
+      </c>
+      <c r="G19">
+        <v>245.8</v>
+      </c>
+      <c r="H19">
+        <v>604</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>472.3</v>
+      </c>
+      <c r="K19">
+        <v>11.1</v>
+      </c>
+      <c r="L19">
+        <v>461.2</v>
+      </c>
+      <c r="M19">
+        <v>11.0063423</v>
+      </c>
+      <c r="N19">
+        <v>450.1936577</v>
+      </c>
+      <c r="O19">
+        <v>90.03873154000003</v>
+      </c>
+      <c r="P19">
+        <v>360.1549261599999</v>
+      </c>
+      <c r="Q19">
+        <v>371.25492616</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1569740125602268</v>
+      </c>
+      <c r="T19">
+        <v>1.284424373051372</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.03656</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>41.90311253539696</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1362781570700711</v>
+      </c>
+      <c r="C20">
+        <v>1235.391036055957</v>
+      </c>
+      <c r="D20">
+        <v>1244.597036055957</v>
+      </c>
+      <c r="E20">
+        <v>-557.6940000000001</v>
+      </c>
+      <c r="F20">
+        <v>255.006</v>
+      </c>
+      <c r="G20">
+        <v>245.8</v>
+      </c>
+      <c r="H20">
+        <v>604</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>472.3</v>
+      </c>
+      <c r="K20">
+        <v>11.1</v>
+      </c>
+      <c r="L20">
+        <v>461.2</v>
+      </c>
+      <c r="M20">
+        <v>11.6537742</v>
+      </c>
+      <c r="N20">
+        <v>449.5462258</v>
+      </c>
+      <c r="O20">
+        <v>89.90924516000003</v>
+      </c>
+      <c r="P20">
+        <v>359.63698064</v>
+      </c>
+      <c r="Q20">
+        <v>370.73698064</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1581675086220379</v>
+      </c>
+      <c r="T20">
+        <v>1.297396391160258</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.03656</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>39.57516183898603</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1360526837151539</v>
+      </c>
+      <c r="C21">
+        <v>1223.484611968972</v>
+      </c>
+      <c r="D21">
+        <v>1246.857611968972</v>
+      </c>
+      <c r="E21">
+        <v>-543.527</v>
+      </c>
+      <c r="F21">
+        <v>269.173</v>
+      </c>
+      <c r="G21">
+        <v>245.8</v>
+      </c>
+      <c r="H21">
+        <v>604</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>472.3</v>
+      </c>
+      <c r="K21">
+        <v>11.1</v>
+      </c>
+      <c r="L21">
+        <v>461.2</v>
+      </c>
+      <c r="M21">
+        <v>12.3012061</v>
+      </c>
+      <c r="N21">
+        <v>448.8987939</v>
+      </c>
+      <c r="O21">
+        <v>89.77975878000002</v>
+      </c>
+      <c r="P21">
+        <v>359.11903512</v>
+      </c>
+      <c r="Q21">
+        <v>370.21903512</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1593904737224123</v>
+      </c>
+      <c r="T21">
+        <v>1.310688706012573</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.03656</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>37.49225858430255</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1358272103602368</v>
+      </c>
+      <c r="C22">
+        <v>1211.586414644418</v>
+      </c>
+      <c r="D22">
+        <v>1249.126414644418</v>
+      </c>
+      <c r="E22">
+        <v>-529.36</v>
+      </c>
+      <c r="F22">
+        <v>283.34</v>
+      </c>
+      <c r="G22">
+        <v>245.8</v>
+      </c>
+      <c r="H22">
+        <v>604</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>472.3</v>
+      </c>
+      <c r="K22">
+        <v>11.1</v>
+      </c>
+      <c r="L22">
+        <v>461.2</v>
+      </c>
+      <c r="M22">
+        <v>12.948638</v>
+      </c>
+      <c r="N22">
+        <v>448.251362</v>
+      </c>
+      <c r="O22">
+        <v>89.65027240000002</v>
+      </c>
+      <c r="P22">
+        <v>358.6010896</v>
+      </c>
+      <c r="Q22">
+        <v>369.7010896</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.160644012950296</v>
+      </c>
+      <c r="T22">
+        <v>1.324313328736197</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.03656</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>35.61764565508742</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1356017370053197</v>
+      </c>
+      <c r="C23">
+        <v>1199.696489072819</v>
+      </c>
+      <c r="D23">
+        <v>1251.403489072819</v>
+      </c>
+      <c r="E23">
+        <v>-515.193</v>
+      </c>
+      <c r="F23">
+        <v>297.507</v>
+      </c>
+      <c r="G23">
+        <v>245.8</v>
+      </c>
+      <c r="H23">
+        <v>604</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>472.3</v>
+      </c>
+      <c r="K23">
+        <v>11.1</v>
+      </c>
+      <c r="L23">
+        <v>461.2</v>
+      </c>
+      <c r="M23">
+        <v>13.5960699</v>
+      </c>
+      <c r="N23">
+        <v>447.6039301</v>
+      </c>
+      <c r="O23">
+        <v>89.52078602000003</v>
+      </c>
+      <c r="P23">
+        <v>358.08314408</v>
+      </c>
+      <c r="Q23">
+        <v>369.18314408</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1619292873485059</v>
+      </c>
+      <c r="T23">
+        <v>1.33828287861738</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.03656</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>33.92156729055945</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1353762636504025</v>
+      </c>
+      <c r="C24">
+        <v>1187.814880573356</v>
+      </c>
+      <c r="D24">
+        <v>1253.688880573356</v>
+      </c>
+      <c r="E24">
+        <v>-501.026</v>
+      </c>
+      <c r="F24">
+        <v>311.674</v>
+      </c>
+      <c r="G24">
+        <v>245.8</v>
+      </c>
+      <c r="H24">
+        <v>604</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>472.3</v>
+      </c>
+      <c r="K24">
+        <v>11.1</v>
+      </c>
+      <c r="L24">
+        <v>461.2</v>
+      </c>
+      <c r="M24">
+        <v>14.2435018</v>
+      </c>
+      <c r="N24">
+        <v>446.9564982</v>
+      </c>
+      <c r="O24">
+        <v>89.39129964000003</v>
+      </c>
+      <c r="P24">
+        <v>357.56519856</v>
+      </c>
+      <c r="Q24">
+        <v>368.66519856</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.163247517500516</v>
+      </c>
+      <c r="T24">
+        <v>1.352610622085261</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W24">
+        <v>0.03656</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>32.3796778682613</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1351507902954853</v>
+      </c>
+      <c r="C25">
+        <v>1175.941634796873</v>
+      </c>
+      <c r="D25">
+        <v>1255.982634796873</v>
+      </c>
+      <c r="E25">
+        <v>-486.859</v>
+      </c>
+      <c r="F25">
+        <v>325.841</v>
+      </c>
+      <c r="G25">
+        <v>245.8</v>
+      </c>
+      <c r="H25">
+        <v>604</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>472.3</v>
+      </c>
+      <c r="K25">
+        <v>11.1</v>
+      </c>
+      <c r="L25">
+        <v>461.2</v>
+      </c>
+      <c r="M25">
+        <v>14.8909337</v>
+      </c>
+      <c r="N25">
+        <v>446.3090663</v>
+      </c>
+      <c r="O25">
+        <v>89.26181326000003</v>
+      </c>
+      <c r="P25">
+        <v>357.04725304</v>
+      </c>
+      <c r="Q25">
+        <v>368.14725304</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1645999873967342</v>
+      </c>
+      <c r="T25">
+        <v>1.367310514734126</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W25">
+        <v>0.03656</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>30.97186578703255</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1349253169405681</v>
+      </c>
+      <c r="C26">
+        <v>1164.076797728923</v>
+      </c>
+      <c r="D26">
+        <v>1258.284797728923</v>
+      </c>
+      <c r="E26">
+        <v>-472.6920000000001</v>
+      </c>
+      <c r="F26">
+        <v>340.008</v>
+      </c>
+      <c r="G26">
+        <v>245.8</v>
+      </c>
+      <c r="H26">
+        <v>604</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>472.3</v>
+      </c>
+      <c r="K26">
+        <v>11.1</v>
+      </c>
+      <c r="L26">
+        <v>461.2</v>
+      </c>
+      <c r="M26">
+        <v>15.5383656</v>
+      </c>
+      <c r="N26">
+        <v>445.6616344</v>
+      </c>
+      <c r="O26">
+        <v>89.13232688000002</v>
+      </c>
+      <c r="P26">
+        <v>356.52930752</v>
+      </c>
+      <c r="Q26">
+        <v>367.62930752</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1659880486060107</v>
+      </c>
+      <c r="T26">
+        <v>1.382397246663223</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W26">
+        <v>0.03656</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>29.68137137923952</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.134699843585651</v>
+      </c>
+      <c r="C27">
+        <v>1152.220415692833</v>
+      </c>
+      <c r="D27">
+        <v>1260.595415692833</v>
+      </c>
+      <c r="E27">
+        <v>-458.525</v>
+      </c>
+      <c r="F27">
+        <v>354.175</v>
+      </c>
+      <c r="G27">
+        <v>245.8</v>
+      </c>
+      <c r="H27">
+        <v>604</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>472.3</v>
+      </c>
+      <c r="K27">
+        <v>11.1</v>
+      </c>
+      <c r="L27">
+        <v>461.2</v>
+      </c>
+      <c r="M27">
+        <v>16.1857975</v>
+      </c>
+      <c r="N27">
+        <v>445.0142025</v>
+      </c>
+      <c r="O27">
+        <v>89.00284050000003</v>
+      </c>
+      <c r="P27">
+        <v>356.011362</v>
+      </c>
+      <c r="Q27">
+        <v>367.111362</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.167413124780868</v>
+      </c>
+      <c r="T27">
+        <v>1.397886291443763</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.03656</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>28.49411652406994</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1344743702307338</v>
+      </c>
+      <c r="C28">
+        <v>1140.372535352814</v>
+      </c>
+      <c r="D28">
+        <v>1262.914535352814</v>
+      </c>
+      <c r="E28">
+        <v>-444.358</v>
+      </c>
+      <c r="F28">
+        <v>368.342</v>
+      </c>
+      <c r="G28">
+        <v>245.8</v>
+      </c>
+      <c r="H28">
+        <v>604</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>472.3</v>
+      </c>
+      <c r="K28">
+        <v>11.1</v>
+      </c>
+      <c r="L28">
+        <v>461.2</v>
+      </c>
+      <c r="M28">
+        <v>16.8332294</v>
+      </c>
+      <c r="N28">
+        <v>444.3667706</v>
+      </c>
+      <c r="O28">
+        <v>88.87335412000003</v>
+      </c>
+      <c r="P28">
+        <v>355.49341648</v>
+      </c>
+      <c r="Q28">
+        <v>366.59341648</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1688767165280187</v>
+      </c>
+      <c r="T28">
+        <v>1.41379395905621</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.03656</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>27.39818896545186</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1342488968758167</v>
+      </c>
+      <c r="C29">
+        <v>1128.533203717105</v>
+      </c>
+      <c r="D29">
+        <v>1265.242203717105</v>
+      </c>
+      <c r="E29">
+        <v>-430.191</v>
+      </c>
+      <c r="F29">
+        <v>382.509</v>
+      </c>
+      <c r="G29">
+        <v>245.8</v>
+      </c>
+      <c r="H29">
+        <v>604</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>472.3</v>
+      </c>
+      <c r="K29">
+        <v>11.1</v>
+      </c>
+      <c r="L29">
+        <v>461.2</v>
+      </c>
+      <c r="M29">
+        <v>17.4806613</v>
+      </c>
+      <c r="N29">
+        <v>443.7193387</v>
+      </c>
+      <c r="O29">
+        <v>88.74386774000003</v>
+      </c>
+      <c r="P29">
+        <v>354.9754709599999</v>
+      </c>
+      <c r="Q29">
+        <v>366.07547096</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1703804066792009</v>
+      </c>
+      <c r="T29">
+        <v>1.430137453178587</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W29">
+        <v>0.03656</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>26.38344122599069</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1340234235208995</v>
+      </c>
+      <c r="C30">
+        <v>1116.702468141146</v>
+      </c>
+      <c r="D30">
+        <v>1267.578468141146</v>
+      </c>
+      <c r="E30">
+        <v>-416.024</v>
+      </c>
+      <c r="F30">
+        <v>396.676</v>
+      </c>
+      <c r="G30">
+        <v>245.8</v>
+      </c>
+      <c r="H30">
+        <v>604</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>472.3</v>
+      </c>
+      <c r="K30">
+        <v>11.1</v>
+      </c>
+      <c r="L30">
+        <v>461.2</v>
+      </c>
+      <c r="M30">
+        <v>18.1280932</v>
+      </c>
+      <c r="N30">
+        <v>443.0719068</v>
+      </c>
+      <c r="O30">
+        <v>88.61438136000002</v>
+      </c>
+      <c r="P30">
+        <v>354.4575254399999</v>
+      </c>
+      <c r="Q30">
+        <v>365.5575254399999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1719258660012493</v>
+      </c>
+      <c r="T30">
+        <v>1.446934933248808</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W30">
+        <v>0.03656</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>25.44117546791959</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1337979501659823</v>
+      </c>
+      <c r="C31">
+        <v>1104.88037633079</v>
+      </c>
+      <c r="D31">
+        <v>1269.92337633079</v>
+      </c>
+      <c r="E31">
+        <v>-401.8570000000001</v>
+      </c>
+      <c r="F31">
+        <v>410.843</v>
+      </c>
+      <c r="G31">
+        <v>245.8</v>
+      </c>
+      <c r="H31">
+        <v>604</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>472.3</v>
+      </c>
+      <c r="K31">
+        <v>11.1</v>
+      </c>
+      <c r="L31">
+        <v>461.2</v>
+      </c>
+      <c r="M31">
+        <v>18.7755251</v>
+      </c>
+      <c r="N31">
+        <v>442.4244749</v>
+      </c>
+      <c r="O31">
+        <v>88.48489498000004</v>
+      </c>
+      <c r="P31">
+        <v>353.93957992</v>
+      </c>
+      <c r="Q31">
+        <v>365.03957992</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1735148593887075</v>
+      </c>
+      <c r="T31">
+        <v>1.464205581771711</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.03656</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>24.56389355523271</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1335724768110652</v>
+      </c>
+      <c r="C32">
+        <v>1093.066976345551</v>
+      </c>
+      <c r="D32">
+        <v>1272.276976345551</v>
+      </c>
+      <c r="E32">
+        <v>-387.6900000000001</v>
+      </c>
+      <c r="F32">
+        <v>425.01</v>
+      </c>
+      <c r="G32">
+        <v>245.8</v>
+      </c>
+      <c r="H32">
+        <v>604</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>472.3</v>
+      </c>
+      <c r="K32">
+        <v>11.1</v>
+      </c>
+      <c r="L32">
+        <v>461.2</v>
+      </c>
+      <c r="M32">
+        <v>19.422957</v>
+      </c>
+      <c r="N32">
+        <v>441.777043</v>
+      </c>
+      <c r="O32">
+        <v>88.35540860000003</v>
+      </c>
+      <c r="P32">
+        <v>353.4216344</v>
+      </c>
+      <c r="Q32">
+        <v>364.5216344</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.175149252587236</v>
+      </c>
+      <c r="T32">
+        <v>1.481969677395268</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.03656</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>23.74509710339162</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.133347003456148</v>
+      </c>
+      <c r="C33">
+        <v>1081.262316601888</v>
+      </c>
+      <c r="D33">
+        <v>1274.639316601888</v>
+      </c>
+      <c r="E33">
+        <v>-373.523</v>
+      </c>
+      <c r="F33">
+        <v>439.177</v>
+      </c>
+      <c r="G33">
+        <v>245.8</v>
+      </c>
+      <c r="H33">
+        <v>604</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>472.3</v>
+      </c>
+      <c r="K33">
+        <v>11.1</v>
+      </c>
+      <c r="L33">
+        <v>461.2</v>
+      </c>
+      <c r="M33">
+        <v>20.0703889</v>
+      </c>
+      <c r="N33">
+        <v>441.1296111</v>
+      </c>
+      <c r="O33">
+        <v>88.22592222000003</v>
+      </c>
+      <c r="P33">
+        <v>352.9036888799999</v>
+      </c>
+      <c r="Q33">
+        <v>364.00368888</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1768310195016638</v>
+      </c>
+      <c r="T33">
+        <v>1.500248674341247</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W33">
+        <v>0.03656</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>22.97912622908866</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1331215301012308</v>
+      </c>
+      <c r="C34">
+        <v>1069.466445876522</v>
+      </c>
+      <c r="D34">
+        <v>1277.010445876522</v>
+      </c>
+      <c r="E34">
+        <v>-359.356</v>
+      </c>
+      <c r="F34">
+        <v>453.3440000000001</v>
+      </c>
+      <c r="G34">
+        <v>245.8</v>
+      </c>
+      <c r="H34">
+        <v>604</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>472.3</v>
+      </c>
+      <c r="K34">
+        <v>11.1</v>
+      </c>
+      <c r="L34">
+        <v>461.2</v>
+      </c>
+      <c r="M34">
+        <v>20.71782080000001</v>
+      </c>
+      <c r="N34">
+        <v>440.4821792</v>
+      </c>
+      <c r="O34">
+        <v>88.09643584000003</v>
+      </c>
+      <c r="P34">
+        <v>352.3857433599999</v>
+      </c>
+      <c r="Q34">
+        <v>363.48574336</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1785622501488689</v>
+      </c>
+      <c r="T34">
+        <v>1.519065288844461</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W34">
+        <v>0.03656</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>22.26102853442964</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1328960567463137</v>
+      </c>
+      <c r="C35">
+        <v>1057.679413309799</v>
+      </c>
+      <c r="D35">
+        <v>1279.390413309799</v>
+      </c>
+      <c r="E35">
+        <v>-345.189</v>
+      </c>
+      <c r="F35">
+        <v>467.511</v>
+      </c>
+      <c r="G35">
+        <v>245.8</v>
+      </c>
+      <c r="H35">
+        <v>604</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>472.3</v>
+      </c>
+      <c r="K35">
+        <v>11.1</v>
+      </c>
+      <c r="L35">
+        <v>461.2</v>
+      </c>
+      <c r="M35">
+        <v>21.3652527</v>
+      </c>
+      <c r="N35">
+        <v>439.8347473</v>
+      </c>
+      <c r="O35">
+        <v>87.96694946000002</v>
+      </c>
+      <c r="P35">
+        <v>351.86779784</v>
+      </c>
+      <c r="Q35">
+        <v>362.96779784</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1803451593228563</v>
+      </c>
+      <c r="T35">
+        <v>1.538443593332846</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W35">
+        <v>0.03656</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>21.5864519121742</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1326705833913965</v>
+      </c>
+      <c r="C36">
+        <v>1045.901268409076</v>
+      </c>
+      <c r="D36">
+        <v>1281.779268409076</v>
+      </c>
+      <c r="E36">
+        <v>-331.022</v>
+      </c>
+      <c r="F36">
+        <v>481.6780000000001</v>
+      </c>
+      <c r="G36">
+        <v>245.8</v>
+      </c>
+      <c r="H36">
+        <v>604</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>472.3</v>
+      </c>
+      <c r="K36">
+        <v>11.1</v>
+      </c>
+      <c r="L36">
+        <v>461.2</v>
+      </c>
+      <c r="M36">
+        <v>22.0126846</v>
+      </c>
+      <c r="N36">
+        <v>439.1873154</v>
+      </c>
+      <c r="O36">
+        <v>87.83746308000002</v>
+      </c>
+      <c r="P36">
+        <v>351.34985232</v>
+      </c>
+      <c r="Q36">
+        <v>362.44985232</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1821820960475705</v>
+      </c>
+      <c r="T36">
+        <v>1.558409119169363</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W36">
+        <v>0.03656</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>20.95155626769849</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1324451100364794</v>
+      </c>
+      <c r="C37">
+        <v>1034.132061052162</v>
+      </c>
+      <c r="D37">
+        <v>1284.177061052162</v>
+      </c>
+      <c r="E37">
+        <v>-316.855</v>
+      </c>
+      <c r="F37">
+        <v>495.8450000000001</v>
+      </c>
+      <c r="G37">
+        <v>245.8</v>
+      </c>
+      <c r="H37">
+        <v>604</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>472.3</v>
+      </c>
+      <c r="K37">
+        <v>11.1</v>
+      </c>
+      <c r="L37">
+        <v>461.2</v>
+      </c>
+      <c r="M37">
+        <v>22.6601165</v>
+      </c>
+      <c r="N37">
+        <v>438.5398835</v>
+      </c>
+      <c r="O37">
+        <v>87.70797670000002</v>
+      </c>
+      <c r="P37">
+        <v>350.8319068</v>
+      </c>
+      <c r="Q37">
+        <v>361.9319068</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.184075553902276</v>
+      </c>
+      <c r="T37">
+        <v>1.578988968877773</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.03656</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>20.35294037433567</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1322196366815622</v>
+      </c>
+      <c r="C38">
+        <v>1022.371841490785</v>
+      </c>
+      <c r="D38">
+        <v>1286.583841490785</v>
+      </c>
+      <c r="E38">
+        <v>-302.688</v>
+      </c>
+      <c r="F38">
+        <v>510.012</v>
+      </c>
+      <c r="G38">
+        <v>245.8</v>
+      </c>
+      <c r="H38">
+        <v>604</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>472.3</v>
+      </c>
+      <c r="K38">
+        <v>11.1</v>
+      </c>
+      <c r="L38">
+        <v>461.2</v>
+      </c>
+      <c r="M38">
+        <v>23.3075484</v>
+      </c>
+      <c r="N38">
+        <v>437.8924516</v>
+      </c>
+      <c r="O38">
+        <v>87.57849032000001</v>
+      </c>
+      <c r="P38">
+        <v>350.3139612799999</v>
+      </c>
+      <c r="Q38">
+        <v>361.41396128</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.186028182314941</v>
+      </c>
+      <c r="T38">
+        <v>1.600211938889571</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W38">
+        <v>0.03656</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>19.78758091949301</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1319941633266451</v>
+      </c>
+      <c r="C39">
+        <v>1010.620660354105</v>
+      </c>
+      <c r="D39">
+        <v>1288.999660354105</v>
+      </c>
+      <c r="E39">
+        <v>-288.5210000000001</v>
+      </c>
+      <c r="F39">
+        <v>524.179</v>
+      </c>
+      <c r="G39">
+        <v>245.8</v>
+      </c>
+      <c r="H39">
+        <v>604</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>472.3</v>
+      </c>
+      <c r="K39">
+        <v>11.1</v>
+      </c>
+      <c r="L39">
+        <v>461.2</v>
+      </c>
+      <c r="M39">
+        <v>23.9549803</v>
+      </c>
+      <c r="N39">
+        <v>437.2450197</v>
+      </c>
+      <c r="O39">
+        <v>87.44900394000003</v>
+      </c>
+      <c r="P39">
+        <v>349.79601576</v>
+      </c>
+      <c r="Q39">
+        <v>360.89601576</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1880427989311826</v>
+      </c>
+      <c r="T39">
+        <v>1.622108653981109</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W39">
+        <v>0.03656</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>19.25278143518239</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1317686899717279</v>
+      </c>
+      <c r="C40">
+        <v>998.878568652261</v>
+      </c>
+      <c r="D40">
+        <v>1291.424568652261</v>
+      </c>
+      <c r="E40">
+        <v>-274.354</v>
+      </c>
+      <c r="F40">
+        <v>538.346</v>
+      </c>
+      <c r="G40">
+        <v>245.8</v>
+      </c>
+      <c r="H40">
+        <v>604</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>472.3</v>
+      </c>
+      <c r="K40">
+        <v>11.1</v>
+      </c>
+      <c r="L40">
+        <v>461.2</v>
+      </c>
+      <c r="M40">
+        <v>24.6024122</v>
+      </c>
+      <c r="N40">
+        <v>436.5975878</v>
+      </c>
+      <c r="O40">
+        <v>87.31951756000002</v>
+      </c>
+      <c r="P40">
+        <v>349.27807024</v>
+      </c>
+      <c r="Q40">
+        <v>360.37807024</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1901224031802063</v>
+      </c>
+      <c r="T40">
+        <v>1.644711714720761</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W40">
+        <v>0.03656</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>18.74612929215128</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1315432166168107</v>
+      </c>
+      <c r="C41">
+        <v>987.1456177799652</v>
+      </c>
+      <c r="D41">
+        <v>1293.858617779965</v>
+      </c>
+      <c r="E41">
+        <v>-260.187</v>
+      </c>
+      <c r="F41">
+        <v>552.513</v>
+      </c>
+      <c r="G41">
+        <v>245.8</v>
+      </c>
+      <c r="H41">
+        <v>604</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>472.3</v>
+      </c>
+      <c r="K41">
+        <v>11.1</v>
+      </c>
+      <c r="L41">
+        <v>461.2</v>
+      </c>
+      <c r="M41">
+        <v>25.2498441</v>
+      </c>
+      <c r="N41">
+        <v>435.9501559</v>
+      </c>
+      <c r="O41">
+        <v>87.19003118000002</v>
+      </c>
+      <c r="P41">
+        <v>348.76012472</v>
+      </c>
+      <c r="Q41">
+        <v>359.86012472</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1922701911750996</v>
+      </c>
+      <c r="T41">
+        <v>1.668055859419089</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W41">
+        <v>0.03656</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>18.26545931030124</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1313177432618936</v>
+      </c>
+      <c r="C42">
+        <v>975.4218595201303</v>
+      </c>
+      <c r="D42">
+        <v>1296.30185952013</v>
+      </c>
+      <c r="E42">
+        <v>-246.02</v>
+      </c>
+      <c r="F42">
+        <v>566.6800000000001</v>
+      </c>
+      <c r="G42">
+        <v>245.8</v>
+      </c>
+      <c r="H42">
+        <v>604</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>472.3</v>
+      </c>
+      <c r="K42">
+        <v>11.1</v>
+      </c>
+      <c r="L42">
+        <v>461.2</v>
+      </c>
+      <c r="M42">
+        <v>25.89727600000001</v>
+      </c>
+      <c r="N42">
+        <v>435.302724</v>
+      </c>
+      <c r="O42">
+        <v>87.06054480000003</v>
+      </c>
+      <c r="P42">
+        <v>348.2421792</v>
+      </c>
+      <c r="Q42">
+        <v>359.3421792</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.194489572103156</v>
+      </c>
+      <c r="T42">
+        <v>1.692178142274029</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W42">
+        <v>0.03656</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>17.80882282754371</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1310922699069764</v>
+      </c>
+      <c r="C43">
+        <v>963.7073460475445</v>
+      </c>
+      <c r="D43">
+        <v>1298.754346047545</v>
+      </c>
+      <c r="E43">
+        <v>-231.853</v>
+      </c>
+      <c r="F43">
+        <v>580.8470000000001</v>
+      </c>
+      <c r="G43">
+        <v>245.8</v>
+      </c>
+      <c r="H43">
+        <v>604</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>472.3</v>
+      </c>
+      <c r="K43">
+        <v>11.1</v>
+      </c>
+      <c r="L43">
+        <v>461.2</v>
+      </c>
+      <c r="M43">
+        <v>26.54470790000001</v>
+      </c>
+      <c r="N43">
+        <v>434.6552921</v>
+      </c>
+      <c r="O43">
+        <v>86.93105842000003</v>
+      </c>
+      <c r="P43">
+        <v>347.72423368</v>
+      </c>
+      <c r="Q43">
+        <v>358.82423368</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1967841862830109</v>
+      </c>
+      <c r="T43">
+        <v>1.717118129632527</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W43">
+        <v>0.03656</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>17.3744612951646</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1308667965520593</v>
+      </c>
+      <c r="C44">
+        <v>952.0021299325846</v>
+      </c>
+      <c r="D44">
+        <v>1301.216129932585</v>
+      </c>
+      <c r="E44">
+        <v>-217.686</v>
+      </c>
+      <c r="F44">
+        <v>595.014</v>
+      </c>
+      <c r="G44">
+        <v>245.8</v>
+      </c>
+      <c r="H44">
+        <v>604</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>472.3</v>
+      </c>
+      <c r="K44">
+        <v>11.1</v>
+      </c>
+      <c r="L44">
+        <v>461.2</v>
+      </c>
+      <c r="M44">
+        <v>27.1921398</v>
+      </c>
+      <c r="N44">
+        <v>434.0078602</v>
+      </c>
+      <c r="O44">
+        <v>86.80157204000002</v>
+      </c>
+      <c r="P44">
+        <v>347.20628816</v>
+      </c>
+      <c r="Q44">
+        <v>358.30628816</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1991579250897573</v>
+      </c>
+      <c r="T44">
+        <v>1.74291811655511</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W44">
+        <v>0.03656</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>16.96078364527973</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1306413231971421</v>
+      </c>
+      <c r="C45">
+        <v>940.306264144971</v>
+      </c>
+      <c r="D45">
+        <v>1303.687264144971</v>
+      </c>
+      <c r="E45">
+        <v>-203.519</v>
+      </c>
+      <c r="F45">
+        <v>609.181</v>
+      </c>
+      <c r="G45">
+        <v>245.8</v>
+      </c>
+      <c r="H45">
+        <v>604</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>472.3</v>
+      </c>
+      <c r="K45">
+        <v>11.1</v>
+      </c>
+      <c r="L45">
+        <v>461.2</v>
+      </c>
+      <c r="M45">
+        <v>27.8395717</v>
+      </c>
+      <c r="N45">
+        <v>433.3604283</v>
+      </c>
+      <c r="O45">
+        <v>86.67208566000002</v>
+      </c>
+      <c r="P45">
+        <v>346.68834264</v>
+      </c>
+      <c r="Q45">
+        <v>357.78834264</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2016149529774423</v>
+      </c>
+      <c r="T45">
+        <v>1.769623366176731</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W45">
+        <v>0.03656</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>16.56634681631973</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.130415849842225</v>
+      </c>
+      <c r="C46">
+        <v>928.6198020575692</v>
+      </c>
+      <c r="D46">
+        <v>1306.167802057569</v>
+      </c>
+      <c r="E46">
+        <v>-189.352</v>
+      </c>
+      <c r="F46">
+        <v>623.3480000000001</v>
+      </c>
+      <c r="G46">
+        <v>245.8</v>
+      </c>
+      <c r="H46">
+        <v>604</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>472.3</v>
+      </c>
+      <c r="K46">
+        <v>11.1</v>
+      </c>
+      <c r="L46">
+        <v>461.2</v>
+      </c>
+      <c r="M46">
+        <v>28.4870036</v>
+      </c>
+      <c r="N46">
+        <v>432.7129964</v>
+      </c>
+      <c r="O46">
+        <v>86.54259928000003</v>
+      </c>
+      <c r="P46">
+        <v>346.17039712</v>
+      </c>
+      <c r="Q46">
+        <v>357.27039712</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.204159731861116</v>
+      </c>
+      <c r="T46">
+        <v>1.79728237471341</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W46">
+        <v>0.03656</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>16.18983893413065</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1301903764873078</v>
+      </c>
+      <c r="C47">
+        <v>916.9427974502313</v>
+      </c>
+      <c r="D47">
+        <v>1308.657797450231</v>
+      </c>
+      <c r="E47">
+        <v>-175.1850000000001</v>
+      </c>
+      <c r="F47">
+        <v>637.515</v>
+      </c>
+      <c r="G47">
+        <v>245.8</v>
+      </c>
+      <c r="H47">
+        <v>604</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>472.3</v>
+      </c>
+      <c r="K47">
+        <v>11.1</v>
+      </c>
+      <c r="L47">
+        <v>461.2</v>
+      </c>
+      <c r="M47">
+        <v>29.1344355</v>
+      </c>
+      <c r="N47">
+        <v>432.0655645</v>
+      </c>
+      <c r="O47">
+        <v>86.41311290000003</v>
+      </c>
+      <c r="P47">
+        <v>345.6524515999999</v>
+      </c>
+      <c r="Q47">
+        <v>356.7524516</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2067970481587414</v>
+      </c>
+      <c r="T47">
+        <v>1.825947165378695</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W47">
+        <v>0.03656</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>15.83006473559441</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1299649031323906</v>
+      </c>
+      <c r="C48">
+        <v>905.2753045136812</v>
+      </c>
+      <c r="D48">
+        <v>1311.157304513681</v>
+      </c>
+      <c r="E48">
+        <v>-161.018</v>
+      </c>
+      <c r="F48">
+        <v>651.682</v>
+      </c>
+      <c r="G48">
+        <v>245.8</v>
+      </c>
+      <c r="H48">
+        <v>604</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>472.3</v>
+      </c>
+      <c r="K48">
+        <v>11.1</v>
+      </c>
+      <c r="L48">
+        <v>461.2</v>
+      </c>
+      <c r="M48">
+        <v>29.7818674</v>
+      </c>
+      <c r="N48">
+        <v>431.4181326</v>
+      </c>
+      <c r="O48">
+        <v>86.28362652000003</v>
+      </c>
+      <c r="P48">
+        <v>345.1345060799999</v>
+      </c>
+      <c r="Q48">
+        <v>356.23450608</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2095320428377604</v>
+      </c>
+      <c r="T48">
+        <v>1.855673614957511</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W48">
+        <v>0.03656</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>15.48593289351627</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1297394297774735</v>
+      </c>
+      <c r="C49">
+        <v>893.6173778534488</v>
+      </c>
+      <c r="D49">
+        <v>1313.666377853449</v>
+      </c>
+      <c r="E49">
+        <v>-146.851</v>
+      </c>
+      <c r="F49">
+        <v>665.849</v>
+      </c>
+      <c r="G49">
+        <v>245.8</v>
+      </c>
+      <c r="H49">
+        <v>604</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>472.3</v>
+      </c>
+      <c r="K49">
+        <v>11.1</v>
+      </c>
+      <c r="L49">
+        <v>461.2</v>
+      </c>
+      <c r="M49">
+        <v>30.4292993</v>
+      </c>
+      <c r="N49">
+        <v>430.7707007</v>
+      </c>
+      <c r="O49">
+        <v>86.15414014000002</v>
+      </c>
+      <c r="P49">
+        <v>344.6165605599999</v>
+      </c>
+      <c r="Q49">
+        <v>355.7165605599999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2123702448631575</v>
+      </c>
+      <c r="T49">
+        <v>1.88652181735062</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W49">
+        <v>0.03656</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>15.15644495961167</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1295139564225563</v>
+      </c>
+      <c r="C50">
+        <v>881.9690724938447</v>
+      </c>
+      <c r="D50">
+        <v>1316.185072493845</v>
+      </c>
+      <c r="E50">
+        <v>-132.6840000000001</v>
+      </c>
+      <c r="F50">
+        <v>680.016</v>
+      </c>
+      <c r="G50">
+        <v>245.8</v>
+      </c>
+      <c r="H50">
+        <v>604</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>472.3</v>
+      </c>
+      <c r="K50">
+        <v>11.1</v>
+      </c>
+      <c r="L50">
+        <v>461.2</v>
+      </c>
+      <c r="M50">
+        <v>31.0767312</v>
+      </c>
+      <c r="N50">
+        <v>430.1232688</v>
+      </c>
+      <c r="O50">
+        <v>86.02465376000004</v>
+      </c>
+      <c r="P50">
+        <v>344.09861504</v>
+      </c>
+      <c r="Q50">
+        <v>355.19861504</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.215317608504916</v>
+      </c>
+      <c r="T50">
+        <v>1.918556489066542</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W50">
+        <v>0.03656</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>14.84068568961976</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1292884830676392</v>
+      </c>
+      <c r="C51">
+        <v>870.3304438819825</v>
+      </c>
+      <c r="D51">
+        <v>1318.713443881983</v>
+      </c>
+      <c r="E51">
+        <v>-118.5170000000001</v>
+      </c>
+      <c r="F51">
+        <v>694.183</v>
+      </c>
+      <c r="G51">
+        <v>245.8</v>
+      </c>
+      <c r="H51">
+        <v>604</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>472.3</v>
+      </c>
+      <c r="K51">
+        <v>11.1</v>
+      </c>
+      <c r="L51">
+        <v>461.2</v>
+      </c>
+      <c r="M51">
+        <v>31.7241631</v>
+      </c>
+      <c r="N51">
+        <v>429.4758369</v>
+      </c>
+      <c r="O51">
+        <v>85.89516738000003</v>
+      </c>
+      <c r="P51">
+        <v>343.58066952</v>
+      </c>
+      <c r="Q51">
+        <v>354.68066952</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2183805550345866</v>
+      </c>
+      <c r="T51">
+        <v>1.951847422418382</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W51">
+        <v>0.03656</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>14.53781455309691</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.129063009712722</v>
+      </c>
+      <c r="C52">
+        <v>858.7015478918489</v>
+      </c>
+      <c r="D52">
+        <v>1321.251547891849</v>
+      </c>
+      <c r="E52">
+        <v>-104.35</v>
+      </c>
+      <c r="F52">
+        <v>708.35</v>
+      </c>
+      <c r="G52">
+        <v>245.8</v>
+      </c>
+      <c r="H52">
+        <v>604</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>472.3</v>
+      </c>
+      <c r="K52">
+        <v>11.1</v>
+      </c>
+      <c r="L52">
+        <v>461.2</v>
+      </c>
+      <c r="M52">
+        <v>32.37159500000001</v>
+      </c>
+      <c r="N52">
+        <v>428.828405</v>
+      </c>
+      <c r="O52">
+        <v>85.76568100000003</v>
+      </c>
+      <c r="P52">
+        <v>343.0627239999999</v>
+      </c>
+      <c r="Q52">
+        <v>354.162724</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.221566019425444</v>
+      </c>
+      <c r="T52">
+        <v>1.986469993104295</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W52">
+        <v>0.03656</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>14.24705826203497</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1288375363578048</v>
+      </c>
+      <c r="C53">
+        <v>847.0824408284179</v>
+      </c>
+      <c r="D53">
+        <v>1323.799440828418</v>
+      </c>
+      <c r="E53">
+        <v>-90.18299999999999</v>
+      </c>
+      <c r="F53">
+        <v>722.5170000000001</v>
+      </c>
+      <c r="G53">
+        <v>245.8</v>
+      </c>
+      <c r="H53">
+        <v>604</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>472.3</v>
+      </c>
+      <c r="K53">
+        <v>11.1</v>
+      </c>
+      <c r="L53">
+        <v>461.2</v>
+      </c>
+      <c r="M53">
+        <v>33.01902690000001</v>
+      </c>
+      <c r="N53">
+        <v>428.1809731</v>
+      </c>
+      <c r="O53">
+        <v>85.63619462000003</v>
+      </c>
+      <c r="P53">
+        <v>342.5447784799999</v>
+      </c>
+      <c r="Q53">
+        <v>353.64477848</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2248815027710303</v>
+      </c>
+      <c r="T53">
+        <v>2.022505729940654</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W53">
+        <v>0.03656</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>13.96770417846566</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1286120630028877</v>
+      </c>
+      <c r="C54">
+        <v>835.4731794318151</v>
+      </c>
+      <c r="D54">
+        <v>1326.357179431815</v>
+      </c>
+      <c r="E54">
+        <v>-76.01599999999996</v>
+      </c>
+      <c r="F54">
+        <v>736.6840000000001</v>
+      </c>
+      <c r="G54">
+        <v>245.8</v>
+      </c>
+      <c r="H54">
+        <v>604</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>472.3</v>
+      </c>
+      <c r="K54">
+        <v>11.1</v>
+      </c>
+      <c r="L54">
+        <v>461.2</v>
+      </c>
+      <c r="M54">
+        <v>33.66645880000001</v>
+      </c>
+      <c r="N54">
+        <v>427.5335412</v>
+      </c>
+      <c r="O54">
+        <v>85.50670824000002</v>
+      </c>
+      <c r="P54">
+        <v>342.02683296</v>
+      </c>
+      <c r="Q54">
+        <v>353.12683296</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.228335131256016</v>
+      </c>
+      <c r="T54">
+        <v>2.060042955811862</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W54">
+        <v>0.03656</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>13.69909448272593</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1283865896479705</v>
+      </c>
+      <c r="C55">
+        <v>823.8738208815309</v>
+      </c>
+      <c r="D55">
+        <v>1328.924820881531</v>
+      </c>
+      <c r="E55">
+        <v>-61.84899999999993</v>
+      </c>
+      <c r="F55">
+        <v>750.8510000000001</v>
+      </c>
+      <c r="G55">
+        <v>245.8</v>
+      </c>
+      <c r="H55">
+        <v>604</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>472.3</v>
+      </c>
+      <c r="K55">
+        <v>11.1</v>
+      </c>
+      <c r="L55">
+        <v>461.2</v>
+      </c>
+      <c r="M55">
+        <v>34.31389070000001</v>
+      </c>
+      <c r="N55">
+        <v>426.8861093</v>
+      </c>
+      <c r="O55">
+        <v>85.37722186000002</v>
+      </c>
+      <c r="P55">
+        <v>341.50888744</v>
+      </c>
+      <c r="Q55">
+        <v>352.60888744</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2319357226552564</v>
+      </c>
+      <c r="T55">
+        <v>2.099177510443546</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W55">
+        <v>0.03656</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>13.44062100191978</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1281611162930533</v>
+      </c>
+      <c r="C56">
+        <v>812.2844228006802</v>
+      </c>
+      <c r="D56">
+        <v>1331.50242280068</v>
+      </c>
+      <c r="E56">
+        <v>-47.68200000000002</v>
+      </c>
+      <c r="F56">
+        <v>765.018</v>
+      </c>
+      <c r="G56">
+        <v>245.8</v>
+      </c>
+      <c r="H56">
+        <v>604</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>472.3</v>
+      </c>
+      <c r="K56">
+        <v>11.1</v>
+      </c>
+      <c r="L56">
+        <v>461.2</v>
+      </c>
+      <c r="M56">
+        <v>34.9613226</v>
+      </c>
+      <c r="N56">
+        <v>426.2386774</v>
+      </c>
+      <c r="O56">
+        <v>85.24773548000002</v>
+      </c>
+      <c r="P56">
+        <v>340.99094192</v>
+      </c>
+      <c r="Q56">
+        <v>352.09094192</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2356928615066377</v>
+      </c>
+      <c r="T56">
+        <v>2.140013567450521</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W56">
+        <v>0.03656</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>13.19172061299534</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1279356429381362</v>
+      </c>
+      <c r="C57">
+        <v>800.7050432603113</v>
+      </c>
+      <c r="D57">
+        <v>1334.090043260311</v>
+      </c>
+      <c r="E57">
+        <v>-33.51499999999999</v>
+      </c>
+      <c r="F57">
+        <v>779.1850000000001</v>
+      </c>
+      <c r="G57">
+        <v>245.8</v>
+      </c>
+      <c r="H57">
+        <v>604</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>472.3</v>
+      </c>
+      <c r="K57">
+        <v>11.1</v>
+      </c>
+      <c r="L57">
+        <v>461.2</v>
+      </c>
+      <c r="M57">
+        <v>35.6087545</v>
+      </c>
+      <c r="N57">
+        <v>425.5912455</v>
+      </c>
+      <c r="O57">
+        <v>85.11824910000003</v>
+      </c>
+      <c r="P57">
+        <v>340.4729964</v>
+      </c>
+      <c r="Q57">
+        <v>351.5729964</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2396169843069693</v>
+      </c>
+      <c r="T57">
+        <v>2.182664560324473</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W57">
+        <v>0.03656</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>12.95187114730452</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.128426969583219</v>
+      </c>
+      <c r="C58">
+        <v>780.9122524689678</v>
+      </c>
+      <c r="D58">
+        <v>1328.464252468968</v>
+      </c>
+      <c r="E58">
+        <v>-19.34799999999996</v>
+      </c>
+      <c r="F58">
+        <v>793.3520000000001</v>
+      </c>
+      <c r="G58">
+        <v>245.8</v>
+      </c>
+      <c r="H58">
+        <v>604</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>472.3</v>
+      </c>
+      <c r="K58">
+        <v>11.1</v>
+      </c>
+      <c r="L58">
+        <v>461.2</v>
+      </c>
+      <c r="M58">
+        <v>37.52554960000001</v>
+      </c>
+      <c r="N58">
+        <v>423.6744504</v>
+      </c>
+      <c r="O58">
+        <v>84.73489008000001</v>
+      </c>
+      <c r="P58">
+        <v>338.9395603199999</v>
+      </c>
+      <c r="Q58">
+        <v>350.03956032</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2437194763254978</v>
+      </c>
+      <c r="T58">
+        <v>2.227254234692695</v>
+      </c>
+      <c r="U58">
+        <v>0.0473</v>
+      </c>
+      <c r="V58">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W58">
+        <v>0.03784</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>12.29029301145798</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1282142962283019</v>
+      </c>
+      <c r="C59">
+        <v>769.1745713600475</v>
+      </c>
+      <c r="D59">
+        <v>1330.893571360048</v>
+      </c>
+      <c r="E59">
+        <v>-5.180999999999926</v>
+      </c>
+      <c r="F59">
+        <v>807.5190000000001</v>
+      </c>
+      <c r="G59">
+        <v>245.8</v>
+      </c>
+      <c r="H59">
+        <v>604</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>472.3</v>
+      </c>
+      <c r="K59">
+        <v>11.1</v>
+      </c>
+      <c r="L59">
+        <v>461.2</v>
+      </c>
+      <c r="M59">
+        <v>38.19564870000001</v>
+      </c>
+      <c r="N59">
+        <v>423.0043513</v>
+      </c>
+      <c r="O59">
+        <v>84.60087026000002</v>
+      </c>
+      <c r="P59">
+        <v>338.40348104</v>
+      </c>
+      <c r="Q59">
+        <v>349.50348104</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2480127819262834</v>
+      </c>
+      <c r="T59">
+        <v>2.273917847403625</v>
+      </c>
+      <c r="U59">
+        <v>0.0473</v>
+      </c>
+      <c r="V59">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W59">
+        <v>0.03784</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>12.07467383581837</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1280016228733847</v>
+      </c>
+      <c r="C60">
+        <v>757.4457913594244</v>
+      </c>
+      <c r="D60">
+        <v>1333.331791359424</v>
+      </c>
+      <c r="E60">
+        <v>8.985999999999876</v>
+      </c>
+      <c r="F60">
+        <v>821.6859999999999</v>
+      </c>
+      <c r="G60">
+        <v>245.8</v>
+      </c>
+      <c r="H60">
+        <v>604</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>472.3</v>
+      </c>
+      <c r="K60">
+        <v>11.1</v>
+      </c>
+      <c r="L60">
+        <v>461.2</v>
+      </c>
+      <c r="M60">
+        <v>38.8657478</v>
+      </c>
+      <c r="N60">
+        <v>422.3342522</v>
+      </c>
+      <c r="O60">
+        <v>84.46685044000003</v>
+      </c>
+      <c r="P60">
+        <v>337.86740176</v>
+      </c>
+      <c r="Q60">
+        <v>348.96740176</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2525105306509159</v>
+      </c>
+      <c r="T60">
+        <v>2.322803536910313</v>
+      </c>
+      <c r="U60">
+        <v>0.0473</v>
+      </c>
+      <c r="V60">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W60">
+        <v>0.03784</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>11.86648980416633</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1277889495184675</v>
+      </c>
+      <c r="C61">
+        <v>745.7259614778383</v>
+      </c>
+      <c r="D61">
+        <v>1335.778961477838</v>
+      </c>
+      <c r="E61">
+        <v>23.15299999999991</v>
+      </c>
+      <c r="F61">
+        <v>835.853</v>
+      </c>
+      <c r="G61">
+        <v>245.8</v>
+      </c>
+      <c r="H61">
+        <v>604</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>472.3</v>
+      </c>
+      <c r="K61">
+        <v>11.1</v>
+      </c>
+      <c r="L61">
+        <v>461.2</v>
+      </c>
+      <c r="M61">
+        <v>39.5358469</v>
+      </c>
+      <c r="N61">
+        <v>421.6641531</v>
+      </c>
+      <c r="O61">
+        <v>84.33283062000004</v>
+      </c>
+      <c r="P61">
+        <v>337.33132248</v>
+      </c>
+      <c r="Q61">
+        <v>348.43132248</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2572276817523598</v>
+      </c>
+      <c r="T61">
+        <v>2.374073894197816</v>
+      </c>
+      <c r="U61">
+        <v>0.0473</v>
+      </c>
+      <c r="V61">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W61">
+        <v>0.03784</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>11.665362858333</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1275762761635504</v>
+      </c>
+      <c r="C62">
+        <v>734.0151310865053</v>
+      </c>
+      <c r="D62">
+        <v>1338.235131086505</v>
+      </c>
+      <c r="E62">
+        <v>37.31999999999994</v>
+      </c>
+      <c r="F62">
+        <v>850.02</v>
+      </c>
+      <c r="G62">
+        <v>245.8</v>
+      </c>
+      <c r="H62">
+        <v>604</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>472.3</v>
+      </c>
+      <c r="K62">
+        <v>11.1</v>
+      </c>
+      <c r="L62">
+        <v>461.2</v>
+      </c>
+      <c r="M62">
+        <v>40.205946</v>
+      </c>
+      <c r="N62">
+        <v>420.994054</v>
+      </c>
+      <c r="O62">
+        <v>84.19881080000003</v>
+      </c>
+      <c r="P62">
+        <v>336.7952432</v>
+      </c>
+      <c r="Q62">
+        <v>347.8952432</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2621806904088759</v>
+      </c>
+      <c r="T62">
+        <v>2.427907769349694</v>
+      </c>
+      <c r="U62">
+        <v>0.0473</v>
+      </c>
+      <c r="V62">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W62">
+        <v>0.03784</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>11.47094014402745</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1273636028086332</v>
+      </c>
+      <c r="C63">
+        <v>722.3133499204363</v>
+      </c>
+      <c r="D63">
+        <v>1340.700349920436</v>
+      </c>
+      <c r="E63">
+        <v>51.48699999999997</v>
+      </c>
+      <c r="F63">
+        <v>864.187</v>
+      </c>
+      <c r="G63">
+        <v>245.8</v>
+      </c>
+      <c r="H63">
+        <v>604</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>472.3</v>
+      </c>
+      <c r="K63">
+        <v>11.1</v>
+      </c>
+      <c r="L63">
+        <v>461.2</v>
+      </c>
+      <c r="M63">
+        <v>40.8760451</v>
+      </c>
+      <c r="N63">
+        <v>420.3239549</v>
+      </c>
+      <c r="O63">
+        <v>84.06479098000003</v>
+      </c>
+      <c r="P63">
+        <v>336.25916392</v>
+      </c>
+      <c r="Q63">
+        <v>347.35916392</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.267387699509316</v>
+      </c>
+      <c r="T63">
+        <v>2.484502356047822</v>
+      </c>
+      <c r="U63">
+        <v>0.0473</v>
+      </c>
+      <c r="V63">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W63">
+        <v>0.03784</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>11.28289194494504</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.127150929453716</v>
+      </c>
+      <c r="C64">
+        <v>710.6206680817943</v>
+      </c>
+      <c r="D64">
+        <v>1343.174668081794</v>
+      </c>
+      <c r="E64">
+        <v>65.654</v>
+      </c>
+      <c r="F64">
+        <v>878.354</v>
+      </c>
+      <c r="G64">
+        <v>245.8</v>
+      </c>
+      <c r="H64">
+        <v>604</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>472.3</v>
+      </c>
+      <c r="K64">
+        <v>11.1</v>
+      </c>
+      <c r="L64">
+        <v>461.2</v>
+      </c>
+      <c r="M64">
+        <v>41.5461442</v>
+      </c>
+      <c r="N64">
+        <v>419.6538558</v>
+      </c>
+      <c r="O64">
+        <v>83.93077116000002</v>
+      </c>
+      <c r="P64">
+        <v>335.72308464</v>
+      </c>
+      <c r="Q64">
+        <v>346.82308464</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2728687617203054</v>
+      </c>
+      <c r="T64">
+        <v>2.544075605203746</v>
+      </c>
+      <c r="U64">
+        <v>0.0473</v>
+      </c>
+      <c r="V64">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W64">
+        <v>0.03784</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>11.10090981680076</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1269382560987989</v>
+      </c>
+      <c r="C65">
+        <v>698.9371360432878</v>
+      </c>
+      <c r="D65">
+        <v>1345.658136043288</v>
+      </c>
+      <c r="E65">
+        <v>79.82100000000003</v>
+      </c>
+      <c r="F65">
+        <v>892.5210000000001</v>
+      </c>
+      <c r="G65">
+        <v>245.8</v>
+      </c>
+      <c r="H65">
+        <v>604</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>472.3</v>
+      </c>
+      <c r="K65">
+        <v>11.1</v>
+      </c>
+      <c r="L65">
+        <v>461.2</v>
+      </c>
+      <c r="M65">
+        <v>42.2162433</v>
+      </c>
+      <c r="N65">
+        <v>418.9837567</v>
+      </c>
+      <c r="O65">
+        <v>83.79675134000001</v>
+      </c>
+      <c r="P65">
+        <v>335.1870053599999</v>
+      </c>
+      <c r="Q65">
+        <v>346.28700536</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2786460975643213</v>
+      </c>
+      <c r="T65">
+        <v>2.606869029989721</v>
+      </c>
+      <c r="U65">
+        <v>0.0473</v>
+      </c>
+      <c r="V65">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W65">
+        <v>0.03784</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>10.92470489907376</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1267255827438817</v>
+      </c>
+      <c r="C66">
+        <v>687.2628046516047</v>
+      </c>
+      <c r="D66">
+        <v>1348.150804651605</v>
+      </c>
+      <c r="E66">
+        <v>93.98800000000006</v>
+      </c>
+      <c r="F66">
+        <v>906.6880000000001</v>
+      </c>
+      <c r="G66">
+        <v>245.8</v>
+      </c>
+      <c r="H66">
+        <v>604</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>472.3</v>
+      </c>
+      <c r="K66">
+        <v>11.1</v>
+      </c>
+      <c r="L66">
+        <v>461.2</v>
+      </c>
+      <c r="M66">
+        <v>42.8863424</v>
+      </c>
+      <c r="N66">
+        <v>418.3136576</v>
+      </c>
+      <c r="O66">
+        <v>83.66273152000002</v>
+      </c>
+      <c r="P66">
+        <v>334.65092608</v>
+      </c>
+      <c r="Q66">
+        <v>345.75092608</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2847443965107826</v>
+      </c>
+      <c r="T66">
+        <v>2.673150978374916</v>
+      </c>
+      <c r="U66">
+        <v>0.0473</v>
+      </c>
+      <c r="V66">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W66">
+        <v>0.03784</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>10.75400638502574</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1265129093889646</v>
+      </c>
+      <c r="C67">
+        <v>675.5977251308814</v>
+      </c>
+      <c r="D67">
+        <v>1350.652725130881</v>
+      </c>
+      <c r="E67">
+        <v>108.155</v>
+      </c>
+      <c r="F67">
+        <v>920.855</v>
+      </c>
+      <c r="G67">
+        <v>245.8</v>
+      </c>
+      <c r="H67">
+        <v>604</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>472.3</v>
+      </c>
+      <c r="K67">
+        <v>11.1</v>
+      </c>
+      <c r="L67">
+        <v>461.2</v>
+      </c>
+      <c r="M67">
+        <v>43.55644150000001</v>
+      </c>
+      <c r="N67">
+        <v>417.6435585</v>
+      </c>
+      <c r="O67">
+        <v>83.52871170000003</v>
+      </c>
+      <c r="P67">
+        <v>334.1148468</v>
+      </c>
+      <c r="Q67">
+        <v>345.2148468</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2911911696827559</v>
+      </c>
+      <c r="T67">
+        <v>2.743220466667836</v>
+      </c>
+      <c r="U67">
+        <v>0.0473</v>
+      </c>
+      <c r="V67">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W67">
+        <v>0.03784</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>10.58856013294842</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1263002360340474</v>
+      </c>
+      <c r="C68">
+        <v>663.9419490862105</v>
+      </c>
+      <c r="D68">
+        <v>1353.163949086211</v>
+      </c>
+      <c r="E68">
+        <v>122.322</v>
+      </c>
+      <c r="F68">
+        <v>935.022</v>
+      </c>
+      <c r="G68">
+        <v>245.8</v>
+      </c>
+      <c r="H68">
+        <v>604</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>472.3</v>
+      </c>
+      <c r="K68">
+        <v>11.1</v>
+      </c>
+      <c r="L68">
+        <v>461.2</v>
+      </c>
+      <c r="M68">
+        <v>44.22654060000001</v>
+      </c>
+      <c r="N68">
+        <v>416.9734594</v>
+      </c>
+      <c r="O68">
+        <v>83.39469188000002</v>
+      </c>
+      <c r="P68">
+        <v>333.5787675199999</v>
+      </c>
+      <c r="Q68">
+        <v>344.67876752</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2980171648060218</v>
+      </c>
+      <c r="T68">
+        <v>2.817411689566223</v>
+      </c>
+      <c r="U68">
+        <v>0.0473</v>
+      </c>
+      <c r="V68">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W68">
+        <v>0.03784</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>10.42812740366132</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1260875626791303</v>
+      </c>
+      <c r="C69">
+        <v>652.295528507191</v>
+      </c>
+      <c r="D69">
+        <v>1355.684528507191</v>
+      </c>
+      <c r="E69">
+        <v>136.489</v>
+      </c>
+      <c r="F69">
+        <v>949.1890000000001</v>
+      </c>
+      <c r="G69">
+        <v>245.8</v>
+      </c>
+      <c r="H69">
+        <v>604</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>472.3</v>
+      </c>
+      <c r="K69">
+        <v>11.1</v>
+      </c>
+      <c r="L69">
+        <v>461.2</v>
+      </c>
+      <c r="M69">
+        <v>44.89663970000001</v>
+      </c>
+      <c r="N69">
+        <v>416.3033603</v>
+      </c>
+      <c r="O69">
+        <v>83.26067206000003</v>
+      </c>
+      <c r="P69">
+        <v>333.04268824</v>
+      </c>
+      <c r="Q69">
+        <v>344.14268824</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3052568566034251</v>
+      </c>
+      <c r="T69">
+        <v>2.896099350216027</v>
+      </c>
+      <c r="U69">
+        <v>0.0473</v>
+      </c>
+      <c r="V69">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W69">
+        <v>0.03784</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>10.27248371106936</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1279420893242131</v>
+      </c>
+      <c r="C70">
+        <v>616.4599223552603</v>
+      </c>
+      <c r="D70">
+        <v>1334.01592235526</v>
+      </c>
+      <c r="E70">
+        <v>150.6560000000001</v>
+      </c>
+      <c r="F70">
+        <v>963.3560000000001</v>
+      </c>
+      <c r="G70">
+        <v>245.8</v>
+      </c>
+      <c r="H70">
+        <v>604</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>472.3</v>
+      </c>
+      <c r="K70">
+        <v>11.1</v>
+      </c>
+      <c r="L70">
+        <v>461.2</v>
+      </c>
+      <c r="M70">
+        <v>49.22749160000001</v>
+      </c>
+      <c r="N70">
+        <v>411.9725084</v>
+      </c>
+      <c r="O70">
+        <v>82.39450168000002</v>
+      </c>
+      <c r="P70">
+        <v>329.57800672</v>
+      </c>
+      <c r="Q70">
+        <v>340.67800672</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.312949029138166</v>
+      </c>
+      <c r="T70">
+        <v>2.979704989656443</v>
+      </c>
+      <c r="U70">
+        <v>0.0511</v>
+      </c>
+      <c r="V70">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W70">
+        <v>0.04088</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>9.368748742013901</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1277598159692959</v>
+      </c>
+      <c r="C71">
+        <v>604.3918924483646</v>
+      </c>
+      <c r="D71">
+        <v>1336.114892448365</v>
+      </c>
+      <c r="E71">
+        <v>164.8230000000001</v>
+      </c>
+      <c r="F71">
+        <v>977.5230000000001</v>
+      </c>
+      <c r="G71">
+        <v>245.8</v>
+      </c>
+      <c r="H71">
+        <v>604</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>472.3</v>
+      </c>
+      <c r="K71">
+        <v>11.1</v>
+      </c>
+      <c r="L71">
+        <v>461.2</v>
+      </c>
+      <c r="M71">
+        <v>49.9514253</v>
+      </c>
+      <c r="N71">
+        <v>411.2485747</v>
+      </c>
+      <c r="O71">
+        <v>82.24971494000003</v>
+      </c>
+      <c r="P71">
+        <v>328.99885976</v>
+      </c>
+      <c r="Q71">
+        <v>340.09885976</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3211374708686967</v>
+      </c>
+      <c r="T71">
+        <v>3.068704541318823</v>
+      </c>
+      <c r="U71">
+        <v>0.0511</v>
+      </c>
+      <c r="V71">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W71">
+        <v>0.04088</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>9.23296977473834</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1275775426143788</v>
+      </c>
+      <c r="C72">
+        <v>592.3304780822424</v>
+      </c>
+      <c r="D72">
+        <v>1338.220478082243</v>
+      </c>
+      <c r="E72">
+        <v>178.9900000000001</v>
+      </c>
+      <c r="F72">
+        <v>991.6900000000002</v>
+      </c>
+      <c r="G72">
+        <v>245.8</v>
+      </c>
+      <c r="H72">
+        <v>604</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>472.3</v>
+      </c>
+      <c r="K72">
+        <v>11.1</v>
+      </c>
+      <c r="L72">
+        <v>461.2</v>
+      </c>
+      <c r="M72">
+        <v>50.67535900000001</v>
+      </c>
+      <c r="N72">
+        <v>410.524641</v>
+      </c>
+      <c r="O72">
+        <v>82.10492820000002</v>
+      </c>
+      <c r="P72">
+        <v>328.4197128</v>
+      </c>
+      <c r="Q72">
+        <v>339.5197128</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.329871808714596</v>
+      </c>
+      <c r="T72">
+        <v>3.16363739642536</v>
+      </c>
+      <c r="U72">
+        <v>0.0511</v>
+      </c>
+      <c r="V72">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W72">
+        <v>0.04088</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>9.10107020652779</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1273952692594616</v>
+      </c>
+      <c r="C73">
+        <v>580.2757105825831</v>
+      </c>
+      <c r="D73">
+        <v>1340.332710582583</v>
+      </c>
+      <c r="E73">
+        <v>193.1569999999999</v>
+      </c>
+      <c r="F73">
+        <v>1005.857</v>
+      </c>
+      <c r="G73">
+        <v>245.8</v>
+      </c>
+      <c r="H73">
+        <v>604</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>472.3</v>
+      </c>
+      <c r="K73">
+        <v>11.1</v>
+      </c>
+      <c r="L73">
+        <v>461.2</v>
+      </c>
+      <c r="M73">
+        <v>51.3992927</v>
+      </c>
+      <c r="N73">
+        <v>409.8007073</v>
+      </c>
+      <c r="O73">
+        <v>81.96014146000003</v>
+      </c>
+      <c r="P73">
+        <v>327.84056584</v>
+      </c>
+      <c r="Q73">
+        <v>338.94056584</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3392085146877987</v>
+      </c>
+      <c r="T73">
+        <v>3.265117344987519</v>
+      </c>
+      <c r="U73">
+        <v>0.0511</v>
+      </c>
+      <c r="V73">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W73">
+        <v>0.04088</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>8.972886119111909</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1272129959045445</v>
+      </c>
+      <c r="C74">
+        <v>568.2276214731668</v>
+      </c>
+      <c r="D74">
+        <v>1342.451621473167</v>
+      </c>
+      <c r="E74">
+        <v>207.324</v>
+      </c>
+      <c r="F74">
+        <v>1020.024</v>
+      </c>
+      <c r="G74">
+        <v>245.8</v>
+      </c>
+      <c r="H74">
+        <v>604</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>472.3</v>
+      </c>
+      <c r="K74">
+        <v>11.1</v>
+      </c>
+      <c r="L74">
+        <v>461.2</v>
+      </c>
+      <c r="M74">
+        <v>52.1232264</v>
+      </c>
+      <c r="N74">
+        <v>409.0767736</v>
+      </c>
+      <c r="O74">
+        <v>81.81535472000002</v>
+      </c>
+      <c r="P74">
+        <v>327.26141888</v>
+      </c>
+      <c r="Q74">
+        <v>338.36141888</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.349212128230516</v>
+      </c>
+      <c r="T74">
+        <v>3.373845861304121</v>
+      </c>
+      <c r="U74">
+        <v>0.0511</v>
+      </c>
+      <c r="V74">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W74">
+        <v>0.04088</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>8.848262700790908</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1270307225496273</v>
+      </c>
+      <c r="C75">
+        <v>556.1862424774308</v>
+      </c>
+      <c r="D75">
+        <v>1344.577242477431</v>
+      </c>
+      <c r="E75">
+        <v>221.491</v>
+      </c>
+      <c r="F75">
+        <v>1034.191</v>
+      </c>
+      <c r="G75">
+        <v>245.8</v>
+      </c>
+      <c r="H75">
+        <v>604</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>472.3</v>
+      </c>
+      <c r="K75">
+        <v>11.1</v>
+      </c>
+      <c r="L75">
+        <v>461.2</v>
+      </c>
+      <c r="M75">
+        <v>52.8471601</v>
+      </c>
+      <c r="N75">
+        <v>408.3528399</v>
+      </c>
+      <c r="O75">
+        <v>81.67056798000003</v>
+      </c>
+      <c r="P75">
+        <v>326.6822719199999</v>
+      </c>
+      <c r="Q75">
+        <v>337.78227192</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3599567501838048</v>
+      </c>
+      <c r="T75">
+        <v>3.490628341792321</v>
+      </c>
+      <c r="U75">
+        <v>0.0511</v>
+      </c>
+      <c r="V75">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W75">
+        <v>0.04088</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>8.727053622697882</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1268484491947101</v>
+      </c>
+      <c r="C76">
+        <v>544.1516055200532</v>
+      </c>
+      <c r="D76">
+        <v>1346.709605520053</v>
+      </c>
+      <c r="E76">
+        <v>235.6579999999999</v>
+      </c>
+      <c r="F76">
+        <v>1048.358</v>
+      </c>
+      <c r="G76">
+        <v>245.8</v>
+      </c>
+      <c r="H76">
+        <v>604</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>472.3</v>
+      </c>
+      <c r="K76">
+        <v>11.1</v>
+      </c>
+      <c r="L76">
+        <v>461.2</v>
+      </c>
+      <c r="M76">
+        <v>53.5710938</v>
+      </c>
+      <c r="N76">
+        <v>407.6289062</v>
+      </c>
+      <c r="O76">
+        <v>81.52578124000001</v>
+      </c>
+      <c r="P76">
+        <v>326.1031249599999</v>
+      </c>
+      <c r="Q76">
+        <v>337.20312496</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3715278815181159</v>
+      </c>
+      <c r="T76">
+        <v>3.616394090010383</v>
+      </c>
+      <c r="U76">
+        <v>0.0511</v>
+      </c>
+      <c r="V76">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W76">
+        <v>0.04088</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>8.609120465634398</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.126666175839793</v>
+      </c>
+      <c r="C77">
+        <v>532.1237427285498</v>
+      </c>
+      <c r="D77">
+        <v>1348.84874272855</v>
+      </c>
+      <c r="E77">
+        <v>249.825</v>
+      </c>
+      <c r="F77">
+        <v>1062.525</v>
+      </c>
+      <c r="G77">
+        <v>245.8</v>
+      </c>
+      <c r="H77">
+        <v>604</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>472.3</v>
+      </c>
+      <c r="K77">
+        <v>11.1</v>
+      </c>
+      <c r="L77">
+        <v>461.2</v>
+      </c>
+      <c r="M77">
+        <v>54.2950275</v>
+      </c>
+      <c r="N77">
+        <v>406.9049725</v>
+      </c>
+      <c r="O77">
+        <v>81.38099450000003</v>
+      </c>
+      <c r="P77">
+        <v>325.5239779999999</v>
+      </c>
+      <c r="Q77">
+        <v>336.623978</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3840247033591719</v>
+      </c>
+      <c r="T77">
+        <v>3.752221098085891</v>
+      </c>
+      <c r="U77">
+        <v>0.0511</v>
+      </c>
+      <c r="V77">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W77">
+        <v>0.04088</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>8.494332192759272</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1264839024848758</v>
+      </c>
+      <c r="C78">
+        <v>520.102686434891</v>
+      </c>
+      <c r="D78">
+        <v>1350.994686434891</v>
+      </c>
+      <c r="E78">
+        <v>263.992</v>
+      </c>
+      <c r="F78">
+        <v>1076.692</v>
+      </c>
+      <c r="G78">
+        <v>245.8</v>
+      </c>
+      <c r="H78">
+        <v>604</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>472.3</v>
+      </c>
+      <c r="K78">
+        <v>11.1</v>
+      </c>
+      <c r="L78">
+        <v>461.2</v>
+      </c>
+      <c r="M78">
+        <v>55.0189612</v>
+      </c>
+      <c r="N78">
+        <v>406.1810388</v>
+      </c>
+      <c r="O78">
+        <v>81.23620776000003</v>
+      </c>
+      <c r="P78">
+        <v>324.94483104</v>
+      </c>
+      <c r="Q78">
+        <v>336.04483104</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3975629270203159</v>
+      </c>
+      <c r="T78">
+        <v>3.899367023501024</v>
+      </c>
+      <c r="U78">
+        <v>0.0511</v>
+      </c>
+      <c r="V78">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W78">
+        <v>0.04088</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>8.382564663907177</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1263016291299587</v>
+      </c>
+      <c r="C79">
+        <v>508.0884691771257</v>
+      </c>
+      <c r="D79">
+        <v>1353.147469177126</v>
+      </c>
+      <c r="E79">
+        <v>278.1590000000001</v>
+      </c>
+      <c r="F79">
+        <v>1090.859</v>
+      </c>
+      <c r="G79">
+        <v>245.8</v>
+      </c>
+      <c r="H79">
+        <v>604</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>472.3</v>
+      </c>
+      <c r="K79">
+        <v>11.1</v>
+      </c>
+      <c r="L79">
+        <v>461.2</v>
+      </c>
+      <c r="M79">
+        <v>55.74289490000001</v>
+      </c>
+      <c r="N79">
+        <v>405.4571051</v>
+      </c>
+      <c r="O79">
+        <v>81.09142102000003</v>
+      </c>
+      <c r="P79">
+        <v>324.3656840799999</v>
+      </c>
+      <c r="Q79">
+        <v>335.46568408</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4122783875215595</v>
+      </c>
+      <c r="T79">
+        <v>4.059308246778343</v>
+      </c>
+      <c r="U79">
+        <v>0.0511</v>
+      </c>
+      <c r="V79">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W79">
+        <v>0.04088</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>8.273700187752535</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1261193557750415</v>
+      </c>
+      <c r="C80">
+        <v>496.0811237010321</v>
+      </c>
+      <c r="D80">
+        <v>1355.307123701032</v>
+      </c>
+      <c r="E80">
+        <v>292.326</v>
+      </c>
+      <c r="F80">
+        <v>1105.026</v>
+      </c>
+      <c r="G80">
+        <v>245.8</v>
+      </c>
+      <c r="H80">
+        <v>604</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>472.3</v>
+      </c>
+      <c r="K80">
+        <v>11.1</v>
+      </c>
+      <c r="L80">
+        <v>461.2</v>
+      </c>
+      <c r="M80">
+        <v>56.4668286</v>
+      </c>
+      <c r="N80">
+        <v>404.7331714</v>
+      </c>
+      <c r="O80">
+        <v>80.94663428000003</v>
+      </c>
+      <c r="P80">
+        <v>323.78653712</v>
+      </c>
+      <c r="Q80">
+        <v>334.88653712</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4283316171592796</v>
+      </c>
+      <c r="T80">
+        <v>4.23378958126269</v>
+      </c>
+      <c r="U80">
+        <v>0.0511</v>
+      </c>
+      <c r="V80">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W80">
+        <v>0.04088</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>8.167627108422376</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1259370824201243</v>
+      </c>
+      <c r="C81">
+        <v>484.0806829617718</v>
+      </c>
+      <c r="D81">
+        <v>1357.473682961772</v>
+      </c>
+      <c r="E81">
+        <v>306.4929999999999</v>
+      </c>
+      <c r="F81">
+        <v>1119.193</v>
+      </c>
+      <c r="G81">
+        <v>245.8</v>
+      </c>
+      <c r="H81">
+        <v>604</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>472.3</v>
+      </c>
+      <c r="K81">
+        <v>11.1</v>
+      </c>
+      <c r="L81">
+        <v>461.2</v>
+      </c>
+      <c r="M81">
+        <v>57.1907623</v>
+      </c>
+      <c r="N81">
+        <v>404.0092377</v>
+      </c>
+      <c r="O81">
+        <v>80.80184754000003</v>
+      </c>
+      <c r="P81">
+        <v>323.2073901599999</v>
+      </c>
+      <c r="Q81">
+        <v>334.30739016</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4459137258101159</v>
+      </c>
+      <c r="T81">
+        <v>4.424888185697927</v>
+      </c>
+      <c r="U81">
+        <v>0.0511</v>
+      </c>
+      <c r="V81">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W81">
+        <v>0.04088</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>8.064239423505638</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1257548090652072</v>
+      </c>
+      <c r="C82">
+        <v>472.0871801255691</v>
+      </c>
+      <c r="D82">
+        <v>1359.647180125569</v>
+      </c>
+      <c r="E82">
+        <v>320.6600000000001</v>
+      </c>
+      <c r="F82">
+        <v>1133.36</v>
+      </c>
+      <c r="G82">
+        <v>245.8</v>
+      </c>
+      <c r="H82">
+        <v>604</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>472.3</v>
+      </c>
+      <c r="K82">
+        <v>11.1</v>
+      </c>
+      <c r="L82">
+        <v>461.2</v>
+      </c>
+      <c r="M82">
+        <v>57.91469600000001</v>
+      </c>
+      <c r="N82">
+        <v>403.285304</v>
+      </c>
+      <c r="O82">
+        <v>80.65706080000002</v>
+      </c>
+      <c r="P82">
+        <v>322.6282432</v>
+      </c>
+      <c r="Q82">
+        <v>333.7282432</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.465254045326036</v>
+      </c>
+      <c r="T82">
+        <v>4.63509665057669</v>
+      </c>
+      <c r="U82">
+        <v>0.0511</v>
+      </c>
+      <c r="V82">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W82">
+        <v>0.04088</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>7.963436430711817</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.12557253571029</v>
+      </c>
+      <c r="C83">
+        <v>460.1006485714056</v>
+      </c>
+      <c r="D83">
+        <v>1361.827648571406</v>
+      </c>
+      <c r="E83">
+        <v>334.827</v>
+      </c>
+      <c r="F83">
+        <v>1147.527</v>
+      </c>
+      <c r="G83">
+        <v>245.8</v>
+      </c>
+      <c r="H83">
+        <v>604</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>472.3</v>
+      </c>
+      <c r="K83">
+        <v>11.1</v>
+      </c>
+      <c r="L83">
+        <v>461.2</v>
+      </c>
+      <c r="M83">
+        <v>58.6386297</v>
+      </c>
+      <c r="N83">
+        <v>402.5613703</v>
+      </c>
+      <c r="O83">
+        <v>80.51227406000002</v>
+      </c>
+      <c r="P83">
+        <v>322.0490962399999</v>
+      </c>
+      <c r="Q83">
+        <v>333.1490962399999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.486630187948895</v>
+      </c>
+      <c r="T83">
+        <v>4.867432322284795</v>
+      </c>
+      <c r="U83">
+        <v>0.0511</v>
+      </c>
+      <c r="V83">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W83">
+        <v>0.04088</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>7.865122400703029</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1266366623553729</v>
+      </c>
+      <c r="C84">
+        <v>433.3017486990254</v>
+      </c>
+      <c r="D84">
+        <v>1349.195748699026</v>
+      </c>
+      <c r="E84">
+        <v>348.9940000000001</v>
+      </c>
+      <c r="F84">
+        <v>1161.694</v>
+      </c>
+      <c r="G84">
+        <v>245.8</v>
+      </c>
+      <c r="H84">
+        <v>604</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>472.3</v>
+      </c>
+      <c r="K84">
+        <v>11.1</v>
+      </c>
+      <c r="L84">
+        <v>461.2</v>
+      </c>
+      <c r="M84">
+        <v>61.56978200000002</v>
+      </c>
+      <c r="N84">
+        <v>399.630218</v>
+      </c>
+      <c r="O84">
+        <v>79.92604360000001</v>
+      </c>
+      <c r="P84">
+        <v>319.7041743999999</v>
+      </c>
+      <c r="Q84">
+        <v>330.8041744</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5103814575298493</v>
+      </c>
+      <c r="T84">
+        <v>5.125583068627134</v>
+      </c>
+      <c r="U84">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V84">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W84">
+        <v>0.0424</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>7.490687558387</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1264695890004557</v>
+      </c>
+      <c r="C85">
+        <v>421.1024913772731</v>
+      </c>
+      <c r="D85">
+        <v>1351.163491377273</v>
+      </c>
+      <c r="E85">
+        <v>363.1610000000001</v>
+      </c>
+      <c r="F85">
+        <v>1175.861</v>
+      </c>
+      <c r="G85">
+        <v>245.8</v>
+      </c>
+      <c r="H85">
+        <v>604</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>472.3</v>
+      </c>
+      <c r="K85">
+        <v>11.1</v>
+      </c>
+      <c r="L85">
+        <v>461.2</v>
+      </c>
+      <c r="M85">
+        <v>62.32063300000002</v>
+      </c>
+      <c r="N85">
+        <v>398.879367</v>
+      </c>
+      <c r="O85">
+        <v>79.77587340000002</v>
+      </c>
+      <c r="P85">
+        <v>319.1034936</v>
+      </c>
+      <c r="Q85">
+        <v>330.2034936</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5369269941203278</v>
+      </c>
+      <c r="T85">
+        <v>5.414104491009748</v>
+      </c>
+      <c r="U85">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V85">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W85">
+        <v>0.0424</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>7.400438310695591</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1263025156455385</v>
+      </c>
+      <c r="C86">
+        <v>408.9089821712521</v>
+      </c>
+      <c r="D86">
+        <v>1353.136982171252</v>
+      </c>
+      <c r="E86">
+        <v>377.328</v>
+      </c>
+      <c r="F86">
+        <v>1190.028</v>
+      </c>
+      <c r="G86">
+        <v>245.8</v>
+      </c>
+      <c r="H86">
+        <v>604</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>472.3</v>
+      </c>
+      <c r="K86">
+        <v>11.1</v>
+      </c>
+      <c r="L86">
+        <v>461.2</v>
+      </c>
+      <c r="M86">
+        <v>63.07148400000001</v>
+      </c>
+      <c r="N86">
+        <v>398.128516</v>
+      </c>
+      <c r="O86">
+        <v>79.62570320000002</v>
+      </c>
+      <c r="P86">
+        <v>318.5028128</v>
+      </c>
+      <c r="Q86">
+        <v>329.6028128</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5667907227846158</v>
+      </c>
+      <c r="T86">
+        <v>5.738691091190186</v>
+      </c>
+      <c r="U86">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V86">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W86">
+        <v>0.0424</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>7.312337854615882</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1261354422906214</v>
+      </c>
+      <c r="C87">
+        <v>396.7212463046603</v>
+      </c>
+      <c r="D87">
+        <v>1355.11624630466</v>
+      </c>
+      <c r="E87">
+        <v>391.4949999999999</v>
+      </c>
+      <c r="F87">
+        <v>1204.195</v>
+      </c>
+      <c r="G87">
+        <v>245.8</v>
+      </c>
+      <c r="H87">
+        <v>604</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>472.3</v>
+      </c>
+      <c r="K87">
+        <v>11.1</v>
+      </c>
+      <c r="L87">
+        <v>461.2</v>
+      </c>
+      <c r="M87">
+        <v>63.822335</v>
+      </c>
+      <c r="N87">
+        <v>397.377665</v>
+      </c>
+      <c r="O87">
+        <v>79.47553300000003</v>
+      </c>
+      <c r="P87">
+        <v>317.9021319999999</v>
+      </c>
+      <c r="Q87">
+        <v>329.002132</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6006362819374758</v>
+      </c>
+      <c r="T87">
+        <v>6.106555904728018</v>
+      </c>
+      <c r="U87">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V87">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W87">
+        <v>0.0424</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>7.226310350443931</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1259683689357042</v>
+      </c>
+      <c r="C88">
+        <v>384.5393091489923</v>
+      </c>
+      <c r="D88">
+        <v>1357.101309148992</v>
+      </c>
+      <c r="E88">
+        <v>405.662</v>
+      </c>
+      <c r="F88">
+        <v>1218.362</v>
+      </c>
+      <c r="G88">
+        <v>245.8</v>
+      </c>
+      <c r="H88">
+        <v>604</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>472.3</v>
+      </c>
+      <c r="K88">
+        <v>11.1</v>
+      </c>
+      <c r="L88">
+        <v>461.2</v>
+      </c>
+      <c r="M88">
+        <v>64.57318600000001</v>
+      </c>
+      <c r="N88">
+        <v>396.626814</v>
+      </c>
+      <c r="O88">
+        <v>79.32536280000002</v>
+      </c>
+      <c r="P88">
+        <v>317.3014512</v>
+      </c>
+      <c r="Q88">
+        <v>328.4014512</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6393169209693157</v>
+      </c>
+      <c r="T88">
+        <v>6.526972834485541</v>
+      </c>
+      <c r="U88">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V88">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W88">
+        <v>0.0424</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>7.142283485903885</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1258012955807871</v>
+      </c>
+      <c r="C89">
+        <v>372.3631962246245</v>
+      </c>
+      <c r="D89">
+        <v>1359.092196224625</v>
+      </c>
+      <c r="E89">
+        <v>419.829</v>
+      </c>
+      <c r="F89">
+        <v>1232.529</v>
+      </c>
+      <c r="G89">
+        <v>245.8</v>
+      </c>
+      <c r="H89">
+        <v>604</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>472.3</v>
+      </c>
+      <c r="K89">
+        <v>11.1</v>
+      </c>
+      <c r="L89">
+        <v>461.2</v>
+      </c>
+      <c r="M89">
+        <v>65.324037</v>
+      </c>
+      <c r="N89">
+        <v>395.875963</v>
+      </c>
+      <c r="O89">
+        <v>79.17519260000002</v>
+      </c>
+      <c r="P89">
+        <v>316.7007704</v>
+      </c>
+      <c r="Q89">
+        <v>327.8007704</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6839484275445158</v>
+      </c>
+      <c r="T89">
+        <v>7.012069291898067</v>
+      </c>
+      <c r="U89">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V89">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W89">
+        <v>0.0424</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>7.060188273422231</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1256342222258699</v>
+      </c>
+      <c r="C90">
+        <v>360.1929332019083</v>
+      </c>
+      <c r="D90">
+        <v>1361.088933201909</v>
+      </c>
+      <c r="E90">
+        <v>433.9960000000001</v>
+      </c>
+      <c r="F90">
+        <v>1246.696</v>
+      </c>
+      <c r="G90">
+        <v>245.8</v>
+      </c>
+      <c r="H90">
+        <v>604</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>472.3</v>
+      </c>
+      <c r="K90">
+        <v>11.1</v>
+      </c>
+      <c r="L90">
+        <v>461.2</v>
+      </c>
+      <c r="M90">
+        <v>66.07488800000002</v>
+      </c>
+      <c r="N90">
+        <v>395.1251119999999</v>
+      </c>
+      <c r="O90">
+        <v>79.02502240000001</v>
+      </c>
+      <c r="P90">
+        <v>316.1000895999999</v>
+      </c>
+      <c r="Q90">
+        <v>327.2000896</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7360185185489159</v>
+      </c>
+      <c r="T90">
+        <v>7.578015158879349</v>
+      </c>
+      <c r="U90">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V90">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W90">
+        <v>0.0424</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>6.97995886122425</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1254671488709527</v>
+      </c>
+      <c r="C91">
+        <v>348.028545902273</v>
+      </c>
+      <c r="D91">
+        <v>1363.091545902273</v>
+      </c>
+      <c r="E91">
+        <v>448.163</v>
+      </c>
+      <c r="F91">
+        <v>1260.863</v>
+      </c>
+      <c r="G91">
+        <v>245.8</v>
+      </c>
+      <c r="H91">
+        <v>604</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>472.3</v>
+      </c>
+      <c r="K91">
+        <v>11.1</v>
+      </c>
+      <c r="L91">
+        <v>461.2</v>
+      </c>
+      <c r="M91">
+        <v>66.82573900000001</v>
+      </c>
+      <c r="N91">
+        <v>394.374261</v>
+      </c>
+      <c r="O91">
+        <v>78.87485220000002</v>
+      </c>
+      <c r="P91">
+        <v>315.4994088</v>
+      </c>
+      <c r="Q91">
+        <v>326.5994088</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.797555898826843</v>
+      </c>
+      <c r="T91">
+        <v>8.24686027440268</v>
+      </c>
+      <c r="U91">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V91">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W91">
+        <v>0.0424</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>6.901532357165551</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1253000755160356</v>
+      </c>
+      <c r="C92">
+        <v>335.8700602993397</v>
+      </c>
+      <c r="D92">
+        <v>1365.10006029934</v>
+      </c>
+      <c r="E92">
+        <v>462.3299999999999</v>
+      </c>
+      <c r="F92">
+        <v>1275.03</v>
+      </c>
+      <c r="G92">
+        <v>245.8</v>
+      </c>
+      <c r="H92">
+        <v>604</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>472.3</v>
+      </c>
+      <c r="K92">
+        <v>11.1</v>
+      </c>
+      <c r="L92">
+        <v>461.2</v>
+      </c>
+      <c r="M92">
+        <v>67.57659000000001</v>
+      </c>
+      <c r="N92">
+        <v>393.62341</v>
+      </c>
+      <c r="O92">
+        <v>78.72468200000002</v>
+      </c>
+      <c r="P92">
+        <v>314.8987279999999</v>
+      </c>
+      <c r="Q92">
+        <v>325.998728</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.871400755160356</v>
+      </c>
+      <c r="T92">
+        <v>9.04947441303068</v>
+      </c>
+      <c r="U92">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V92">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W92">
+        <v>0.0424</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>6.824848664308156</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1251330021611184</v>
+      </c>
+      <c r="C93">
+        <v>323.7175025200429</v>
+      </c>
+      <c r="D93">
+        <v>1367.114502520043</v>
+      </c>
+      <c r="E93">
+        <v>476.4970000000001</v>
+      </c>
+      <c r="F93">
+        <v>1289.197</v>
+      </c>
+      <c r="G93">
+        <v>245.8</v>
+      </c>
+      <c r="H93">
+        <v>604</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>472.3</v>
+      </c>
+      <c r="K93">
+        <v>11.1</v>
+      </c>
+      <c r="L93">
+        <v>461.2</v>
+      </c>
+      <c r="M93">
+        <v>68.32744100000001</v>
+      </c>
+      <c r="N93">
+        <v>392.872559</v>
+      </c>
+      <c r="O93">
+        <v>78.57451180000002</v>
+      </c>
+      <c r="P93">
+        <v>314.2980471999999</v>
+      </c>
+      <c r="Q93">
+        <v>325.3980472</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9616555795679826</v>
+      </c>
+      <c r="T93">
+        <v>10.03044724913157</v>
+      </c>
+      <c r="U93">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V93">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W93">
+        <v>0.0424</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>6.749850327337737</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1249659288062013</v>
+      </c>
+      <c r="C94">
+        <v>311.5708988457666</v>
+      </c>
+      <c r="D94">
+        <v>1369.134898845767</v>
+      </c>
+      <c r="E94">
+        <v>490.664</v>
+      </c>
+      <c r="F94">
+        <v>1303.364</v>
+      </c>
+      <c r="G94">
+        <v>245.8</v>
+      </c>
+      <c r="H94">
+        <v>604</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>472.3</v>
+      </c>
+      <c r="K94">
+        <v>11.1</v>
+      </c>
+      <c r="L94">
+        <v>461.2</v>
+      </c>
+      <c r="M94">
+        <v>69.078292</v>
+      </c>
+      <c r="N94">
+        <v>392.121708</v>
+      </c>
+      <c r="O94">
+        <v>78.42434160000003</v>
+      </c>
+      <c r="P94">
+        <v>313.6973664</v>
+      </c>
+      <c r="Q94">
+        <v>324.7973664</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.074474110077516</v>
+      </c>
+      <c r="T94">
+        <v>11.25666329425768</v>
+      </c>
+      <c r="U94">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V94">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W94">
+        <v>0.0424</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>6.67648238899711</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1247988554512841</v>
+      </c>
+      <c r="C95">
+        <v>299.4302757134826</v>
+      </c>
+      <c r="D95">
+        <v>1371.161275713483</v>
+      </c>
+      <c r="E95">
+        <v>504.8310000000001</v>
+      </c>
+      <c r="F95">
+        <v>1317.531</v>
+      </c>
+      <c r="G95">
+        <v>245.8</v>
+      </c>
+      <c r="H95">
+        <v>604</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>472.3</v>
+      </c>
+      <c r="K95">
+        <v>11.1</v>
+      </c>
+      <c r="L95">
+        <v>461.2</v>
+      </c>
+      <c r="M95">
+        <v>69.82914300000002</v>
+      </c>
+      <c r="N95">
+        <v>391.370857</v>
+      </c>
+      <c r="O95">
+        <v>78.27417140000003</v>
+      </c>
+      <c r="P95">
+        <v>313.0966856</v>
+      </c>
+      <c r="Q95">
+        <v>324.1966856</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.219526506446917</v>
+      </c>
+      <c r="T95">
+        <v>12.83322678084839</v>
+      </c>
+      <c r="U95">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V95">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W95">
+        <v>0.0424</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>6.604692255782087</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1246317820963669</v>
+      </c>
+      <c r="C96">
+        <v>287.2956597169077</v>
+      </c>
+      <c r="D96">
+        <v>1373.193659716908</v>
+      </c>
+      <c r="E96">
+        <v>518.998</v>
+      </c>
+      <c r="F96">
+        <v>1331.698</v>
+      </c>
+      <c r="G96">
+        <v>245.8</v>
+      </c>
+      <c r="H96">
+        <v>604</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>472.3</v>
+      </c>
+      <c r="K96">
+        <v>11.1</v>
+      </c>
+      <c r="L96">
+        <v>461.2</v>
+      </c>
+      <c r="M96">
+        <v>70.57999400000001</v>
+      </c>
+      <c r="N96">
+        <v>390.620006</v>
+      </c>
+      <c r="O96">
+        <v>78.12400120000002</v>
+      </c>
+      <c r="P96">
+        <v>312.4960048</v>
+      </c>
+      <c r="Q96">
+        <v>323.5960048</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.412929701606117</v>
+      </c>
+      <c r="T96">
+        <v>14.93531142963601</v>
+      </c>
+      <c r="U96">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V96">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W96">
+        <v>0.0424</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>6.534429572209937</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1244647087414498</v>
+      </c>
+      <c r="C97">
+        <v>275.1670776076642</v>
+      </c>
+      <c r="D97">
+        <v>1375.232077607664</v>
+      </c>
+      <c r="E97">
+        <v>533.1650000000002</v>
+      </c>
+      <c r="F97">
+        <v>1345.865</v>
+      </c>
+      <c r="G97">
+        <v>245.8</v>
+      </c>
+      <c r="H97">
+        <v>604</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>472.3</v>
+      </c>
+      <c r="K97">
+        <v>11.1</v>
+      </c>
+      <c r="L97">
+        <v>461.2</v>
+      </c>
+      <c r="M97">
+        <v>71.33084500000002</v>
+      </c>
+      <c r="N97">
+        <v>389.869155</v>
+      </c>
+      <c r="O97">
+        <v>77.97383100000002</v>
+      </c>
+      <c r="P97">
+        <v>311.895324</v>
+      </c>
+      <c r="Q97">
+        <v>322.995324</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.683694174828998</v>
+      </c>
+      <c r="T97">
+        <v>17.87822993793868</v>
+      </c>
+      <c r="U97">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V97">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W97">
+        <v>0.0424</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>6.465646103028779</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1242976353865326</v>
+      </c>
+      <c r="C98">
+        <v>263.0445562964551</v>
+      </c>
+      <c r="D98">
+        <v>1377.276556296455</v>
+      </c>
+      <c r="E98">
+        <v>547.3319999999999</v>
+      </c>
+      <c r="F98">
+        <v>1360.032</v>
+      </c>
+      <c r="G98">
+        <v>245.8</v>
+      </c>
+      <c r="H98">
+        <v>604</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>472.3</v>
+      </c>
+      <c r="K98">
+        <v>11.1</v>
+      </c>
+      <c r="L98">
+        <v>461.2</v>
+      </c>
+      <c r="M98">
+        <v>72.08169600000001</v>
+      </c>
+      <c r="N98">
+        <v>389.118304</v>
+      </c>
+      <c r="O98">
+        <v>77.82366080000001</v>
+      </c>
+      <c r="P98">
+        <v>311.2946431999999</v>
+      </c>
+      <c r="Q98">
+        <v>322.3946432</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.089840884663314</v>
+      </c>
+      <c r="T98">
+        <v>22.29260770039263</v>
+      </c>
+      <c r="U98">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V98">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W98">
+        <v>0.0424</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>6.398295622788897</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1241305620316155</v>
+      </c>
+      <c r="C99">
+        <v>250.9281228542484</v>
+      </c>
+      <c r="D99">
+        <v>1379.327122854249</v>
+      </c>
+      <c r="E99">
+        <v>561.499</v>
+      </c>
+      <c r="F99">
+        <v>1374.199</v>
+      </c>
+      <c r="G99">
+        <v>245.8</v>
+      </c>
+      <c r="H99">
+        <v>604</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>472.3</v>
+      </c>
+      <c r="K99">
+        <v>11.1</v>
+      </c>
+      <c r="L99">
+        <v>461.2</v>
+      </c>
+      <c r="M99">
+        <v>72.83254700000001</v>
+      </c>
+      <c r="N99">
+        <v>388.367453</v>
+      </c>
+      <c r="O99">
+        <v>77.67349060000002</v>
+      </c>
+      <c r="P99">
+        <v>310.6939623999999</v>
+      </c>
+      <c r="Q99">
+        <v>321.7939623999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.766752067720513</v>
+      </c>
+      <c r="T99">
+        <v>29.64990397114927</v>
+      </c>
+      <c r="U99">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V99">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W99">
+        <v>0.0424</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>6.332333812244682</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1239634886766983</v>
+      </c>
+      <c r="C100">
+        <v>238.8178045134712</v>
+      </c>
+      <c r="D100">
+        <v>1381.383804513471</v>
+      </c>
+      <c r="E100">
+        <v>575.6659999999999</v>
+      </c>
+      <c r="F100">
+        <v>1388.366</v>
+      </c>
+      <c r="G100">
+        <v>245.8</v>
+      </c>
+      <c r="H100">
+        <v>604</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>472.3</v>
+      </c>
+      <c r="K100">
+        <v>11.1</v>
+      </c>
+      <c r="L100">
+        <v>461.2</v>
+      </c>
+      <c r="M100">
+        <v>73.583398</v>
+      </c>
+      <c r="N100">
+        <v>387.616602</v>
+      </c>
+      <c r="O100">
+        <v>77.52332040000003</v>
+      </c>
+      <c r="P100">
+        <v>310.0932816</v>
+      </c>
+      <c r="Q100">
+        <v>321.1932816</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.120574433834912</v>
+      </c>
+      <c r="T100">
+        <v>44.36449651266256</v>
+      </c>
+      <c r="U100">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V100">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W100">
+        <v>0.0424</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>6.267718161099328</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1253804153217812</v>
+      </c>
+      <c r="C101">
+        <v>207.4004968194877</v>
+      </c>
+      <c r="D101">
+        <v>1364.133496819488</v>
+      </c>
+      <c r="E101">
+        <v>589.8330000000001</v>
+      </c>
+      <c r="F101">
+        <v>1402.533</v>
+      </c>
+      <c r="G101">
+        <v>245.8</v>
+      </c>
+      <c r="H101">
+        <v>604</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>472.3</v>
+      </c>
+      <c r="K101">
+        <v>11.1</v>
+      </c>
+      <c r="L101">
+        <v>461.2</v>
+      </c>
+      <c r="M101">
+        <v>77.13931500000001</v>
+      </c>
+      <c r="N101">
+        <v>384.060685</v>
+      </c>
+      <c r="O101">
+        <v>76.81213700000002</v>
+      </c>
+      <c r="P101">
+        <v>307.248548</v>
+      </c>
+      <c r="Q101">
+        <v>318.348548</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.182041532178108</v>
+      </c>
+      <c r="T101">
+        <v>88.50827413720242</v>
+      </c>
+      <c r="U101">
+        <v>0.055</v>
+      </c>
+      <c r="V101">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="W101">
+        <v>0.044</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>5.978793044765823</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_precious_metals.xlsx
@@ -1149,7 +1149,7 @@
         <v>3.6738178522344</v>
       </c>
       <c r="Z2">
-        <v>1.12723667025745</v>
+        <v>1.12723667025744</v>
       </c>
       <c r="AA2">
         <v>13.7</v>
@@ -1227,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1364,22 +1364,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1127191100881548</v>
+        <v>0.1125296718679785</v>
       </c>
       <c r="C2">
-        <v>17.94297202213695</v>
+        <v>17.81382214629813</v>
       </c>
       <c r="D2">
-        <v>17.91197202213695</v>
+        <v>17.96282214629813</v>
       </c>
       <c r="E2">
-        <v>-13.7</v>
+        <v>-13.52</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G2">
         <v>0.031</v>
@@ -1400,28 +1400,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.009054</v>
       </c>
       <c r="N2">
-        <v>0.4723333333333333</v>
+        <v>0.4632793333333333</v>
       </c>
       <c r="O2">
-        <v>0.09446666666666667</v>
+        <v>0.09265586666666667</v>
       </c>
       <c r="P2">
-        <v>0.3778666666666667</v>
+        <v>0.3706234666666667</v>
       </c>
       <c r="Q2">
-        <v>0.3838666666666667</v>
+        <v>0.3766234666666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1127191100881548</v>
+        <v>0.1132598705737157</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.043582742965612</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>52.16847065753627</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1446,22 +1446,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1125296718679785</v>
+        <v>0.1123402336478022</v>
       </c>
       <c r="C3">
-        <v>17.81382214629813</v>
+        <v>17.68496180827692</v>
       </c>
       <c r="D3">
-        <v>17.96282214629813</v>
+        <v>18.01396180827692</v>
       </c>
       <c r="E3">
-        <v>-13.52</v>
+        <v>-13.34</v>
       </c>
       <c r="F3">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="G3">
         <v>0.031</v>
@@ -1482,28 +1482,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M3">
-        <v>0.009054</v>
+        <v>0.018108</v>
       </c>
       <c r="N3">
-        <v>0.4632793333333333</v>
+        <v>0.4542253333333333</v>
       </c>
       <c r="O3">
-        <v>0.09265586666666667</v>
+        <v>0.09084506666666667</v>
       </c>
       <c r="P3">
-        <v>0.3706234666666667</v>
+        <v>0.3633802666666667</v>
       </c>
       <c r="Q3">
-        <v>0.3766234666666667</v>
+        <v>0.3693802666666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1132598705737157</v>
+        <v>0.1138116669875533</v>
       </c>
       <c r="T3">
-        <v>1.043582742965612</v>
+        <v>1.052118857995391</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>52.16847065753627</v>
+        <v>26.08423532876813</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1123402336478022</v>
+        <v>0.1121507954276259</v>
       </c>
       <c r="C4">
-        <v>17.68496180827692</v>
+        <v>17.55639348805243</v>
       </c>
       <c r="D4">
-        <v>18.01396180827692</v>
+        <v>18.06539348805243</v>
       </c>
       <c r="E4">
-        <v>-13.34</v>
+        <v>-13.16</v>
       </c>
       <c r="F4">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="G4">
         <v>0.031</v>
@@ -1564,28 +1564,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M4">
-        <v>0.018108</v>
+        <v>0.027162</v>
       </c>
       <c r="N4">
-        <v>0.4542253333333333</v>
+        <v>0.4451713333333333</v>
       </c>
       <c r="O4">
-        <v>0.09084506666666667</v>
+        <v>0.08903426666666667</v>
       </c>
       <c r="P4">
-        <v>0.3633802666666667</v>
+        <v>0.3561370666666667</v>
       </c>
       <c r="Q4">
-        <v>0.3693802666666667</v>
+        <v>0.3621370666666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1138116669875533</v>
+        <v>0.114374840647037</v>
       </c>
       <c r="T4">
-        <v>1.052118857995391</v>
+        <v>1.060830975396918</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.08423532876813</v>
+        <v>17.38949021917875</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1121507954276259</v>
+        <v>0.1119613572074496</v>
       </c>
       <c r="C5">
-        <v>17.55639348805243</v>
+        <v>17.42811969400722</v>
       </c>
       <c r="D5">
-        <v>18.06539348805243</v>
+        <v>18.11711969400722</v>
       </c>
       <c r="E5">
-        <v>-13.16</v>
+        <v>-12.98</v>
       </c>
       <c r="F5">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="G5">
         <v>0.031</v>
@@ -1646,28 +1646,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M5">
-        <v>0.027162</v>
+        <v>0.036216</v>
       </c>
       <c r="N5">
-        <v>0.4451713333333333</v>
+        <v>0.4361173333333334</v>
       </c>
       <c r="O5">
-        <v>0.08903426666666667</v>
+        <v>0.08722346666666668</v>
       </c>
       <c r="P5">
-        <v>0.3561370666666667</v>
+        <v>0.3488938666666667</v>
       </c>
       <c r="Q5">
-        <v>0.3621370666666667</v>
+        <v>0.3548938666666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.114374840647037</v>
+        <v>0.1149497470910933</v>
       </c>
       <c r="T5">
-        <v>1.060830975396918</v>
+        <v>1.06972459524431</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.38949021917875</v>
+        <v>13.04211766438407</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1119613572074496</v>
+        <v>0.1118319189872733</v>
       </c>
       <c r="C6">
-        <v>17.42811969400722</v>
+        <v>17.28363354494295</v>
       </c>
       <c r="D6">
-        <v>18.11711969400722</v>
+        <v>18.15263354494295</v>
       </c>
       <c r="E6">
-        <v>-12.98</v>
+        <v>-12.8</v>
       </c>
       <c r="F6">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="G6">
         <v>0.031</v>
@@ -1728,45 +1728,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M6">
-        <v>0.036216</v>
+        <v>0.04662</v>
       </c>
       <c r="N6">
-        <v>0.4361173333333334</v>
+        <v>0.4257133333333333</v>
       </c>
       <c r="O6">
-        <v>0.08722346666666668</v>
+        <v>0.08514266666666667</v>
       </c>
       <c r="P6">
-        <v>0.3488938666666667</v>
+        <v>0.3405706666666667</v>
       </c>
       <c r="Q6">
-        <v>0.3548938666666667</v>
+        <v>0.3465706666666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1149497470910933</v>
+        <v>0.1155367568287087</v>
       </c>
       <c r="T6">
-        <v>1.06972459524431</v>
+        <v>1.078805449193752</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.04211766438407</v>
+        <v>10.13156013156013</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1118319189872733</v>
+        <v>0.111736080767097</v>
       </c>
       <c r="C7">
-        <v>17.28363354494295</v>
+        <v>17.13001843270425</v>
       </c>
       <c r="D7">
-        <v>18.15263354494295</v>
+        <v>18.17901843270425</v>
       </c>
       <c r="E7">
-        <v>-12.8</v>
+        <v>-12.62</v>
       </c>
       <c r="F7">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="G7">
         <v>0.031</v>
@@ -1810,45 +1810,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M7">
-        <v>0.04662</v>
+        <v>0.05778</v>
       </c>
       <c r="N7">
-        <v>0.4257133333333333</v>
+        <v>0.4145533333333333</v>
       </c>
       <c r="O7">
-        <v>0.08514266666666667</v>
+        <v>0.08291066666666667</v>
       </c>
       <c r="P7">
-        <v>0.3405706666666667</v>
+        <v>0.3316426666666666</v>
       </c>
       <c r="Q7">
-        <v>0.3465706666666667</v>
+        <v>0.3376426666666666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1155367568287087</v>
+        <v>0.1161362561352096</v>
       </c>
       <c r="T7">
-        <v>1.078805449193752</v>
+        <v>1.088079512801694</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.13156013156013</v>
+        <v>8.174685589015805</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.111736080767097</v>
+        <v>0.1116170425469207</v>
       </c>
       <c r="C8">
-        <v>17.13001843270425</v>
+        <v>16.9828974244523</v>
       </c>
       <c r="D8">
-        <v>18.17901843270425</v>
+        <v>18.2118974244523</v>
       </c>
       <c r="E8">
-        <v>-12.62</v>
+        <v>-12.44</v>
       </c>
       <c r="F8">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="G8">
         <v>0.031</v>
@@ -1892,45 +1892,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M8">
-        <v>0.05778</v>
+        <v>0.06841799999999999</v>
       </c>
       <c r="N8">
-        <v>0.4145533333333333</v>
+        <v>0.4039153333333333</v>
       </c>
       <c r="O8">
-        <v>0.08291066666666667</v>
+        <v>0.08078306666666668</v>
       </c>
       <c r="P8">
-        <v>0.3316426666666666</v>
+        <v>0.3231322666666667</v>
       </c>
       <c r="Q8">
-        <v>0.3376426666666666</v>
+        <v>0.3291322666666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1161362561352096</v>
+        <v>0.1167486478999147</v>
       </c>
       <c r="T8">
-        <v>1.088079512801694</v>
+        <v>1.097553018637762</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.174685589015805</v>
+        <v>6.903641341947051</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1116170425469207</v>
+        <v>0.1115236043267444</v>
       </c>
       <c r="C9">
-        <v>16.98289742445229</v>
+        <v>16.82878899413728</v>
       </c>
       <c r="D9">
-        <v>18.2118974244523</v>
+        <v>18.23778899413728</v>
       </c>
       <c r="E9">
-        <v>-12.44</v>
+        <v>-12.26</v>
       </c>
       <c r="F9">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="G9">
         <v>0.031</v>
@@ -1974,45 +1974,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M9">
-        <v>0.06841800000000002</v>
+        <v>0.07963199999999999</v>
       </c>
       <c r="N9">
-        <v>0.4039153333333333</v>
+        <v>0.3927013333333333</v>
       </c>
       <c r="O9">
-        <v>0.08078306666666667</v>
+        <v>0.07854026666666668</v>
       </c>
       <c r="P9">
-        <v>0.3231322666666666</v>
+        <v>0.3141610666666667</v>
       </c>
       <c r="Q9">
-        <v>0.3291322666666666</v>
+        <v>0.3201610666666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1167486478999147</v>
+        <v>0.11737435252907</v>
       </c>
       <c r="T9">
-        <v>1.097553018637762</v>
+        <v>1.107232470252876</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.903641341947049</v>
+        <v>5.931451342843748</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1115236043267444</v>
+        <v>0.111374166106568</v>
       </c>
       <c r="C10">
-        <v>16.82878899413728</v>
+        <v>16.69035143997618</v>
       </c>
       <c r="D10">
-        <v>18.23778899413728</v>
+        <v>18.27935143997618</v>
       </c>
       <c r="E10">
-        <v>-12.26</v>
+        <v>-12.08</v>
       </c>
       <c r="F10">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="G10">
         <v>0.031</v>
@@ -2056,28 +2056,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M10">
-        <v>0.07963199999999999</v>
+        <v>0.089586</v>
       </c>
       <c r="N10">
-        <v>0.3927013333333333</v>
+        <v>0.3827473333333333</v>
       </c>
       <c r="O10">
-        <v>0.07854026666666668</v>
+        <v>0.07654946666666668</v>
       </c>
       <c r="P10">
-        <v>0.3141610666666667</v>
+        <v>0.3061978666666667</v>
       </c>
       <c r="Q10">
-        <v>0.3201610666666667</v>
+        <v>0.3121978666666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.11737435252907</v>
+        <v>0.1180138089083165</v>
       </c>
       <c r="T10">
-        <v>1.107232470252876</v>
+        <v>1.117124657068322</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.931451342843748</v>
+        <v>5.272401193638887</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.111374166106568</v>
+        <v>0.1112247278863917</v>
       </c>
       <c r="C11">
-        <v>16.69035143997618</v>
+        <v>16.55210375341202</v>
       </c>
       <c r="D11">
-        <v>18.27935143997618</v>
+        <v>18.32110375341203</v>
       </c>
       <c r="E11">
-        <v>-12.08</v>
+        <v>-11.9</v>
       </c>
       <c r="F11">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="G11">
         <v>0.031</v>
@@ -2138,28 +2138,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M11">
-        <v>0.089586</v>
+        <v>0.09953999999999999</v>
       </c>
       <c r="N11">
-        <v>0.3827473333333333</v>
+        <v>0.3727933333333333</v>
       </c>
       <c r="O11">
-        <v>0.07654946666666668</v>
+        <v>0.07455866666666666</v>
       </c>
       <c r="P11">
-        <v>0.3061978666666667</v>
+        <v>0.2982346666666666</v>
       </c>
       <c r="Q11">
-        <v>0.3121978666666667</v>
+        <v>0.3042346666666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1180138089083165</v>
+        <v>0.1186674754293242</v>
       </c>
       <c r="T11">
-        <v>1.117124657068322</v>
+        <v>1.127236670257445</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.272401193638887</v>
+        <v>4.745161074274998</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1112247278863917</v>
+        <v>0.1112952896662154</v>
       </c>
       <c r="C12">
-        <v>16.55210375341202</v>
+        <v>16.35236539213804</v>
       </c>
       <c r="D12">
-        <v>18.32110375341203</v>
+        <v>18.30136539213805</v>
       </c>
       <c r="E12">
-        <v>-11.9</v>
+        <v>-11.72</v>
       </c>
       <c r="F12">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="G12">
         <v>0.031</v>
@@ -2220,45 +2220,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M12">
-        <v>0.09954</v>
+        <v>0.114444</v>
       </c>
       <c r="N12">
-        <v>0.3727933333333333</v>
+        <v>0.3578893333333333</v>
       </c>
       <c r="O12">
-        <v>0.07455866666666666</v>
+        <v>0.07157786666666667</v>
       </c>
       <c r="P12">
-        <v>0.2982346666666666</v>
+        <v>0.2863114666666667</v>
       </c>
       <c r="Q12">
-        <v>0.3042346666666667</v>
+        <v>0.2923114666666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1186674754293242</v>
+        <v>0.1193358310856353</v>
       </c>
       <c r="T12">
-        <v>1.127236670257445</v>
+        <v>1.137575919698008</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.745161074274998</v>
+        <v>4.127200493982501</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1112952896662154</v>
+        <v>0.1115018514460391</v>
       </c>
       <c r="C13">
-        <v>16.35236539213804</v>
+        <v>16.11482724784833</v>
       </c>
       <c r="D13">
-        <v>18.30136539213805</v>
+        <v>18.24382724784833</v>
       </c>
       <c r="E13">
-        <v>-11.72</v>
+        <v>-11.54</v>
       </c>
       <c r="F13">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="G13">
         <v>0.031</v>
@@ -2302,45 +2302,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M13">
-        <v>0.114444</v>
+        <v>0.132408</v>
       </c>
       <c r="N13">
-        <v>0.3578893333333333</v>
+        <v>0.3399253333333333</v>
       </c>
       <c r="O13">
-        <v>0.07157786666666667</v>
+        <v>0.06798506666666666</v>
       </c>
       <c r="P13">
-        <v>0.2863114666666667</v>
+        <v>0.2719402666666667</v>
       </c>
       <c r="Q13">
-        <v>0.2923114666666667</v>
+        <v>0.2779402666666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1193358310856353</v>
+        <v>0.1200193766432263</v>
       </c>
       <c r="T13">
-        <v>1.137575919698008</v>
+        <v>1.148150152080403</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.127200493982501</v>
+        <v>3.567256761927779</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1115018514460391</v>
+        <v>0.1116916132258628</v>
       </c>
       <c r="C14">
-        <v>16.11482724784833</v>
+        <v>15.88228670498015</v>
       </c>
       <c r="D14">
-        <v>18.24382724784833</v>
+        <v>18.19128670498015</v>
       </c>
       <c r="E14">
-        <v>-11.54</v>
+        <v>-11.36</v>
       </c>
       <c r="F14">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="G14">
         <v>0.031</v>
@@ -2384,45 +2384,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M14">
-        <v>0.132408</v>
+        <v>0.149994</v>
       </c>
       <c r="N14">
-        <v>0.3399253333333333</v>
+        <v>0.3223393333333333</v>
       </c>
       <c r="O14">
-        <v>0.06798506666666666</v>
+        <v>0.06446786666666666</v>
       </c>
       <c r="P14">
-        <v>0.2719402666666667</v>
+        <v>0.2578714666666667</v>
       </c>
       <c r="Q14">
-        <v>0.2779402666666667</v>
+        <v>0.2638714666666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1200193766432263</v>
+        <v>0.1207186358917963</v>
       </c>
       <c r="T14">
-        <v>1.148150152080403</v>
+        <v>1.158967470264692</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.567256761927779</v>
+        <v>3.149014849482868</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1116916132258628</v>
+        <v>0.1124861750056865</v>
       </c>
       <c r="C15">
-        <v>15.88228670498015</v>
+        <v>15.48553861378494</v>
       </c>
       <c r="D15">
-        <v>18.19128670498015</v>
+        <v>17.97453861378494</v>
       </c>
       <c r="E15">
-        <v>-11.36</v>
+        <v>-11.18</v>
       </c>
       <c r="F15">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="G15">
         <v>0.031</v>
@@ -2466,45 +2466,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M15">
-        <v>0.149994</v>
+        <v>0.181188</v>
       </c>
       <c r="N15">
-        <v>0.3223393333333333</v>
+        <v>0.2911453333333333</v>
       </c>
       <c r="O15">
-        <v>0.06446786666666666</v>
+        <v>0.05822906666666666</v>
       </c>
       <c r="P15">
-        <v>0.2578714666666667</v>
+        <v>0.2329162666666666</v>
       </c>
       <c r="Q15">
-        <v>0.2638714666666667</v>
+        <v>0.2389162666666666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1207186358917963</v>
+        <v>0.1214341569833564</v>
       </c>
       <c r="T15">
-        <v>1.158967470264692</v>
+        <v>1.17003635398815</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.149014849482868</v>
+        <v>2.606868740387516</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1124861750056865</v>
+        <v>0.1129375367855102</v>
       </c>
       <c r="C16">
-        <v>15.48553861378494</v>
+        <v>15.1846968294617</v>
       </c>
       <c r="D16">
-        <v>17.97453861378494</v>
+        <v>17.8536968294617</v>
       </c>
       <c r="E16">
-        <v>-11.18</v>
+        <v>-11</v>
       </c>
       <c r="F16">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="G16">
         <v>0.031</v>
@@ -2548,45 +2548,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M16">
-        <v>0.181188</v>
+        <v>0.20466</v>
       </c>
       <c r="N16">
-        <v>0.2911453333333333</v>
+        <v>0.2676733333333333</v>
       </c>
       <c r="O16">
-        <v>0.05822906666666666</v>
+        <v>0.05353466666666667</v>
       </c>
       <c r="P16">
-        <v>0.2329162666666666</v>
+        <v>0.2141386666666666</v>
       </c>
       <c r="Q16">
-        <v>0.2389162666666666</v>
+        <v>0.2201386666666666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1214341569833564</v>
+        <v>0.1221665138653061</v>
       </c>
       <c r="T16">
-        <v>1.17003635398815</v>
+        <v>1.181365682034513</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.606868740387516</v>
+        <v>2.307892765236653</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1129375367855102</v>
+        <v>0.1129520985653339</v>
       </c>
       <c r="C17">
-        <v>15.18469682946171</v>
+        <v>15.00082529591586</v>
       </c>
       <c r="D17">
-        <v>17.85369682946171</v>
+        <v>17.84982529591586</v>
       </c>
       <c r="E17">
-        <v>-11</v>
+        <v>-10.82</v>
       </c>
       <c r="F17">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="G17">
         <v>0.031</v>
@@ -2630,28 +2630,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M17">
-        <v>0.20466</v>
+        <v>0.218304</v>
       </c>
       <c r="N17">
-        <v>0.2676733333333333</v>
+        <v>0.2540293333333333</v>
       </c>
       <c r="O17">
-        <v>0.05353466666666667</v>
+        <v>0.05080586666666667</v>
       </c>
       <c r="P17">
-        <v>0.2141386666666666</v>
+        <v>0.2032234666666667</v>
       </c>
       <c r="Q17">
-        <v>0.2201386666666666</v>
+        <v>0.2092234666666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1221665138653061</v>
+        <v>0.1229163078158737</v>
       </c>
       <c r="T17">
-        <v>1.181365682034513</v>
+        <v>1.192964755986742</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.307892765236653</v>
+        <v>2.163649467409362</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1129520985653339</v>
+        <v>0.1129666603451576</v>
       </c>
       <c r="C18">
-        <v>15.00082529591586</v>
+        <v>14.81695544107249</v>
       </c>
       <c r="D18">
-        <v>17.84982529591586</v>
+        <v>17.84595544107249</v>
       </c>
       <c r="E18">
-        <v>-10.82</v>
+        <v>-10.64</v>
       </c>
       <c r="F18">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="G18">
         <v>0.031</v>
@@ -2712,28 +2712,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M18">
-        <v>0.218304</v>
+        <v>0.231948</v>
       </c>
       <c r="N18">
-        <v>0.2540293333333333</v>
+        <v>0.2403853333333333</v>
       </c>
       <c r="O18">
-        <v>0.05080586666666667</v>
+        <v>0.04807706666666667</v>
       </c>
       <c r="P18">
-        <v>0.2032234666666667</v>
+        <v>0.1923082666666666</v>
       </c>
       <c r="Q18">
-        <v>0.2092234666666667</v>
+        <v>0.1983082666666666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1229163078158737</v>
+        <v>0.1236841690905513</v>
       </c>
       <c r="T18">
-        <v>1.192964755986742</v>
+        <v>1.204843325696856</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.163649467409362</v>
+        <v>2.036375969326458</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1129666603451576</v>
+        <v>0.1150260221249813</v>
       </c>
       <c r="C19">
-        <v>14.81695544107249</v>
+        <v>14.1060672370178</v>
       </c>
       <c r="D19">
-        <v>17.84595544107249</v>
+        <v>17.3150672370178</v>
       </c>
       <c r="E19">
-        <v>-10.64</v>
+        <v>-10.46</v>
       </c>
       <c r="F19">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="G19">
         <v>0.031</v>
@@ -2794,45 +2794,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M19">
-        <v>0.231948</v>
+        <v>0.2916</v>
       </c>
       <c r="N19">
-        <v>0.2403853333333333</v>
+        <v>0.1807333333333333</v>
       </c>
       <c r="O19">
-        <v>0.04807706666666667</v>
+        <v>0.03614666666666666</v>
       </c>
       <c r="P19">
-        <v>0.1923082666666666</v>
+        <v>0.1445866666666666</v>
       </c>
       <c r="Q19">
-        <v>0.1983082666666666</v>
+        <v>0.1505866666666666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1236841690905513</v>
+        <v>0.1244707586890015</v>
       </c>
       <c r="T19">
-        <v>1.204843325696856</v>
+        <v>1.217011616619412</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.036375969326458</v>
+        <v>1.619798811156836</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1150260221249813</v>
+        <v>0.115154183904805</v>
       </c>
       <c r="C20">
-        <v>14.10606723701779</v>
+        <v>13.89407017916315</v>
       </c>
       <c r="D20">
-        <v>17.31506723701779</v>
+        <v>17.28307017916315</v>
       </c>
       <c r="E20">
-        <v>-10.46</v>
+        <v>-10.28</v>
       </c>
       <c r="F20">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="G20">
         <v>0.031</v>
@@ -2876,28 +2876,28 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M20">
-        <v>0.2916</v>
+        <v>0.3078</v>
       </c>
       <c r="N20">
-        <v>0.1807333333333334</v>
+        <v>0.1645333333333334</v>
       </c>
       <c r="O20">
-        <v>0.03614666666666667</v>
+        <v>0.03290666666666667</v>
       </c>
       <c r="P20">
-        <v>0.1445866666666667</v>
+        <v>0.1316266666666667</v>
       </c>
       <c r="Q20">
-        <v>0.1505866666666667</v>
+        <v>0.1376266666666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1244707586890015</v>
+        <v>0.1252767702528456</v>
       </c>
       <c r="T20">
-        <v>1.217011616619412</v>
+        <v>1.229480359169685</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.619798811156836</v>
+        <v>1.534546242148581</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.115154183904805</v>
+        <v>0.1252785818059136</v>
       </c>
       <c r="C21">
-        <v>13.89407017916315</v>
+        <v>11.51246220540824</v>
       </c>
       <c r="D21">
-        <v>17.28307017916315</v>
+        <v>15.08146220540823</v>
       </c>
       <c r="E21">
-        <v>-10.28</v>
+        <v>-10.1</v>
       </c>
       <c r="F21">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="G21">
         <v>0.031</v>
@@ -2958,45 +2958,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M21">
-        <v>0.3078</v>
+        <v>0.5284800000000001</v>
       </c>
       <c r="N21">
-        <v>0.1645333333333334</v>
+        <v>-0.05614666666666673</v>
       </c>
       <c r="O21">
-        <v>0.03290666666666667</v>
+        <v>-0.01122933333333335</v>
       </c>
       <c r="P21">
-        <v>0.1316266666666667</v>
+        <v>-0.04491733333333339</v>
       </c>
       <c r="Q21">
-        <v>0.1376266666666667</v>
+        <v>-0.03891733333333339</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1252767702528456</v>
+        <v>0.1264584124425771</v>
       </c>
       <c r="T21">
-        <v>1.229480359169685</v>
+        <v>1.247759988037582</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2</v>
+        <v>0.178751639923302</v>
       </c>
       <c r="W21">
-        <v>0.07199999999999999</v>
+        <v>0.1205592592592593</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.534546242148581</v>
+        <v>0.8937581996165102</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1252785818059136</v>
+        <v>0.1262885818059136</v>
       </c>
       <c r="C22">
-        <v>11.51246220540824</v>
+        <v>11.14321453218928</v>
       </c>
       <c r="D22">
-        <v>15.08146220540823</v>
+        <v>14.89221453218928</v>
       </c>
       <c r="E22">
-        <v>-10.1</v>
+        <v>-9.919999999999998</v>
       </c>
       <c r="F22">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="G22">
         <v>0.031</v>
@@ -3040,37 +3040,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M22">
-        <v>0.5284800000000001</v>
+        <v>0.5549040000000001</v>
       </c>
       <c r="N22">
-        <v>-0.05614666666666673</v>
+        <v>-0.08257066666666674</v>
       </c>
       <c r="O22">
-        <v>-0.01122933333333335</v>
+        <v>-0.01651413333333335</v>
       </c>
       <c r="P22">
-        <v>-0.04491733333333339</v>
+        <v>-0.06605653333333339</v>
       </c>
       <c r="Q22">
-        <v>-0.03891733333333339</v>
+        <v>-0.06005653333333339</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1264584124425771</v>
+        <v>0.1274794050051414</v>
       </c>
       <c r="T22">
-        <v>1.247759988037582</v>
+        <v>1.263554418265906</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.178751639923302</v>
+        <v>0.1702396570698115</v>
       </c>
       <c r="W22">
-        <v>0.1205592592592593</v>
+        <v>0.1218088183421517</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8937581996165102</v>
+        <v>0.8511982853490573</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1262885818059136</v>
+        <v>0.1272985818059136</v>
       </c>
       <c r="C23">
-        <v>11.14321453218928</v>
+        <v>10.77865749641986</v>
       </c>
       <c r="D23">
-        <v>14.89221453218928</v>
+        <v>14.70765749641986</v>
       </c>
       <c r="E23">
-        <v>-9.92</v>
+        <v>-9.739999999999998</v>
       </c>
       <c r="F23">
-        <v>3.78</v>
+        <v>3.96</v>
       </c>
       <c r="G23">
         <v>0.031</v>
@@ -3122,37 +3122,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M23">
-        <v>0.5549040000000001</v>
+        <v>0.5813280000000001</v>
       </c>
       <c r="N23">
-        <v>-0.08257066666666674</v>
+        <v>-0.1089946666666667</v>
       </c>
       <c r="O23">
-        <v>-0.01651413333333335</v>
+        <v>-0.02179893333333335</v>
       </c>
       <c r="P23">
-        <v>-0.06605653333333339</v>
+        <v>-0.08719573333333339</v>
       </c>
       <c r="Q23">
-        <v>-0.06005653333333339</v>
+        <v>-0.08119573333333338</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1274794050051414</v>
+        <v>0.1285265768641817</v>
       </c>
       <c r="T23">
-        <v>1.263554418265906</v>
+        <v>1.2797538338847</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1702396570698115</v>
+        <v>0.1625014908393655</v>
       </c>
       <c r="W23">
-        <v>0.1218088183421517</v>
+        <v>0.1229447811447812</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8511982853490573</v>
+        <v>0.8125074541968274</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1272985818059136</v>
+        <v>0.1413719509654804</v>
       </c>
       <c r="C24">
-        <v>10.77865749641986</v>
+        <v>8.432893469123306</v>
       </c>
       <c r="D24">
-        <v>14.70765749641986</v>
+        <v>12.54189346912331</v>
       </c>
       <c r="E24">
-        <v>-9.739999999999998</v>
+        <v>-9.559999999999999</v>
       </c>
       <c r="F24">
-        <v>3.96</v>
+        <v>4.140000000000001</v>
       </c>
       <c r="G24">
         <v>0.031</v>
@@ -3204,45 +3204,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M24">
-        <v>0.5813280000000001</v>
+        <v>0.8313120000000002</v>
       </c>
       <c r="N24">
-        <v>-0.1089946666666667</v>
+        <v>-0.3589786666666668</v>
       </c>
       <c r="O24">
-        <v>-0.02179893333333335</v>
+        <v>-0.07179573333333338</v>
       </c>
       <c r="P24">
-        <v>-0.08719573333333339</v>
+        <v>-0.2871829333333334</v>
       </c>
       <c r="Q24">
-        <v>-0.08119573333333338</v>
+        <v>-0.2811829333333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1285265768641817</v>
+        <v>0.1304364923553618</v>
       </c>
       <c r="T24">
-        <v>1.2797538338847</v>
+        <v>1.309299619107342</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1625014908393655</v>
+        <v>0.1136356345952743</v>
       </c>
       <c r="W24">
-        <v>0.1229447811447812</v>
+        <v>0.1779819645732689</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8125074541968274</v>
+        <v>0.5681781729763713</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1413719509654804</v>
+        <v>0.1429219509654804</v>
       </c>
       <c r="C25">
-        <v>8.432893469123306</v>
+        <v>8.052733415871794</v>
       </c>
       <c r="D25">
-        <v>12.54189346912331</v>
+        <v>12.34173341587179</v>
       </c>
       <c r="E25">
-        <v>-9.559999999999999</v>
+        <v>-9.379999999999999</v>
       </c>
       <c r="F25">
-        <v>4.140000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="G25">
         <v>0.031</v>
@@ -3286,37 +3286,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M25">
-        <v>0.8313120000000002</v>
+        <v>0.8674560000000001</v>
       </c>
       <c r="N25">
-        <v>-0.3589786666666668</v>
+        <v>-0.3951226666666668</v>
       </c>
       <c r="O25">
-        <v>-0.07179573333333338</v>
+        <v>-0.07902453333333337</v>
       </c>
       <c r="P25">
-        <v>-0.2871829333333334</v>
+        <v>-0.3160981333333334</v>
       </c>
       <c r="Q25">
-        <v>-0.2811829333333334</v>
+        <v>-0.3100981333333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1304364923553618</v>
+        <v>0.1315501304126692</v>
       </c>
       <c r="T25">
-        <v>1.309299619107342</v>
+        <v>1.326527245674544</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1136356345952743</v>
+        <v>0.1089008164871379</v>
       </c>
       <c r="W25">
-        <v>0.1779819645732689</v>
+        <v>0.1789327160493827</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5681781729763713</v>
+        <v>0.5445040824356893</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1429219509654804</v>
+        <v>0.1444719509654804</v>
       </c>
       <c r="C26">
-        <v>8.052733415871794</v>
+        <v>7.678861838311789</v>
       </c>
       <c r="D26">
-        <v>12.34173341587179</v>
+        <v>12.14786183831179</v>
       </c>
       <c r="E26">
-        <v>-9.379999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F26">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="G26">
         <v>0.031</v>
@@ -3368,37 +3368,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M26">
-        <v>0.8674560000000001</v>
+        <v>0.9036000000000001</v>
       </c>
       <c r="N26">
-        <v>-0.3951226666666668</v>
+        <v>-0.4312666666666667</v>
       </c>
       <c r="O26">
-        <v>-0.07902453333333337</v>
+        <v>-0.08625333333333335</v>
       </c>
       <c r="P26">
-        <v>-0.3160981333333334</v>
+        <v>-0.3450133333333334</v>
       </c>
       <c r="Q26">
-        <v>-0.3100981333333334</v>
+        <v>-0.3390133333333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1315501304126692</v>
+        <v>0.1326934654848381</v>
       </c>
       <c r="T26">
-        <v>1.326527245674544</v>
+        <v>1.344214275616871</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1089008164871379</v>
+        <v>0.1045447838276524</v>
       </c>
       <c r="W26">
-        <v>0.1789327160493827</v>
+        <v>0.1798074074074074</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5445040824356893</v>
+        <v>0.5227239191382618</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1444719509654804</v>
+        <v>0.1460219509654804</v>
       </c>
       <c r="C27">
-        <v>7.678861838311789</v>
+        <v>7.310986969902288</v>
       </c>
       <c r="D27">
-        <v>12.14786183831179</v>
+        <v>11.95998696990229</v>
       </c>
       <c r="E27">
-        <v>-9.199999999999999</v>
+        <v>-9.02</v>
       </c>
       <c r="F27">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="G27">
         <v>0.031</v>
@@ -3450,37 +3450,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M27">
-        <v>0.9036000000000001</v>
+        <v>0.939744</v>
       </c>
       <c r="N27">
-        <v>-0.4312666666666667</v>
+        <v>-0.4674106666666667</v>
       </c>
       <c r="O27">
-        <v>-0.08625333333333335</v>
+        <v>-0.09348213333333334</v>
       </c>
       <c r="P27">
-        <v>-0.3450133333333334</v>
+        <v>-0.3739285333333334</v>
       </c>
       <c r="Q27">
-        <v>-0.3390133333333334</v>
+        <v>-0.3679285333333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1326934654848381</v>
+        <v>0.1338677015049035</v>
       </c>
       <c r="T27">
-        <v>1.344214275616871</v>
+        <v>1.362379333395477</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1045447838276524</v>
+        <v>0.1005238306035119</v>
       </c>
       <c r="W27">
-        <v>0.1798074074074074</v>
+        <v>0.1806148148148148</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5227239191382618</v>
+        <v>0.5026191530175594</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1460219509654804</v>
+        <v>0.1572815581924033</v>
       </c>
       <c r="C28">
-        <v>7.310986969902288</v>
+        <v>5.923031520555221</v>
       </c>
       <c r="D28">
-        <v>11.95998696990229</v>
+        <v>10.75203152055522</v>
       </c>
       <c r="E28">
-        <v>-9.02</v>
+        <v>-8.84</v>
       </c>
       <c r="F28">
-        <v>4.68</v>
+        <v>4.86</v>
       </c>
       <c r="G28">
         <v>0.031</v>
@@ -3532,45 +3532,45 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M28">
-        <v>0.939744</v>
+        <v>1.145988</v>
       </c>
       <c r="N28">
-        <v>-0.4674106666666667</v>
+        <v>-0.673654666666667</v>
       </c>
       <c r="O28">
-        <v>-0.09348213333333334</v>
+        <v>-0.1347309333333334</v>
       </c>
       <c r="P28">
-        <v>-0.3739285333333334</v>
+        <v>-0.5389237333333335</v>
       </c>
       <c r="Q28">
-        <v>-0.3679285333333334</v>
+        <v>-0.5329237333333335</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1338677015049035</v>
+        <v>0.1354297347130842</v>
       </c>
       <c r="T28">
-        <v>1.362379333395477</v>
+        <v>1.386543490339943</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1005238306035119</v>
+        <v>0.08243250947363032</v>
       </c>
       <c r="W28">
-        <v>0.1806148148148148</v>
+        <v>0.216362414266118</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5026191530175594</v>
+        <v>0.4121625473681515</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1572815581924033</v>
+        <v>0.1591815581924033</v>
       </c>
       <c r="C29">
-        <v>5.923031520555221</v>
+        <v>5.562853542630558</v>
       </c>
       <c r="D29">
-        <v>10.75203152055522</v>
+        <v>10.57185354263056</v>
       </c>
       <c r="E29">
-        <v>-8.84</v>
+        <v>-8.659999999999998</v>
       </c>
       <c r="F29">
-        <v>4.86</v>
+        <v>5.040000000000001</v>
       </c>
       <c r="G29">
         <v>0.031</v>
@@ -3614,37 +3614,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M29">
-        <v>1.145988</v>
+        <v>1.188432</v>
       </c>
       <c r="N29">
-        <v>-0.673654666666667</v>
+        <v>-0.7160986666666671</v>
       </c>
       <c r="O29">
-        <v>-0.1347309333333334</v>
+        <v>-0.1432197333333334</v>
       </c>
       <c r="P29">
-        <v>-0.5389237333333335</v>
+        <v>-0.5728789333333337</v>
       </c>
       <c r="Q29">
-        <v>-0.5329237333333335</v>
+        <v>-0.5668789333333337</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1354297347130842</v>
+        <v>0.1366745921396548</v>
       </c>
       <c r="T29">
-        <v>1.386543490339943</v>
+        <v>1.405801038816887</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.08243250947363032</v>
+        <v>0.0794884912781435</v>
       </c>
       <c r="W29">
-        <v>0.216362414266118</v>
+        <v>0.2170566137566138</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4121625473681515</v>
+        <v>0.3974424563907174</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1591815581924033</v>
+        <v>0.1610815581924033</v>
       </c>
       <c r="C30">
-        <v>5.562853542630558</v>
+        <v>5.208614730751611</v>
       </c>
       <c r="D30">
-        <v>10.57185354263056</v>
+        <v>10.39761473075161</v>
       </c>
       <c r="E30">
-        <v>-8.659999999999998</v>
+        <v>-8.479999999999999</v>
       </c>
       <c r="F30">
-        <v>5.040000000000001</v>
+        <v>5.220000000000001</v>
       </c>
       <c r="G30">
         <v>0.031</v>
@@ -3696,37 +3696,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M30">
-        <v>1.188432</v>
+        <v>1.230876</v>
       </c>
       <c r="N30">
-        <v>-0.7160986666666671</v>
+        <v>-0.758542666666667</v>
       </c>
       <c r="O30">
-        <v>-0.1432197333333334</v>
+        <v>-0.1517085333333334</v>
       </c>
       <c r="P30">
-        <v>-0.5728789333333337</v>
+        <v>-0.6068341333333336</v>
       </c>
       <c r="Q30">
-        <v>-0.5668789333333337</v>
+        <v>-0.6008341333333336</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1366745921396548</v>
+        <v>0.1379545159726077</v>
       </c>
       <c r="T30">
-        <v>1.405801038816887</v>
+        <v>1.425601053448111</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.0794884912781435</v>
+        <v>0.07674750882027649</v>
       </c>
       <c r="W30">
-        <v>0.2170566137566138</v>
+        <v>0.2177029374201788</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3974424563907174</v>
+        <v>0.3837375441013824</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1610815581924033</v>
+        <v>0.1629815581924033</v>
       </c>
       <c r="C31">
-        <v>5.208614730751612</v>
+        <v>4.860026189233916</v>
       </c>
       <c r="D31">
-        <v>10.39761473075161</v>
+        <v>10.22902618923391</v>
       </c>
       <c r="E31">
-        <v>-8.48</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F31">
-        <v>5.22</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="G31">
         <v>0.031</v>
@@ -3778,37 +3778,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M31">
-        <v>1.230876</v>
+        <v>1.27332</v>
       </c>
       <c r="N31">
-        <v>-0.7585426666666668</v>
+        <v>-0.8009866666666667</v>
       </c>
       <c r="O31">
-        <v>-0.1517085333333334</v>
+        <v>-0.1601973333333334</v>
       </c>
       <c r="P31">
-        <v>-0.6068341333333335</v>
+        <v>-0.6407893333333334</v>
       </c>
       <c r="Q31">
-        <v>-0.6008341333333335</v>
+        <v>-0.6347893333333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1379545159726077</v>
+        <v>0.1392710090579307</v>
       </c>
       <c r="T31">
-        <v>1.425601053448111</v>
+        <v>1.445966782783084</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.07674750882027651</v>
+        <v>0.07418925852626729</v>
       </c>
       <c r="W31">
-        <v>0.2177029374201788</v>
+        <v>0.2183061728395062</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3837375441013825</v>
+        <v>0.3709462926313364</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1629815581924033</v>
+        <v>0.1648815581924033</v>
       </c>
       <c r="C32">
-        <v>4.860026189233916</v>
+        <v>4.516817460237085</v>
       </c>
       <c r="D32">
-        <v>10.22902618923391</v>
+        <v>10.06581746023708</v>
       </c>
       <c r="E32">
-        <v>-8.300000000000001</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="F32">
-        <v>5.399999999999999</v>
+        <v>5.58</v>
       </c>
       <c r="G32">
         <v>0.031</v>
@@ -3860,37 +3860,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M32">
-        <v>1.27332</v>
+        <v>1.315764</v>
       </c>
       <c r="N32">
-        <v>-0.8009866666666667</v>
+        <v>-0.8434306666666669</v>
       </c>
       <c r="O32">
-        <v>-0.1601973333333334</v>
+        <v>-0.1686861333333334</v>
       </c>
       <c r="P32">
-        <v>-0.6407893333333334</v>
+        <v>-0.6747445333333335</v>
       </c>
       <c r="Q32">
-        <v>-0.6347893333333334</v>
+        <v>-0.6687445333333335</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1392710090579307</v>
+        <v>0.1406256613631181</v>
       </c>
       <c r="T32">
-        <v>1.445966782783084</v>
+        <v>1.466922823113274</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.07418925852626729</v>
+        <v>0.07179605663832318</v>
       </c>
       <c r="W32">
-        <v>0.2183061728395062</v>
+        <v>0.2188704898446834</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3709462926313364</v>
+        <v>0.3589802831916158</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1648815581924033</v>
+        <v>0.1667815581924033</v>
       </c>
       <c r="C33">
-        <v>4.516817460237085</v>
+        <v>4.178735075944802</v>
       </c>
       <c r="D33">
-        <v>10.06581746023708</v>
+        <v>9.907735075944801</v>
       </c>
       <c r="E33">
-        <v>-8.119999999999999</v>
+        <v>-7.94</v>
       </c>
       <c r="F33">
-        <v>5.58</v>
+        <v>5.76</v>
       </c>
       <c r="G33">
         <v>0.031</v>
@@ -3942,37 +3942,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M33">
-        <v>1.315764</v>
+        <v>1.358208</v>
       </c>
       <c r="N33">
-        <v>-0.8434306666666669</v>
+        <v>-0.8858746666666668</v>
       </c>
       <c r="O33">
-        <v>-0.1686861333333334</v>
+        <v>-0.1771749333333334</v>
       </c>
       <c r="P33">
-        <v>-0.6747445333333335</v>
+        <v>-0.7086997333333335</v>
       </c>
       <c r="Q33">
-        <v>-0.6687445333333335</v>
+        <v>-0.7026997333333335</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1406256613631181</v>
+        <v>0.142020156383164</v>
       </c>
       <c r="T33">
-        <v>1.466922823113274</v>
+        <v>1.488495217570822</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.07179605663832318</v>
+        <v>0.06955242986837558</v>
       </c>
       <c r="W33">
-        <v>0.2188704898446834</v>
+        <v>0.219399537037037</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3589802831916158</v>
+        <v>0.3477621493418779</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1667815581924033</v>
+        <v>0.1686815581924033</v>
       </c>
       <c r="C34">
-        <v>4.178735075944802</v>
+        <v>3.845541245062384</v>
       </c>
       <c r="D34">
-        <v>9.907735075944801</v>
+        <v>9.754541245062384</v>
       </c>
       <c r="E34">
-        <v>-7.94</v>
+        <v>-7.759999999999999</v>
       </c>
       <c r="F34">
-        <v>5.76</v>
+        <v>5.94</v>
       </c>
       <c r="G34">
         <v>0.031</v>
@@ -4024,37 +4024,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M34">
-        <v>1.358208</v>
+        <v>1.400652</v>
       </c>
       <c r="N34">
-        <v>-0.8858746666666668</v>
+        <v>-0.928318666666667</v>
       </c>
       <c r="O34">
-        <v>-0.1771749333333334</v>
+        <v>-0.1856637333333334</v>
       </c>
       <c r="P34">
-        <v>-0.7086997333333335</v>
+        <v>-0.7426549333333335</v>
       </c>
       <c r="Q34">
-        <v>-0.7026997333333335</v>
+        <v>-0.7366549333333335</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.142020156383164</v>
+        <v>0.1434562781202261</v>
       </c>
       <c r="T34">
-        <v>1.488495217570822</v>
+        <v>1.510711564101729</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06955242986837558</v>
+        <v>0.0674447804784248</v>
       </c>
       <c r="W34">
-        <v>0.219399537037037</v>
+        <v>0.2198965207631874</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3477621493418779</v>
+        <v>0.337223902392124</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1686815581924033</v>
+        <v>0.1705815581924033</v>
       </c>
       <c r="C35">
-        <v>3.845541245062384</v>
+        <v>3.517012659315433</v>
       </c>
       <c r="D35">
-        <v>9.754541245062384</v>
+        <v>9.606012659315432</v>
       </c>
       <c r="E35">
-        <v>-7.759999999999999</v>
+        <v>-7.579999999999999</v>
       </c>
       <c r="F35">
-        <v>5.94</v>
+        <v>6.12</v>
       </c>
       <c r="G35">
         <v>0.031</v>
@@ -4106,37 +4106,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M35">
-        <v>1.400652</v>
+        <v>1.443096</v>
       </c>
       <c r="N35">
-        <v>-0.928318666666667</v>
+        <v>-0.9707626666666669</v>
       </c>
       <c r="O35">
-        <v>-0.1856637333333334</v>
+        <v>-0.1941525333333334</v>
       </c>
       <c r="P35">
-        <v>-0.7426549333333335</v>
+        <v>-0.7766101333333335</v>
       </c>
       <c r="Q35">
-        <v>-0.7366549333333335</v>
+        <v>-0.7706101333333335</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1434562781202261</v>
+        <v>0.1449359186978053</v>
       </c>
       <c r="T35">
-        <v>1.510711564101729</v>
+        <v>1.533601133254786</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0674447804784248</v>
+        <v>0.06546111046435349</v>
       </c>
       <c r="W35">
-        <v>0.2198965207631874</v>
+        <v>0.2203642701525055</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.337223902392124</v>
+        <v>0.3273055523217674</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1705815581924033</v>
+        <v>0.1724815581924034</v>
       </c>
       <c r="C36">
-        <v>3.517012659315433</v>
+        <v>3.192939407351014</v>
       </c>
       <c r="D36">
-        <v>9.606012659315432</v>
+        <v>9.461939407351014</v>
       </c>
       <c r="E36">
-        <v>-7.579999999999999</v>
+        <v>-7.399999999999999</v>
       </c>
       <c r="F36">
-        <v>6.12</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="G36">
         <v>0.031</v>
@@ -4188,37 +4188,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M36">
-        <v>1.443096</v>
+        <v>1.48554</v>
       </c>
       <c r="N36">
-        <v>-0.9707626666666669</v>
+        <v>-1.013206666666667</v>
       </c>
       <c r="O36">
-        <v>-0.1941525333333334</v>
+        <v>-0.2026413333333334</v>
       </c>
       <c r="P36">
-        <v>-0.7766101333333335</v>
+        <v>-0.8105653333333336</v>
       </c>
       <c r="Q36">
-        <v>-0.7706101333333335</v>
+        <v>-0.8045653333333336</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1449359186978053</v>
+        <v>0.1464610866777715</v>
       </c>
       <c r="T36">
-        <v>1.533601133254786</v>
+        <v>1.557194996843321</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.06546111046435349</v>
+        <v>0.0635907930225148</v>
       </c>
       <c r="W36">
-        <v>0.2203642701525055</v>
+        <v>0.220805291005291</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3273055523217674</v>
+        <v>0.317953965112574</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1724815581924034</v>
+        <v>0.1743815581924033</v>
       </c>
       <c r="C37">
-        <v>3.192939407351014</v>
+        <v>2.873123984931992</v>
       </c>
       <c r="D37">
-        <v>9.461939407351014</v>
+        <v>9.322123984931991</v>
       </c>
       <c r="E37">
-        <v>-7.399999999999999</v>
+        <v>-7.219999999999999</v>
       </c>
       <c r="F37">
-        <v>6.300000000000001</v>
+        <v>6.48</v>
       </c>
       <c r="G37">
         <v>0.031</v>
@@ -4270,37 +4270,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M37">
-        <v>1.48554</v>
+        <v>1.527984</v>
       </c>
       <c r="N37">
-        <v>-1.013206666666667</v>
+        <v>-1.055650666666667</v>
       </c>
       <c r="O37">
-        <v>-0.2026413333333334</v>
+        <v>-0.2111301333333334</v>
       </c>
       <c r="P37">
-        <v>-0.8105653333333336</v>
+        <v>-0.8445205333333335</v>
       </c>
       <c r="Q37">
-        <v>-0.8045653333333336</v>
+        <v>-0.8385205333333335</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1464610866777715</v>
+        <v>0.1480339161571117</v>
       </c>
       <c r="T37">
-        <v>1.557194996843321</v>
+        <v>1.581526168668998</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0635907930225148</v>
+        <v>0.06182438210522273</v>
       </c>
       <c r="W37">
-        <v>0.220805291005291</v>
+        <v>0.2212218106995885</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.317953965112574</v>
+        <v>0.3091219105261136</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1743815581924033</v>
+        <v>0.1762815581924033</v>
       </c>
       <c r="C38">
-        <v>2.873123984931993</v>
+        <v>2.557380391609376</v>
       </c>
       <c r="D38">
-        <v>9.322123984931991</v>
+        <v>9.186380391609376</v>
       </c>
       <c r="E38">
-        <v>-7.22</v>
+        <v>-7.039999999999999</v>
       </c>
       <c r="F38">
-        <v>6.48</v>
+        <v>6.66</v>
       </c>
       <c r="G38">
         <v>0.031</v>
@@ -4352,37 +4352,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M38">
-        <v>1.527984</v>
+        <v>1.570428</v>
       </c>
       <c r="N38">
-        <v>-1.055650666666667</v>
+        <v>-1.098094666666667</v>
       </c>
       <c r="O38">
-        <v>-0.2111301333333334</v>
+        <v>-0.2196189333333334</v>
       </c>
       <c r="P38">
-        <v>-0.8445205333333334</v>
+        <v>-0.8784757333333335</v>
       </c>
       <c r="Q38">
-        <v>-0.8385205333333334</v>
+        <v>-0.8724757333333335</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1480339161571117</v>
+        <v>0.1496566767310341</v>
       </c>
       <c r="T38">
-        <v>1.581526168668998</v>
+        <v>1.606629758647871</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.06182438210522274</v>
+        <v>0.06015345285913564</v>
       </c>
       <c r="W38">
-        <v>0.2212218106995885</v>
+        <v>0.2216158158158158</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3091219105261137</v>
+        <v>0.3007672642956781</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1762815581924033</v>
+        <v>0.1781815581924033</v>
       </c>
       <c r="C39">
-        <v>2.557380391609376</v>
+        <v>2.245533305184468</v>
       </c>
       <c r="D39">
-        <v>9.186380391609376</v>
+        <v>9.054533305184467</v>
       </c>
       <c r="E39">
-        <v>-7.039999999999999</v>
+        <v>-6.859999999999999</v>
       </c>
       <c r="F39">
-        <v>6.66</v>
+        <v>6.84</v>
       </c>
       <c r="G39">
         <v>0.031</v>
@@ -4434,37 +4434,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M39">
-        <v>1.570428</v>
+        <v>1.612872</v>
       </c>
       <c r="N39">
-        <v>-1.098094666666667</v>
+        <v>-1.140538666666667</v>
       </c>
       <c r="O39">
-        <v>-0.2196189333333334</v>
+        <v>-0.2281077333333334</v>
       </c>
       <c r="P39">
-        <v>-0.8784757333333335</v>
+        <v>-0.9124309333333335</v>
       </c>
       <c r="Q39">
-        <v>-0.8724757333333335</v>
+        <v>-0.9064309333333335</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1496566767310341</v>
+        <v>0.1513317844202443</v>
       </c>
       <c r="T39">
-        <v>1.606629758647871</v>
+        <v>1.632543141851869</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06015345285913564</v>
+        <v>0.05857046725757944</v>
       </c>
       <c r="W39">
-        <v>0.2216158158158158</v>
+        <v>0.2219890838206628</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3007672642956781</v>
+        <v>0.2928523362878972</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1781815581924033</v>
+        <v>0.1800815581924033</v>
       </c>
       <c r="C40">
-        <v>2.245533305184468</v>
+        <v>1.93741732625607</v>
       </c>
       <c r="D40">
-        <v>9.054533305184467</v>
+        <v>8.92641732625607</v>
       </c>
       <c r="E40">
-        <v>-6.859999999999999</v>
+        <v>-6.679999999999999</v>
       </c>
       <c r="F40">
-        <v>6.84</v>
+        <v>7.02</v>
       </c>
       <c r="G40">
         <v>0.031</v>
@@ -4516,37 +4516,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M40">
-        <v>1.612872</v>
+        <v>1.655316</v>
       </c>
       <c r="N40">
-        <v>-1.140538666666667</v>
+        <v>-1.182982666666667</v>
       </c>
       <c r="O40">
-        <v>-0.2281077333333334</v>
+        <v>-0.2365965333333334</v>
       </c>
       <c r="P40">
-        <v>-0.9124309333333335</v>
+        <v>-0.9463861333333335</v>
       </c>
       <c r="Q40">
-        <v>-0.9064309333333335</v>
+        <v>-0.9403861333333335</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1513317844202443</v>
+        <v>0.1530618136730352</v>
       </c>
       <c r="T40">
-        <v>1.632543141851869</v>
+        <v>1.659306144177309</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05857046725757944</v>
+        <v>0.05706866040482098</v>
       </c>
       <c r="W40">
-        <v>0.2219890838206628</v>
+        <v>0.2223432098765432</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2928523362878972</v>
+        <v>0.2853433020241049</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1800815581924033</v>
+        <v>0.1819815581924034</v>
       </c>
       <c r="C41">
-        <v>1.93741732625607</v>
+        <v>1.632876286007988</v>
       </c>
       <c r="D41">
-        <v>8.92641732625607</v>
+        <v>8.801876286007987</v>
       </c>
       <c r="E41">
-        <v>-6.679999999999999</v>
+        <v>-6.499999999999999</v>
       </c>
       <c r="F41">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="G41">
         <v>0.031</v>
@@ -4598,37 +4598,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M41">
-        <v>1.655316</v>
+        <v>1.69776</v>
       </c>
       <c r="N41">
-        <v>-1.182982666666667</v>
+        <v>-1.225426666666667</v>
       </c>
       <c r="O41">
-        <v>-0.2365965333333334</v>
+        <v>-0.2450853333333334</v>
       </c>
       <c r="P41">
-        <v>-0.9463861333333335</v>
+        <v>-0.9803413333333335</v>
       </c>
       <c r="Q41">
-        <v>-0.9403861333333335</v>
+        <v>-0.9743413333333335</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1530618136730352</v>
+        <v>0.1548495105675858</v>
       </c>
       <c r="T41">
-        <v>1.659306144177309</v>
+        <v>1.686961246580265</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05706866040482098</v>
+        <v>0.05564194389470047</v>
       </c>
       <c r="W41">
-        <v>0.2223432098765432</v>
+        <v>0.2226796296296296</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2853433020241049</v>
+        <v>0.2782097194735023</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1819815581924034</v>
+        <v>0.1838815581924033</v>
       </c>
       <c r="C42">
-        <v>1.632876286007988</v>
+        <v>1.331762611145539</v>
       </c>
       <c r="D42">
-        <v>8.801876286007987</v>
+        <v>8.680762611145539</v>
       </c>
       <c r="E42">
-        <v>-6.499999999999999</v>
+        <v>-6.319999999999999</v>
       </c>
       <c r="F42">
-        <v>7.2</v>
+        <v>7.380000000000001</v>
       </c>
       <c r="G42">
         <v>0.031</v>
@@ -4680,37 +4680,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M42">
-        <v>1.69776</v>
+        <v>1.740204</v>
       </c>
       <c r="N42">
-        <v>-1.225426666666667</v>
+        <v>-1.267870666666667</v>
       </c>
       <c r="O42">
-        <v>-0.2450853333333334</v>
+        <v>-0.2535741333333334</v>
       </c>
       <c r="P42">
-        <v>-0.9803413333333335</v>
+        <v>-1.014296533333334</v>
       </c>
       <c r="Q42">
-        <v>-0.9743413333333335</v>
+        <v>-1.008296533333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1548495105675858</v>
+        <v>0.1566978073568669</v>
       </c>
       <c r="T42">
-        <v>1.686961246580265</v>
+        <v>1.715553810081625</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05564194389470047</v>
+        <v>0.05428482331190289</v>
       </c>
       <c r="W42">
-        <v>0.2226796296296296</v>
+        <v>0.2229996386630533</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2782097194735023</v>
+        <v>0.2714241165595144</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1838815581924033</v>
+        <v>0.1857815581924033</v>
       </c>
       <c r="C43">
-        <v>1.331762611145539</v>
+        <v>1.033936740551168</v>
       </c>
       <c r="D43">
-        <v>8.680762611145539</v>
+        <v>8.562936740551168</v>
       </c>
       <c r="E43">
-        <v>-6.319999999999999</v>
+        <v>-6.139999999999999</v>
       </c>
       <c r="F43">
-        <v>7.380000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="G43">
         <v>0.031</v>
@@ -4762,37 +4762,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M43">
-        <v>1.740204</v>
+        <v>1.782648</v>
       </c>
       <c r="N43">
-        <v>-1.267870666666667</v>
+        <v>-1.310314666666667</v>
       </c>
       <c r="O43">
-        <v>-0.2535741333333334</v>
+        <v>-0.2620629333333334</v>
       </c>
       <c r="P43">
-        <v>-1.014296533333334</v>
+        <v>-1.048251733333334</v>
       </c>
       <c r="Q43">
-        <v>-1.008296533333334</v>
+        <v>-1.042251733333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1566978073568669</v>
+        <v>0.1586098385181922</v>
       </c>
       <c r="T43">
-        <v>1.715553810081625</v>
+        <v>1.74513232404855</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05428482331190289</v>
+        <v>0.05299232751876234</v>
       </c>
       <c r="W43">
-        <v>0.2229996386630533</v>
+        <v>0.2233044091710758</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2714241165595144</v>
+        <v>0.2649616375938116</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1857815581924033</v>
+        <v>0.1876815581924033</v>
       </c>
       <c r="C44">
-        <v>1.033936740551169</v>
+        <v>0.7392665888110503</v>
       </c>
       <c r="D44">
-        <v>8.562936740551168</v>
+        <v>8.44826658881105</v>
       </c>
       <c r="E44">
-        <v>-6.14</v>
+        <v>-5.959999999999999</v>
       </c>
       <c r="F44">
-        <v>7.56</v>
+        <v>7.74</v>
       </c>
       <c r="G44">
         <v>0.031</v>
@@ -4844,37 +4844,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M44">
-        <v>1.782648</v>
+        <v>1.825092</v>
       </c>
       <c r="N44">
-        <v>-1.310314666666667</v>
+        <v>-1.352758666666667</v>
       </c>
       <c r="O44">
-        <v>-0.2620629333333334</v>
+        <v>-0.2705517333333334</v>
       </c>
       <c r="P44">
-        <v>-1.048251733333333</v>
+        <v>-1.082206933333334</v>
       </c>
       <c r="Q44">
-        <v>-1.042251733333333</v>
+        <v>-1.076206933333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1586098385181922</v>
+        <v>0.1605889584921956</v>
       </c>
       <c r="T44">
-        <v>1.745132324048549</v>
+        <v>1.775748680610804</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05299232751876235</v>
+        <v>0.05175994780902369</v>
       </c>
       <c r="W44">
-        <v>0.2233044091710758</v>
+        <v>0.2235950043066322</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2649616375938117</v>
+        <v>0.2587997390451184</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1876815581924033</v>
+        <v>0.1895815581924034</v>
       </c>
       <c r="C45">
-        <v>0.7392665888110503</v>
+        <v>0.4476270522770172</v>
       </c>
       <c r="D45">
-        <v>8.44826658881105</v>
+        <v>8.336627052277017</v>
       </c>
       <c r="E45">
-        <v>-5.959999999999999</v>
+        <v>-5.779999999999999</v>
       </c>
       <c r="F45">
-        <v>7.74</v>
+        <v>7.92</v>
       </c>
       <c r="G45">
         <v>0.031</v>
@@ -4926,37 +4926,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M45">
-        <v>1.825092</v>
+        <v>1.867536</v>
       </c>
       <c r="N45">
-        <v>-1.352758666666667</v>
+        <v>-1.395202666666667</v>
       </c>
       <c r="O45">
-        <v>-0.2705517333333334</v>
+        <v>-0.2790405333333334</v>
       </c>
       <c r="P45">
-        <v>-1.082206933333334</v>
+        <v>-1.116162133333333</v>
       </c>
       <c r="Q45">
-        <v>-1.076206933333334</v>
+        <v>-1.110162133333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1605889584921956</v>
+        <v>0.1626387613224134</v>
       </c>
       <c r="T45">
-        <v>1.775748680610804</v>
+        <v>1.807458478478855</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05175994780902369</v>
+        <v>0.05058358535881861</v>
       </c>
       <c r="W45">
-        <v>0.2235950043066322</v>
+        <v>0.2238723905723906</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2587997390451184</v>
+        <v>0.252917926794093</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1895815581924034</v>
+        <v>0.1914815581924033</v>
       </c>
       <c r="C46">
-        <v>0.4476270522770172</v>
+        <v>0.1588995537805591</v>
       </c>
       <c r="D46">
-        <v>8.336627052277017</v>
+        <v>8.227899553780558</v>
       </c>
       <c r="E46">
-        <v>-5.779999999999999</v>
+        <v>-5.6</v>
       </c>
       <c r="F46">
-        <v>7.92</v>
+        <v>8.1</v>
       </c>
       <c r="G46">
         <v>0.031</v>
@@ -5008,37 +5008,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M46">
-        <v>1.867536</v>
+        <v>1.90998</v>
       </c>
       <c r="N46">
-        <v>-1.395202666666667</v>
+        <v>-1.437646666666667</v>
       </c>
       <c r="O46">
-        <v>-0.2790405333333334</v>
+        <v>-0.2875293333333334</v>
       </c>
       <c r="P46">
-        <v>-1.116162133333333</v>
+        <v>-1.150117333333333</v>
       </c>
       <c r="Q46">
-        <v>-1.110162133333333</v>
+        <v>-1.144117333333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1626387613224134</v>
+        <v>0.1647631024373663</v>
       </c>
       <c r="T46">
-        <v>1.807458478478855</v>
+        <v>1.840321359905743</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05058358535881861</v>
+        <v>0.0494595056841782</v>
       </c>
       <c r="W46">
-        <v>0.2238723905723906</v>
+        <v>0.2241374485596708</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.252917926794093</v>
+        <v>0.2472975284208909</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1914815581924033</v>
+        <v>0.1933815581924033</v>
       </c>
       <c r="C47">
-        <v>0.1588995537805591</v>
+        <v>-0.1270283774844181</v>
       </c>
       <c r="D47">
-        <v>8.227899553780558</v>
+        <v>8.121971622515582</v>
       </c>
       <c r="E47">
-        <v>-5.6</v>
+        <v>-5.419999999999998</v>
       </c>
       <c r="F47">
-        <v>8.1</v>
+        <v>8.280000000000001</v>
       </c>
       <c r="G47">
         <v>0.031</v>
@@ -5090,37 +5090,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M47">
-        <v>1.90998</v>
+        <v>1.952424</v>
       </c>
       <c r="N47">
-        <v>-1.437646666666667</v>
+        <v>-1.480090666666667</v>
       </c>
       <c r="O47">
-        <v>-0.2875293333333334</v>
+        <v>-0.2960181333333334</v>
       </c>
       <c r="P47">
-        <v>-1.150117333333333</v>
+        <v>-1.184072533333334</v>
       </c>
       <c r="Q47">
-        <v>-1.144117333333333</v>
+        <v>-1.178072533333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1647631024373663</v>
+        <v>0.1669661228528731</v>
       </c>
       <c r="T47">
-        <v>1.840321359905743</v>
+        <v>1.874401385089183</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0494595056841782</v>
+        <v>0.04838429903886996</v>
       </c>
       <c r="W47">
-        <v>0.2241374485596708</v>
+        <v>0.2243909822866345</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2472975284208909</v>
+        <v>0.2419214951943498</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1933815581924033</v>
+        <v>0.1952815581924034</v>
       </c>
       <c r="C48">
-        <v>-0.1270283774844181</v>
+        <v>-0.4102634940391798</v>
       </c>
       <c r="D48">
-        <v>8.121971622515582</v>
+        <v>8.01873650596082</v>
       </c>
       <c r="E48">
-        <v>-5.419999999999998</v>
+        <v>-5.239999999999998</v>
       </c>
       <c r="F48">
-        <v>8.280000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G48">
         <v>0.031</v>
@@ -5172,37 +5172,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M48">
-        <v>1.952424</v>
+        <v>1.994868</v>
       </c>
       <c r="N48">
-        <v>-1.480090666666667</v>
+        <v>-1.522534666666667</v>
       </c>
       <c r="O48">
-        <v>-0.2960181333333334</v>
+        <v>-0.3045069333333335</v>
       </c>
       <c r="P48">
-        <v>-1.184072533333334</v>
+        <v>-1.218027733333334</v>
       </c>
       <c r="Q48">
-        <v>-1.178072533333334</v>
+        <v>-1.212027733333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1669661228528731</v>
+        <v>0.1692522761142481</v>
       </c>
       <c r="T48">
-        <v>1.874401385089183</v>
+        <v>1.90976744895879</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04838429903886996</v>
+        <v>0.04735484586783018</v>
       </c>
       <c r="W48">
-        <v>0.2243909822866345</v>
+        <v>0.2246337273443657</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2419214951943498</v>
+        <v>0.2367742293391508</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1952815581924034</v>
+        <v>0.1971815581924034</v>
       </c>
       <c r="C49">
-        <v>-0.4102634940391798</v>
+        <v>-0.690907188973017</v>
       </c>
       <c r="D49">
-        <v>8.01873650596082</v>
+        <v>7.918092811026984</v>
       </c>
       <c r="E49">
-        <v>-5.239999999999998</v>
+        <v>-5.059999999999999</v>
       </c>
       <c r="F49">
-        <v>8.460000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G49">
         <v>0.031</v>
@@ -5254,37 +5254,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M49">
-        <v>1.994868</v>
+        <v>2.037312</v>
       </c>
       <c r="N49">
-        <v>-1.522534666666667</v>
+        <v>-1.564978666666667</v>
       </c>
       <c r="O49">
-        <v>-0.3045069333333335</v>
+        <v>-0.3129957333333334</v>
       </c>
       <c r="P49">
-        <v>-1.218027733333334</v>
+        <v>-1.251982933333333</v>
       </c>
       <c r="Q49">
-        <v>-1.212027733333334</v>
+        <v>-1.245982933333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1692522761142481</v>
+        <v>0.1716263583472144</v>
       </c>
       <c r="T49">
-        <v>1.90976744895879</v>
+        <v>1.946493746054152</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04735484586783018</v>
+        <v>0.04636828657891706</v>
       </c>
       <c r="W49">
-        <v>0.2246337273443657</v>
+        <v>0.2248663580246914</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2367742293391508</v>
+        <v>0.2318414328945853</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1971815581924034</v>
+        <v>0.1990815581924034</v>
       </c>
       <c r="C50">
-        <v>-0.690907188973017</v>
+        <v>-0.9690558281071988</v>
       </c>
       <c r="D50">
-        <v>7.918092811026984</v>
+        <v>7.819944171892802</v>
       </c>
       <c r="E50">
-        <v>-5.059999999999999</v>
+        <v>-4.879999999999999</v>
       </c>
       <c r="F50">
-        <v>8.640000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G50">
         <v>0.031</v>
@@ -5336,37 +5336,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M50">
-        <v>2.037312</v>
+        <v>2.079756</v>
       </c>
       <c r="N50">
-        <v>-1.564978666666667</v>
+        <v>-1.607422666666667</v>
       </c>
       <c r="O50">
-        <v>-0.3129957333333334</v>
+        <v>-0.3214845333333334</v>
       </c>
       <c r="P50">
-        <v>-1.251982933333333</v>
+        <v>-1.285938133333334</v>
       </c>
       <c r="Q50">
-        <v>-1.245982933333333</v>
+        <v>-1.279938133333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1716263583472144</v>
+        <v>0.1740935418442186</v>
       </c>
       <c r="T50">
-        <v>1.946493746054151</v>
+        <v>1.984660290094429</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04636828657891706</v>
+        <v>0.04542199501608202</v>
       </c>
       <c r="W50">
-        <v>0.2248663580246914</v>
+        <v>0.2250894935752079</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2318414328945853</v>
+        <v>0.22710997508041</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1990815581924034</v>
+        <v>0.2009815581924033</v>
       </c>
       <c r="C51">
-        <v>-0.9690558281071988</v>
+        <v>-1.244801057757326</v>
       </c>
       <c r="D51">
-        <v>7.819944171892802</v>
+        <v>7.724198942242674</v>
       </c>
       <c r="E51">
-        <v>-4.879999999999999</v>
+        <v>-4.699999999999999</v>
       </c>
       <c r="F51">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="G51">
         <v>0.031</v>
@@ -5418,37 +5418,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M51">
-        <v>2.079756</v>
+        <v>2.1222</v>
       </c>
       <c r="N51">
-        <v>-1.607422666666667</v>
+        <v>-1.649866666666667</v>
       </c>
       <c r="O51">
-        <v>-0.3214845333333334</v>
+        <v>-0.3299733333333335</v>
       </c>
       <c r="P51">
-        <v>-1.285938133333334</v>
+        <v>-1.319893333333334</v>
       </c>
       <c r="Q51">
-        <v>-1.279938133333334</v>
+        <v>-1.313893333333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1740935418442186</v>
+        <v>0.176659412681103</v>
       </c>
       <c r="T51">
-        <v>1.984660290094429</v>
+        <v>2.024353495896317</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04542199501608202</v>
+        <v>0.04451355511576037</v>
       </c>
       <c r="W51">
-        <v>0.2250894935752079</v>
+        <v>0.2253037037037037</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.22710997508041</v>
+        <v>0.2225677755788018</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2009815581924033</v>
+        <v>0.2028815581924033</v>
       </c>
       <c r="C52">
-        <v>-1.244801057757326</v>
+        <v>-1.518230090160258</v>
       </c>
       <c r="D52">
-        <v>7.724198942242674</v>
+        <v>7.630769909839742</v>
       </c>
       <c r="E52">
-        <v>-4.699999999999999</v>
+        <v>-4.52</v>
       </c>
       <c r="F52">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="G52">
         <v>0.031</v>
@@ -5500,37 +5500,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M52">
-        <v>2.1222</v>
+        <v>2.164644</v>
       </c>
       <c r="N52">
-        <v>-1.649866666666667</v>
+        <v>-1.692310666666667</v>
       </c>
       <c r="O52">
-        <v>-0.3299733333333335</v>
+        <v>-0.3384621333333334</v>
       </c>
       <c r="P52">
-        <v>-1.319893333333334</v>
+        <v>-1.353848533333333</v>
       </c>
       <c r="Q52">
-        <v>-1.313893333333334</v>
+        <v>-1.347848533333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.176659412681103</v>
+        <v>0.179330012939901</v>
       </c>
       <c r="T52">
-        <v>2.024353495896317</v>
+        <v>2.065666832547262</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04451355511576037</v>
+        <v>0.04364074030956899</v>
       </c>
       <c r="W52">
-        <v>0.2253037037037037</v>
+        <v>0.2255095134350036</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2225677755788018</v>
+        <v>0.218203701547845</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2028815581924033</v>
+        <v>0.2047815581924033</v>
       </c>
       <c r="C53">
-        <v>-1.518230090160258</v>
+        <v>-1.789425968434071</v>
       </c>
       <c r="D53">
-        <v>7.630769909839742</v>
+        <v>7.539574031565929</v>
       </c>
       <c r="E53">
-        <v>-4.52</v>
+        <v>-4.34</v>
       </c>
       <c r="F53">
-        <v>9.18</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G53">
         <v>0.031</v>
@@ -5582,37 +5582,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M53">
-        <v>2.164644</v>
+        <v>2.207088</v>
       </c>
       <c r="N53">
-        <v>-1.692310666666667</v>
+        <v>-1.734754666666667</v>
       </c>
       <c r="O53">
-        <v>-0.3384621333333334</v>
+        <v>-0.3469509333333334</v>
       </c>
       <c r="P53">
-        <v>-1.353848533333333</v>
+        <v>-1.387803733333334</v>
       </c>
       <c r="Q53">
-        <v>-1.347848533333333</v>
+        <v>-1.381803733333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.179330012939901</v>
+        <v>0.1821118882094823</v>
       </c>
       <c r="T53">
-        <v>2.065666832547262</v>
+        <v>2.108701558225331</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04364074030956899</v>
+        <v>0.04280149530361574</v>
       </c>
       <c r="W53">
-        <v>0.2255095134350036</v>
+        <v>0.2257074074074074</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.218203701547845</v>
+        <v>0.2140074765180787</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2047815581924033</v>
+        <v>0.2066815581924033</v>
       </c>
       <c r="C54">
-        <v>-1.789425968434071</v>
+        <v>-2.058467812763073</v>
       </c>
       <c r="D54">
-        <v>7.539574031565929</v>
+        <v>7.450532187236928</v>
       </c>
       <c r="E54">
-        <v>-4.34</v>
+        <v>-4.159999999999998</v>
       </c>
       <c r="F54">
-        <v>9.359999999999999</v>
+        <v>9.540000000000001</v>
       </c>
       <c r="G54">
         <v>0.031</v>
@@ -5664,37 +5664,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M54">
-        <v>2.207088</v>
+        <v>2.249532</v>
       </c>
       <c r="N54">
-        <v>-1.734754666666667</v>
+        <v>-1.777198666666667</v>
       </c>
       <c r="O54">
-        <v>-0.3469509333333334</v>
+        <v>-0.3554397333333335</v>
       </c>
       <c r="P54">
-        <v>-1.387803733333334</v>
+        <v>-1.421758933333334</v>
       </c>
       <c r="Q54">
-        <v>-1.381803733333334</v>
+        <v>-1.415758933333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1821118882094823</v>
+        <v>0.1850121411501095</v>
       </c>
       <c r="T54">
-        <v>2.108701558225331</v>
+        <v>2.153567548825869</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04280149530361574</v>
+        <v>0.04199391992052865</v>
       </c>
       <c r="W54">
-        <v>0.2257074074074074</v>
+        <v>0.2258978336827393</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2140074765180787</v>
+        <v>0.2099695996026432</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2066815581924033</v>
+        <v>0.2085815581924034</v>
       </c>
       <c r="C55">
-        <v>-2.058467812763073</v>
+        <v>-2.325431049341867</v>
       </c>
       <c r="D55">
-        <v>7.450532187236928</v>
+        <v>7.363568950658134</v>
       </c>
       <c r="E55">
-        <v>-4.159999999999998</v>
+        <v>-3.979999999999999</v>
       </c>
       <c r="F55">
-        <v>9.540000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G55">
         <v>0.031</v>
@@ -5746,37 +5746,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M55">
-        <v>2.249532</v>
+        <v>2.291976</v>
       </c>
       <c r="N55">
-        <v>-1.777198666666667</v>
+        <v>-1.819642666666667</v>
       </c>
       <c r="O55">
-        <v>-0.3554397333333335</v>
+        <v>-0.3639285333333335</v>
       </c>
       <c r="P55">
-        <v>-1.421758933333334</v>
+        <v>-1.455714133333334</v>
       </c>
       <c r="Q55">
-        <v>-1.415758933333334</v>
+        <v>-1.449714133333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1850121411501095</v>
+        <v>0.1880384920446772</v>
       </c>
       <c r="T55">
-        <v>2.153567548825869</v>
+        <v>2.20038423466991</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04199391992052865</v>
+        <v>0.04121625473681516</v>
       </c>
       <c r="W55">
-        <v>0.2258978336827393</v>
+        <v>0.226081207133059</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2099695996026432</v>
+        <v>0.2060812736840757</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2085815581924034</v>
+        <v>0.2104815581924033</v>
       </c>
       <c r="C56">
-        <v>-2.325431049341867</v>
+        <v>-2.590387623470854</v>
       </c>
       <c r="D56">
-        <v>7.363568950658134</v>
+        <v>7.278612376529146</v>
       </c>
       <c r="E56">
-        <v>-3.979999999999999</v>
+        <v>-3.799999999999999</v>
       </c>
       <c r="F56">
-        <v>9.720000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="G56">
         <v>0.031</v>
@@ -5828,37 +5828,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M56">
-        <v>2.291976</v>
+        <v>2.33442</v>
       </c>
       <c r="N56">
-        <v>-1.819642666666667</v>
+        <v>-1.862086666666667</v>
       </c>
       <c r="O56">
-        <v>-0.3639285333333335</v>
+        <v>-0.3724173333333334</v>
       </c>
       <c r="P56">
-        <v>-1.455714133333334</v>
+        <v>-1.489669333333334</v>
       </c>
       <c r="Q56">
-        <v>-1.449714133333334</v>
+        <v>-1.483669333333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1880384920446772</v>
+        <v>0.1911993474234478</v>
       </c>
       <c r="T56">
-        <v>2.20038423466991</v>
+        <v>2.24928166210702</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04121625473681516</v>
+        <v>0.04046686828705488</v>
       </c>
       <c r="W56">
-        <v>0.226081207133059</v>
+        <v>0.2262579124579125</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2060812736840757</v>
+        <v>0.2023343414352744</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2104815581924033</v>
+        <v>0.2123815581924034</v>
       </c>
       <c r="C57">
-        <v>-2.590387623470854</v>
+        <v>-2.853406198068607</v>
       </c>
       <c r="D57">
-        <v>7.278612376529146</v>
+        <v>7.195593801931396</v>
       </c>
       <c r="E57">
-        <v>-3.799999999999999</v>
+        <v>-3.619999999999997</v>
       </c>
       <c r="F57">
-        <v>9.9</v>
+        <v>10.08</v>
       </c>
       <c r="G57">
         <v>0.031</v>
@@ -5910,37 +5910,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M57">
-        <v>2.33442</v>
+        <v>2.376864000000001</v>
       </c>
       <c r="N57">
-        <v>-1.862086666666667</v>
+        <v>-1.904530666666667</v>
       </c>
       <c r="O57">
-        <v>-0.3724173333333334</v>
+        <v>-0.3809061333333335</v>
       </c>
       <c r="P57">
-        <v>-1.489669333333334</v>
+        <v>-1.523624533333334</v>
       </c>
       <c r="Q57">
-        <v>-1.483669333333334</v>
+        <v>-1.517624533333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1911993474234478</v>
+        <v>0.1945038780467079</v>
       </c>
       <c r="T57">
-        <v>2.24928166210702</v>
+        <v>2.300401699882179</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04046686828705488</v>
+        <v>0.03974424563907175</v>
       </c>
       <c r="W57">
-        <v>0.2262579124579125</v>
+        <v>0.2264283068783069</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2023343414352744</v>
+        <v>0.1987212281953588</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2123815581924034</v>
+        <v>0.2142815581924034</v>
       </c>
       <c r="C58">
-        <v>-2.853406198068607</v>
+        <v>-3.114552338752187</v>
       </c>
       <c r="D58">
-        <v>7.195593801931396</v>
+        <v>7.114447661247815</v>
       </c>
       <c r="E58">
-        <v>-3.619999999999997</v>
+        <v>-3.439999999999998</v>
       </c>
       <c r="F58">
-        <v>10.08</v>
+        <v>10.26</v>
       </c>
       <c r="G58">
         <v>0.031</v>
@@ -5992,37 +5992,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M58">
-        <v>2.376864000000001</v>
+        <v>2.419308</v>
       </c>
       <c r="N58">
-        <v>-1.904530666666667</v>
+        <v>-1.946974666666667</v>
       </c>
       <c r="O58">
-        <v>-0.3809061333333335</v>
+        <v>-0.3893949333333335</v>
       </c>
       <c r="P58">
-        <v>-1.523624533333334</v>
+        <v>-1.557579733333334</v>
       </c>
       <c r="Q58">
-        <v>-1.517624533333334</v>
+        <v>-1.551579733333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1945038780467079</v>
+        <v>0.1979621077687244</v>
       </c>
       <c r="T58">
-        <v>2.300401699882179</v>
+        <v>2.353899413832928</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03974424563907175</v>
+        <v>0.03904697817171962</v>
       </c>
       <c r="W58">
-        <v>0.2264283068783069</v>
+        <v>0.2265927225471085</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1987212281953588</v>
+        <v>0.195234890858598</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2142815581924034</v>
+        <v>0.2161815581924034</v>
       </c>
       <c r="C59">
-        <v>-3.114552338752187</v>
+        <v>-3.373888686534064</v>
       </c>
       <c r="D59">
-        <v>7.114447661247815</v>
+        <v>7.035111313465937</v>
       </c>
       <c r="E59">
-        <v>-3.439999999999998</v>
+        <v>-3.259999999999998</v>
       </c>
       <c r="F59">
-        <v>10.26</v>
+        <v>10.44</v>
       </c>
       <c r="G59">
         <v>0.031</v>
@@ -6074,37 +6074,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M59">
-        <v>2.419308</v>
+        <v>2.461752000000001</v>
       </c>
       <c r="N59">
-        <v>-1.946974666666667</v>
+        <v>-1.989418666666667</v>
       </c>
       <c r="O59">
-        <v>-0.3893949333333335</v>
+        <v>-0.3978837333333335</v>
       </c>
       <c r="P59">
-        <v>-1.557579733333334</v>
+        <v>-1.591534933333334</v>
       </c>
       <c r="Q59">
-        <v>-1.551579733333334</v>
+        <v>-1.585534933333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1979621077687244</v>
+        <v>0.2015850150965512</v>
       </c>
       <c r="T59">
-        <v>2.353899413832928</v>
+        <v>2.409944637971807</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03904697817171962</v>
+        <v>0.03837375441013825</v>
       </c>
       <c r="W59">
-        <v>0.2265927225471085</v>
+        <v>0.2267514687100894</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.195234890858598</v>
+        <v>0.1918687720506912</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2161815581924033</v>
+        <v>0.2180815581924033</v>
       </c>
       <c r="C60">
-        <v>-3.373888686534061</v>
+        <v>-3.631475119091499</v>
       </c>
       <c r="D60">
-        <v>7.035111313465939</v>
+        <v>6.9575248809085</v>
       </c>
       <c r="E60">
-        <v>-3.26</v>
+        <v>-3.08</v>
       </c>
       <c r="F60">
-        <v>10.44</v>
+        <v>10.62</v>
       </c>
       <c r="G60">
         <v>0.031</v>
@@ -6156,37 +6156,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M60">
-        <v>2.461752</v>
+        <v>2.504196</v>
       </c>
       <c r="N60">
-        <v>-1.989418666666667</v>
+        <v>-2.031862666666667</v>
       </c>
       <c r="O60">
-        <v>-0.3978837333333334</v>
+        <v>-0.4063725333333333</v>
       </c>
       <c r="P60">
-        <v>-1.591534933333334</v>
+        <v>-1.625490133333333</v>
       </c>
       <c r="Q60">
-        <v>-1.585534933333334</v>
+        <v>-1.619490133333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2015850150965511</v>
+        <v>0.2053846496111012</v>
       </c>
       <c r="T60">
-        <v>2.409944637971806</v>
+        <v>2.468723775483314</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03837375441013825</v>
+        <v>0.03772335179301727</v>
       </c>
       <c r="W60">
-        <v>0.2267514687100894</v>
+        <v>0.2269048336472065</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1918687720506912</v>
+        <v>0.1886167589650863</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2180815581924033</v>
+        <v>0.2199815581924033</v>
       </c>
       <c r="C61">
-        <v>-3.631475119091499</v>
+        <v>-3.887368901481045</v>
       </c>
       <c r="D61">
-        <v>6.9575248809085</v>
+        <v>6.881631098518954</v>
       </c>
       <c r="E61">
-        <v>-3.08</v>
+        <v>-2.9</v>
       </c>
       <c r="F61">
-        <v>10.62</v>
+        <v>10.8</v>
       </c>
       <c r="G61">
         <v>0.031</v>
@@ -6238,37 +6238,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M61">
-        <v>2.504196</v>
+        <v>2.54664</v>
       </c>
       <c r="N61">
-        <v>-2.031862666666667</v>
+        <v>-2.074306666666667</v>
       </c>
       <c r="O61">
-        <v>-0.4063725333333333</v>
+        <v>-0.4148613333333334</v>
       </c>
       <c r="P61">
-        <v>-1.625490133333333</v>
+        <v>-1.659445333333333</v>
       </c>
       <c r="Q61">
-        <v>-1.619490133333333</v>
+        <v>-1.653445333333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2053846496111012</v>
+        <v>0.2093742658513787</v>
       </c>
       <c r="T61">
-        <v>2.468723775483314</v>
+        <v>2.530441869870396</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03772335179301727</v>
+        <v>0.03709462926313364</v>
       </c>
       <c r="W61">
-        <v>0.2269048336472065</v>
+        <v>0.2270530864197531</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1886167589650863</v>
+        <v>0.1854731463156682</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2199815581924033</v>
+        <v>0.2218815581924033</v>
       </c>
       <c r="C62">
-        <v>-3.887368901481045</v>
+        <v>-4.141624827095352</v>
       </c>
       <c r="D62">
-        <v>6.881631098518954</v>
+        <v>6.807375172904648</v>
       </c>
       <c r="E62">
-        <v>-2.9</v>
+        <v>-2.719999999999999</v>
       </c>
       <c r="F62">
-        <v>10.8</v>
+        <v>10.98</v>
       </c>
       <c r="G62">
         <v>0.031</v>
@@ -6320,37 +6320,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M62">
-        <v>2.54664</v>
+        <v>2.589084</v>
       </c>
       <c r="N62">
-        <v>-2.074306666666667</v>
+        <v>-2.116750666666667</v>
       </c>
       <c r="O62">
-        <v>-0.4148613333333334</v>
+        <v>-0.4233501333333334</v>
       </c>
       <c r="P62">
-        <v>-1.659445333333333</v>
+        <v>-1.693400533333334</v>
       </c>
       <c r="Q62">
-        <v>-1.653445333333333</v>
+        <v>-1.687400533333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2093742658513787</v>
+        <v>0.2135684777962858</v>
       </c>
       <c r="T62">
-        <v>2.530441869870396</v>
+        <v>2.595324994738868</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03709462926313364</v>
+        <v>0.03648652058668883</v>
       </c>
       <c r="W62">
-        <v>0.2270530864197531</v>
+        <v>0.2271964784456588</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1854731463156682</v>
+        <v>0.1824326029334441</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2218815581924033</v>
+        <v>0.2237815581924034</v>
       </c>
       <c r="C63">
-        <v>-4.141624827095352</v>
+        <v>-4.39429534959149</v>
       </c>
       <c r="D63">
-        <v>6.807375172904648</v>
+        <v>6.73470465040851</v>
       </c>
       <c r="E63">
-        <v>-2.719999999999999</v>
+        <v>-2.539999999999999</v>
       </c>
       <c r="F63">
-        <v>10.98</v>
+        <v>11.16</v>
       </c>
       <c r="G63">
         <v>0.031</v>
@@ -6402,37 +6402,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M63">
-        <v>2.589084</v>
+        <v>2.631528</v>
       </c>
       <c r="N63">
-        <v>-2.116750666666667</v>
+        <v>-2.159194666666667</v>
       </c>
       <c r="O63">
-        <v>-0.4233501333333334</v>
+        <v>-0.4318389333333335</v>
       </c>
       <c r="P63">
-        <v>-1.693400533333334</v>
+        <v>-1.727355733333334</v>
       </c>
       <c r="Q63">
-        <v>-1.687400533333334</v>
+        <v>-1.721355733333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2135684777962858</v>
+        <v>0.2179834377382933</v>
       </c>
       <c r="T63">
-        <v>2.595324994738868</v>
+        <v>2.663623020916207</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03648652058668883</v>
+        <v>0.03589802831916159</v>
       </c>
       <c r="W63">
-        <v>0.2271964784456588</v>
+        <v>0.2273352449223417</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1824326029334441</v>
+        <v>0.1794901415958079</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2237815581924034</v>
+        <v>0.2256815581924033</v>
       </c>
       <c r="C64">
-        <v>-4.39429534959149</v>
+        <v>-4.645430706458308</v>
       </c>
       <c r="D64">
-        <v>6.73470465040851</v>
+        <v>6.663569293541692</v>
       </c>
       <c r="E64">
-        <v>-2.539999999999999</v>
+        <v>-2.359999999999999</v>
       </c>
       <c r="F64">
-        <v>11.16</v>
+        <v>11.34</v>
       </c>
       <c r="G64">
         <v>0.031</v>
@@ -6484,37 +6484,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M64">
-        <v>2.631528</v>
+        <v>2.673972</v>
       </c>
       <c r="N64">
-        <v>-2.159194666666667</v>
+        <v>-2.201638666666667</v>
       </c>
       <c r="O64">
-        <v>-0.4318389333333335</v>
+        <v>-0.4403277333333334</v>
       </c>
       <c r="P64">
-        <v>-1.727355733333334</v>
+        <v>-1.761310933333333</v>
       </c>
       <c r="Q64">
-        <v>-1.721355733333334</v>
+        <v>-1.755310933333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2179834377382933</v>
+        <v>0.2226370441636526</v>
       </c>
       <c r="T64">
-        <v>2.663623020916207</v>
+        <v>2.735612832292321</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03589802831916159</v>
+        <v>0.03532821834584157</v>
       </c>
       <c r="W64">
-        <v>0.2273352449223417</v>
+        <v>0.2274696061140506</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1794901415958079</v>
+        <v>0.1766410917292078</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2256815581924033</v>
+        <v>0.2275815581924033</v>
       </c>
       <c r="C65">
-        <v>-4.645430706458308</v>
+        <v>-4.895079034834549</v>
       </c>
       <c r="D65">
-        <v>6.663569293541692</v>
+        <v>6.59392096516545</v>
       </c>
       <c r="E65">
-        <v>-2.359999999999999</v>
+        <v>-2.18</v>
       </c>
       <c r="F65">
-        <v>11.34</v>
+        <v>11.52</v>
       </c>
       <c r="G65">
         <v>0.031</v>
@@ -6566,37 +6566,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M65">
-        <v>2.673972</v>
+        <v>2.716416</v>
       </c>
       <c r="N65">
-        <v>-2.201638666666667</v>
+        <v>-2.244082666666667</v>
       </c>
       <c r="O65">
-        <v>-0.4403277333333334</v>
+        <v>-0.4488165333333334</v>
       </c>
       <c r="P65">
-        <v>-1.761310933333333</v>
+        <v>-1.795266133333334</v>
       </c>
       <c r="Q65">
-        <v>-1.755310933333333</v>
+        <v>-1.789266133333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2226370441636526</v>
+        <v>0.2275491842793097</v>
       </c>
       <c r="T65">
-        <v>2.735612832292321</v>
+        <v>2.811602077633774</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03532821834584157</v>
+        <v>0.03477621493418779</v>
       </c>
       <c r="W65">
-        <v>0.2274696061140506</v>
+        <v>0.2275997685185185</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1766410917292078</v>
+        <v>0.1738810746709389</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2275815581924033</v>
+        <v>0.2294815581924033</v>
       </c>
       <c r="C66">
-        <v>-4.895079034834549</v>
+        <v>-5.143286480138837</v>
       </c>
       <c r="D66">
-        <v>6.59392096516545</v>
+        <v>6.525713519861164</v>
       </c>
       <c r="E66">
-        <v>-2.18</v>
+        <v>-1.999999999999998</v>
       </c>
       <c r="F66">
-        <v>11.52</v>
+        <v>11.7</v>
       </c>
       <c r="G66">
         <v>0.031</v>
@@ -6648,37 +6648,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M66">
-        <v>2.716416</v>
+        <v>2.75886</v>
       </c>
       <c r="N66">
-        <v>-2.244082666666667</v>
+        <v>-2.286526666666667</v>
       </c>
       <c r="O66">
-        <v>-0.4488165333333334</v>
+        <v>-0.4573053333333335</v>
       </c>
       <c r="P66">
-        <v>-1.795266133333334</v>
+        <v>-1.829221333333334</v>
       </c>
       <c r="Q66">
-        <v>-1.789266133333334</v>
+        <v>-1.823221333333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2275491842793097</v>
+        <v>0.2327420181158614</v>
       </c>
       <c r="T66">
-        <v>2.811602077633774</v>
+        <v>2.891933565566168</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03477621493418779</v>
+        <v>0.03424119624289259</v>
       </c>
       <c r="W66">
-        <v>0.2275997685185185</v>
+        <v>0.2277259259259259</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1738810746709389</v>
+        <v>0.171205981214463</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2294815581924033</v>
+        <v>0.2313815581924034</v>
       </c>
       <c r="C67">
-        <v>-5.143286480138837</v>
+        <v>-5.390097298026688</v>
       </c>
       <c r="D67">
-        <v>6.525713519861164</v>
+        <v>6.458902701973313</v>
       </c>
       <c r="E67">
-        <v>-1.999999999999998</v>
+        <v>-1.819999999999999</v>
       </c>
       <c r="F67">
-        <v>11.7</v>
+        <v>11.88</v>
       </c>
       <c r="G67">
         <v>0.031</v>
@@ -6730,37 +6730,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M67">
-        <v>2.75886</v>
+        <v>2.801304</v>
       </c>
       <c r="N67">
-        <v>-2.286526666666667</v>
+        <v>-2.328970666666667</v>
       </c>
       <c r="O67">
-        <v>-0.4573053333333335</v>
+        <v>-0.4657941333333335</v>
       </c>
       <c r="P67">
-        <v>-1.829221333333334</v>
+        <v>-1.863176533333334</v>
       </c>
       <c r="Q67">
-        <v>-1.823221333333334</v>
+        <v>-1.857176533333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2327420181158614</v>
+        <v>0.2382403127663279</v>
       </c>
       <c r="T67">
-        <v>2.891933565566168</v>
+        <v>2.976990435141644</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03424119624289259</v>
+        <v>0.0337223902392124</v>
       </c>
       <c r="W67">
-        <v>0.2277259259259259</v>
+        <v>0.2278482603815937</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.171205981214463</v>
+        <v>0.168611951196062</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2313815581924034</v>
+        <v>0.2332815581924034</v>
       </c>
       <c r="C68">
-        <v>-5.390097298026688</v>
+        <v>-5.635553950147934</v>
       </c>
       <c r="D68">
-        <v>6.458902701973313</v>
+        <v>6.393446049852066</v>
       </c>
       <c r="E68">
-        <v>-1.819999999999999</v>
+        <v>-1.639999999999999</v>
       </c>
       <c r="F68">
-        <v>11.88</v>
+        <v>12.06</v>
       </c>
       <c r="G68">
         <v>0.031</v>
@@ -6812,37 +6812,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M68">
-        <v>2.801304</v>
+        <v>2.843748</v>
       </c>
       <c r="N68">
-        <v>-2.328970666666667</v>
+        <v>-2.371414666666667</v>
       </c>
       <c r="O68">
-        <v>-0.4657941333333335</v>
+        <v>-0.4742829333333334</v>
       </c>
       <c r="P68">
-        <v>-1.863176533333334</v>
+        <v>-1.897131733333334</v>
       </c>
       <c r="Q68">
-        <v>-1.857176533333334</v>
+        <v>-1.891131733333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2382403127663279</v>
+        <v>0.2440718373956106</v>
       </c>
       <c r="T68">
-        <v>2.976990435141644</v>
+        <v>3.067202266509572</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0337223902392124</v>
+        <v>0.03321907098191073</v>
       </c>
       <c r="W68">
-        <v>0.2278482603815937</v>
+        <v>0.2279669430624655</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.168611951196062</v>
+        <v>0.1660953549095536</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2332815581924034</v>
+        <v>0.2351815581924033</v>
       </c>
       <c r="C69">
-        <v>-5.635553950147934</v>
+        <v>-5.879697194139923</v>
       </c>
       <c r="D69">
-        <v>6.393446049852066</v>
+        <v>6.329302805860078</v>
       </c>
       <c r="E69">
-        <v>-1.639999999999999</v>
+        <v>-1.459999999999999</v>
       </c>
       <c r="F69">
-        <v>12.06</v>
+        <v>12.24</v>
       </c>
       <c r="G69">
         <v>0.031</v>
@@ -6894,37 +6894,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M69">
-        <v>2.843748</v>
+        <v>2.886192</v>
       </c>
       <c r="N69">
-        <v>-2.371414666666667</v>
+        <v>-2.413858666666667</v>
       </c>
       <c r="O69">
-        <v>-0.4742829333333334</v>
+        <v>-0.4827717333333335</v>
       </c>
       <c r="P69">
-        <v>-1.897131733333334</v>
+        <v>-1.931086933333334</v>
       </c>
       <c r="Q69">
-        <v>-1.891131733333334</v>
+        <v>-1.925086933333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2440718373956106</v>
+        <v>0.2502678323142234</v>
       </c>
       <c r="T69">
-        <v>3.067202266509572</v>
+        <v>3.163052337337997</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03321907098191073</v>
+        <v>0.03273055523217674</v>
       </c>
       <c r="W69">
-        <v>0.2279669430624655</v>
+        <v>0.2280821350762527</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1660953549095536</v>
+        <v>0.1636527761608837</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2351815581924033</v>
+        <v>0.2370815581924033</v>
       </c>
       <c r="C70">
-        <v>-5.879697194139923</v>
+        <v>-6.122566168257326</v>
       </c>
       <c r="D70">
-        <v>6.329302805860078</v>
+        <v>6.266433831742676</v>
       </c>
       <c r="E70">
-        <v>-1.459999999999999</v>
+        <v>-1.279999999999998</v>
       </c>
       <c r="F70">
-        <v>12.24</v>
+        <v>12.42</v>
       </c>
       <c r="G70">
         <v>0.031</v>
@@ -6976,37 +6976,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M70">
-        <v>2.886192</v>
+        <v>2.928636</v>
       </c>
       <c r="N70">
-        <v>-2.413858666666667</v>
+        <v>-2.456302666666667</v>
       </c>
       <c r="O70">
-        <v>-0.4827717333333335</v>
+        <v>-0.4912605333333335</v>
       </c>
       <c r="P70">
-        <v>-1.931086933333334</v>
+        <v>-1.965042133333334</v>
       </c>
       <c r="Q70">
-        <v>-1.925086933333334</v>
+        <v>-1.959042133333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2502678323142234</v>
+        <v>0.2568635688404887</v>
       </c>
       <c r="T70">
-        <v>3.163052337337997</v>
+        <v>3.265086283703738</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03273055523217674</v>
+        <v>0.03225619935924664</v>
       </c>
       <c r="W70">
-        <v>0.2280821350762527</v>
+        <v>0.2281939881910897</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1636527761608837</v>
+        <v>0.1612809967962332</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2370815581924033</v>
+        <v>0.2389815581924034</v>
       </c>
       <c r="C71">
-        <v>-6.122566168257326</v>
+        <v>-6.364198471007739</v>
       </c>
       <c r="D71">
-        <v>6.266433831742676</v>
+        <v>6.204801528992262</v>
       </c>
       <c r="E71">
-        <v>-1.279999999999998</v>
+        <v>-1.099999999999998</v>
       </c>
       <c r="F71">
-        <v>12.42</v>
+        <v>12.6</v>
       </c>
       <c r="G71">
         <v>0.031</v>
@@ -7058,37 +7058,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M71">
-        <v>2.928636</v>
+        <v>2.971080000000001</v>
       </c>
       <c r="N71">
-        <v>-2.456302666666667</v>
+        <v>-2.498746666666667</v>
       </c>
       <c r="O71">
-        <v>-0.4912605333333335</v>
+        <v>-0.4997493333333335</v>
       </c>
       <c r="P71">
-        <v>-1.965042133333334</v>
+        <v>-1.998997333333334</v>
       </c>
       <c r="Q71">
-        <v>-1.959042133333334</v>
+        <v>-1.992997333333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2568635688404887</v>
+        <v>0.2638990211351716</v>
       </c>
       <c r="T71">
-        <v>3.265086283703738</v>
+        <v>3.37392249316053</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03225619935924664</v>
+        <v>0.0317953965112574</v>
       </c>
       <c r="W71">
-        <v>0.2281939881910897</v>
+        <v>0.2283026455026455</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1612809967962332</v>
+        <v>0.158976982556287</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2389815581924034</v>
+        <v>0.2408815581924034</v>
       </c>
       <c r="C72">
-        <v>-6.364198471007739</v>
+        <v>-6.604630236133677</v>
       </c>
       <c r="D72">
-        <v>6.204801528992262</v>
+        <v>6.144369763866324</v>
       </c>
       <c r="E72">
-        <v>-1.099999999999998</v>
+        <v>-0.9199999999999982</v>
       </c>
       <c r="F72">
-        <v>12.6</v>
+        <v>12.78</v>
       </c>
       <c r="G72">
         <v>0.031</v>
@@ -7140,37 +7140,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M72">
-        <v>2.971080000000001</v>
+        <v>3.013524</v>
       </c>
       <c r="N72">
-        <v>-2.498746666666667</v>
+        <v>-2.541190666666667</v>
       </c>
       <c r="O72">
-        <v>-0.4997493333333335</v>
+        <v>-0.5082381333333335</v>
       </c>
       <c r="P72">
-        <v>-1.998997333333334</v>
+        <v>-2.032952533333334</v>
       </c>
       <c r="Q72">
-        <v>-1.992997333333334</v>
+        <v>-2.026952533333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2638990211351716</v>
+        <v>0.2714196770363845</v>
       </c>
       <c r="T72">
-        <v>3.37392249316053</v>
+        <v>3.4902646480971</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0317953965112574</v>
+        <v>0.03134757402518337</v>
       </c>
       <c r="W72">
-        <v>0.2283026455026455</v>
+        <v>0.2284082420448618</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.158976982556287</v>
+        <v>0.1567378701259168</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2408815581924033</v>
+        <v>0.2427815581924034</v>
       </c>
       <c r="C73">
-        <v>-6.604630236133676</v>
+        <v>-6.84389620325504</v>
       </c>
       <c r="D73">
-        <v>6.144369763866324</v>
+        <v>6.085103796744959</v>
       </c>
       <c r="E73">
-        <v>-0.9199999999999999</v>
+        <v>-0.7400000000000002</v>
       </c>
       <c r="F73">
-        <v>12.78</v>
+        <v>12.96</v>
       </c>
       <c r="G73">
         <v>0.031</v>
@@ -7222,37 +7222,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M73">
-        <v>3.013524</v>
+        <v>3.055968</v>
       </c>
       <c r="N73">
-        <v>-2.541190666666667</v>
+        <v>-2.583634666666667</v>
       </c>
       <c r="O73">
-        <v>-0.5082381333333333</v>
+        <v>-0.5167269333333334</v>
       </c>
       <c r="P73">
-        <v>-2.032952533333333</v>
+        <v>-2.066907733333333</v>
       </c>
       <c r="Q73">
-        <v>-2.026952533333334</v>
+        <v>-2.060907733333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2714196770363844</v>
+        <v>0.2794775226448267</v>
       </c>
       <c r="T73">
-        <v>3.490264648097098</v>
+        <v>3.61491695695771</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03134757402518337</v>
+        <v>0.03091219105261137</v>
       </c>
       <c r="W73">
-        <v>0.2284082420448618</v>
+        <v>0.2285109053497943</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1567378701259168</v>
+        <v>0.1545609552630568</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2427815581924034</v>
+        <v>0.2446815581924033</v>
       </c>
       <c r="C74">
-        <v>-6.84389620325504</v>
+        <v>-7.082029784462355</v>
       </c>
       <c r="D74">
-        <v>6.085103796744959</v>
+        <v>6.026970215537646</v>
       </c>
       <c r="E74">
-        <v>-0.7400000000000002</v>
+        <v>-0.5599999999999987</v>
       </c>
       <c r="F74">
-        <v>12.96</v>
+        <v>13.14</v>
       </c>
       <c r="G74">
         <v>0.031</v>
@@ -7304,37 +7304,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M74">
-        <v>3.055968</v>
+        <v>3.098412</v>
       </c>
       <c r="N74">
-        <v>-2.583634666666667</v>
+        <v>-2.626078666666667</v>
       </c>
       <c r="O74">
-        <v>-0.5167269333333334</v>
+        <v>-0.5252157333333334</v>
       </c>
       <c r="P74">
-        <v>-2.066907733333333</v>
+        <v>-2.100862933333334</v>
       </c>
       <c r="Q74">
-        <v>-2.060907733333333</v>
+        <v>-2.094862933333334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2794775226448267</v>
+        <v>0.2881322457057462</v>
       </c>
       <c r="T74">
-        <v>3.61491695695771</v>
+        <v>3.748802770178365</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03091219105261137</v>
+        <v>0.03048873638065779</v>
       </c>
       <c r="W74">
-        <v>0.2285109053497943</v>
+        <v>0.2286107559614409</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1545609552630568</v>
+        <v>0.1524436819032889</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2446815581924033</v>
+        <v>0.2465815581924033</v>
       </c>
       <c r="C75">
-        <v>-7.082029784462355</v>
+        <v>-7.319063127128956</v>
       </c>
       <c r="D75">
-        <v>6.026970215537646</v>
+        <v>5.969936872871044</v>
       </c>
       <c r="E75">
-        <v>-0.5599999999999987</v>
+        <v>-0.379999999999999</v>
       </c>
       <c r="F75">
-        <v>13.14</v>
+        <v>13.32</v>
       </c>
       <c r="G75">
         <v>0.031</v>
@@ -7386,37 +7386,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M75">
-        <v>3.098412</v>
+        <v>3.140856</v>
       </c>
       <c r="N75">
-        <v>-2.626078666666667</v>
+        <v>-2.668522666666667</v>
       </c>
       <c r="O75">
-        <v>-0.5252157333333334</v>
+        <v>-0.5337045333333335</v>
       </c>
       <c r="P75">
-        <v>-2.100862933333334</v>
+        <v>-2.134818133333334</v>
       </c>
       <c r="Q75">
-        <v>-2.094862933333334</v>
+        <v>-2.128818133333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2881322457057462</v>
+        <v>0.2974527166944287</v>
       </c>
       <c r="T75">
-        <v>3.748802770178365</v>
+        <v>3.892987492108302</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03048873638065779</v>
+        <v>0.03007672642956782</v>
       </c>
       <c r="W75">
-        <v>0.2286107559614409</v>
+        <v>0.2287079079079079</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1524436819032889</v>
+        <v>0.1503836321478391</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2465815581924033</v>
+        <v>0.2484815581924033</v>
       </c>
       <c r="C76">
-        <v>-7.319063127128956</v>
+        <v>-7.555027173190253</v>
       </c>
       <c r="D76">
-        <v>5.969936872871044</v>
+        <v>5.913972826809747</v>
       </c>
       <c r="E76">
-        <v>-0.379999999999999</v>
+        <v>-0.1999999999999993</v>
       </c>
       <c r="F76">
-        <v>13.32</v>
+        <v>13.5</v>
       </c>
       <c r="G76">
         <v>0.031</v>
@@ -7468,37 +7468,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M76">
-        <v>3.140856</v>
+        <v>3.1833</v>
       </c>
       <c r="N76">
-        <v>-2.668522666666667</v>
+        <v>-2.710966666666667</v>
       </c>
       <c r="O76">
-        <v>-0.5337045333333335</v>
+        <v>-0.5421933333333334</v>
       </c>
       <c r="P76">
-        <v>-2.134818133333334</v>
+        <v>-2.168773333333333</v>
       </c>
       <c r="Q76">
-        <v>-2.128818133333334</v>
+        <v>-2.162773333333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2974527166944287</v>
+        <v>0.3075188253622059</v>
       </c>
       <c r="T76">
-        <v>3.892987492108302</v>
+        <v>4.048706991792635</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03007672642956782</v>
+        <v>0.02967570341050692</v>
       </c>
       <c r="W76">
-        <v>0.2287079079079079</v>
+        <v>0.2288024691358025</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1503836321478391</v>
+        <v>0.1483785170525346</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2484815581924033</v>
+        <v>0.2503815581924033</v>
       </c>
       <c r="C77">
-        <v>-7.555027173190253</v>
+        <v>-7.789951715119739</v>
       </c>
       <c r="D77">
-        <v>5.913972826809747</v>
+        <v>5.859048284880261</v>
       </c>
       <c r="E77">
-        <v>-0.1999999999999993</v>
+        <v>-0.01999999999999957</v>
       </c>
       <c r="F77">
-        <v>13.5</v>
+        <v>13.68</v>
       </c>
       <c r="G77">
         <v>0.031</v>
@@ -7550,37 +7550,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M77">
-        <v>3.1833</v>
+        <v>3.225744</v>
       </c>
       <c r="N77">
-        <v>-2.710966666666667</v>
+        <v>-2.753410666666667</v>
       </c>
       <c r="O77">
-        <v>-0.5421933333333334</v>
+        <v>-0.5506821333333334</v>
       </c>
       <c r="P77">
-        <v>-2.168773333333333</v>
+        <v>-2.202728533333334</v>
       </c>
       <c r="Q77">
-        <v>-2.162773333333333</v>
+        <v>-2.196728533333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3075188253622059</v>
+        <v>0.3184237764189645</v>
       </c>
       <c r="T77">
-        <v>4.048706991792635</v>
+        <v>4.217403116450661</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02967570341050692</v>
+        <v>0.02928523362878972</v>
       </c>
       <c r="W77">
-        <v>0.2288024691358025</v>
+        <v>0.2288945419103314</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1483785170525346</v>
+        <v>0.1464261681439486</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2503815581924033</v>
+        <v>0.2522815581924033</v>
       </c>
       <c r="C78">
-        <v>-7.789951715119739</v>
+        <v>-8.02386544881454</v>
       </c>
       <c r="D78">
-        <v>5.859048284880261</v>
+        <v>5.80513455118546</v>
       </c>
       <c r="E78">
-        <v>-0.01999999999999957</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="F78">
-        <v>13.68</v>
+        <v>13.86</v>
       </c>
       <c r="G78">
         <v>0.031</v>
@@ -7632,37 +7632,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M78">
-        <v>3.225744</v>
+        <v>3.268188</v>
       </c>
       <c r="N78">
-        <v>-2.753410666666667</v>
+        <v>-2.795854666666667</v>
       </c>
       <c r="O78">
-        <v>-0.5506821333333334</v>
+        <v>-0.5591709333333333</v>
       </c>
       <c r="P78">
-        <v>-2.202728533333334</v>
+        <v>-2.236683733333333</v>
       </c>
       <c r="Q78">
-        <v>-2.196728533333334</v>
+        <v>-2.230683733333334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3184237764189645</v>
+        <v>0.3302769840893543</v>
       </c>
       <c r="T78">
-        <v>4.217403116450661</v>
+        <v>4.400768469339821</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02928523362878972</v>
+        <v>0.02890490591932492</v>
       </c>
       <c r="W78">
-        <v>0.2288945419103314</v>
+        <v>0.2289842231842232</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1464261681439486</v>
+        <v>0.1445245295966245</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2522815581924033</v>
+        <v>0.2541815581924033</v>
       </c>
       <c r="C79">
-        <v>-8.02386544881454</v>
+        <v>-8.256796023587709</v>
       </c>
       <c r="D79">
-        <v>5.80513455118546</v>
+        <v>5.752203976412292</v>
       </c>
       <c r="E79">
-        <v>0.1600000000000001</v>
+        <v>0.3400000000000016</v>
       </c>
       <c r="F79">
-        <v>13.86</v>
+        <v>14.04</v>
       </c>
       <c r="G79">
         <v>0.031</v>
@@ -7714,37 +7714,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M79">
-        <v>3.268188</v>
+        <v>3.310632</v>
       </c>
       <c r="N79">
-        <v>-2.795854666666667</v>
+        <v>-2.838298666666667</v>
       </c>
       <c r="O79">
-        <v>-0.5591709333333333</v>
+        <v>-0.5676597333333334</v>
       </c>
       <c r="P79">
-        <v>-2.236683733333333</v>
+        <v>-2.270638933333334</v>
       </c>
       <c r="Q79">
-        <v>-2.230683733333334</v>
+        <v>-2.264638933333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3302769840893543</v>
+        <v>0.3432077560934159</v>
       </c>
       <c r="T79">
-        <v>4.400768469339821</v>
+        <v>4.600803399764358</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02890490591932492</v>
+        <v>0.02853433020241049</v>
       </c>
       <c r="W79">
-        <v>0.2289842231842232</v>
+        <v>0.2290716049382716</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1445245295966245</v>
+        <v>0.1426716510120525</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2541815581924033</v>
+        <v>0.2560815581924033</v>
       </c>
       <c r="C80">
-        <v>-8.256796023587709</v>
+        <v>-8.488770089450313</v>
       </c>
       <c r="D80">
-        <v>5.752203976412292</v>
+        <v>5.700229910549687</v>
       </c>
       <c r="E80">
-        <v>0.3400000000000016</v>
+        <v>0.5200000000000014</v>
       </c>
       <c r="F80">
-        <v>14.04</v>
+        <v>14.22</v>
       </c>
       <c r="G80">
         <v>0.031</v>
@@ -7796,37 +7796,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M80">
-        <v>3.310632</v>
+        <v>3.353076</v>
       </c>
       <c r="N80">
-        <v>-2.838298666666667</v>
+        <v>-2.880742666666667</v>
       </c>
       <c r="O80">
-        <v>-0.5676597333333334</v>
+        <v>-0.5761485333333334</v>
       </c>
       <c r="P80">
-        <v>-2.270638933333334</v>
+        <v>-2.304594133333334</v>
       </c>
       <c r="Q80">
-        <v>-2.264638933333334</v>
+        <v>-2.298594133333334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3432077560934159</v>
+        <v>0.3573700301931023</v>
       </c>
       <c r="T80">
-        <v>4.600803399764358</v>
+        <v>4.819889275943614</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02853433020241049</v>
+        <v>0.02817313614921543</v>
       </c>
       <c r="W80">
-        <v>0.2290716049382716</v>
+        <v>0.229156774496015</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1426716510120525</v>
+        <v>0.1408656807460771</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2560815581924033</v>
+        <v>0.2579815581924033</v>
       </c>
       <c r="C81">
-        <v>-8.488770089450313</v>
+        <v>-8.719813341853163</v>
       </c>
       <c r="D81">
-        <v>5.700229910549687</v>
+        <v>5.649186658146838</v>
       </c>
       <c r="E81">
-        <v>0.5200000000000014</v>
+        <v>0.7000000000000011</v>
       </c>
       <c r="F81">
-        <v>14.22</v>
+        <v>14.4</v>
       </c>
       <c r="G81">
         <v>0.031</v>
@@ -7878,37 +7878,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M81">
-        <v>3.353076</v>
+        <v>3.39552</v>
       </c>
       <c r="N81">
-        <v>-2.880742666666667</v>
+        <v>-2.923186666666667</v>
       </c>
       <c r="O81">
-        <v>-0.5761485333333334</v>
+        <v>-0.5846373333333335</v>
       </c>
       <c r="P81">
-        <v>-2.304594133333334</v>
+        <v>-2.338549333333334</v>
       </c>
       <c r="Q81">
-        <v>-2.298594133333334</v>
+        <v>-2.332549333333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3573700301931023</v>
+        <v>0.3729485317027575</v>
       </c>
       <c r="T81">
-        <v>4.819889275943614</v>
+        <v>5.060883739740794</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02817313614921543</v>
+        <v>0.02782097194735023</v>
       </c>
       <c r="W81">
-        <v>0.229156774496015</v>
+        <v>0.2292398148148148</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1408656807460771</v>
+        <v>0.1391048597367511</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2579815581924033</v>
+        <v>0.2598815581924034</v>
       </c>
       <c r="C82">
-        <v>-8.719813341853163</v>
+        <v>-8.949950564045992</v>
       </c>
       <c r="D82">
-        <v>5.649186658146838</v>
+        <v>5.599049435954011</v>
       </c>
       <c r="E82">
-        <v>0.7000000000000011</v>
+        <v>0.8800000000000026</v>
       </c>
       <c r="F82">
-        <v>14.4</v>
+        <v>14.58</v>
       </c>
       <c r="G82">
         <v>0.031</v>
@@ -7960,37 +7960,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M82">
-        <v>3.39552</v>
+        <v>3.437964</v>
       </c>
       <c r="N82">
-        <v>-2.923186666666667</v>
+        <v>-2.965630666666667</v>
       </c>
       <c r="O82">
-        <v>-0.5846373333333335</v>
+        <v>-0.5931261333333334</v>
       </c>
       <c r="P82">
-        <v>-2.338549333333334</v>
+        <v>-2.372504533333334</v>
       </c>
       <c r="Q82">
-        <v>-2.332549333333334</v>
+        <v>-2.366504533333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3729485317027575</v>
+        <v>0.3901668754765868</v>
       </c>
       <c r="T82">
-        <v>5.060883739740794</v>
+        <v>5.327246041832415</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02782097194735023</v>
+        <v>0.02747750315787677</v>
       </c>
       <c r="W82">
-        <v>0.2292398148148148</v>
+        <v>0.2293208047553727</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1391048597367511</v>
+        <v>0.1373875157893838</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2598815581924034</v>
+        <v>0.2617815581924033</v>
       </c>
       <c r="C83">
-        <v>-8.949950564045992</v>
+        <v>-9.179205667200844</v>
       </c>
       <c r="D83">
-        <v>5.599049435954011</v>
+        <v>5.549794332799159</v>
       </c>
       <c r="E83">
-        <v>0.8800000000000026</v>
+        <v>1.060000000000002</v>
       </c>
       <c r="F83">
-        <v>14.58</v>
+        <v>14.76</v>
       </c>
       <c r="G83">
         <v>0.031</v>
@@ -8042,37 +8042,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M83">
-        <v>3.437964</v>
+        <v>3.480408000000001</v>
       </c>
       <c r="N83">
-        <v>-2.965630666666667</v>
+        <v>-3.008074666666667</v>
       </c>
       <c r="O83">
-        <v>-0.5931261333333334</v>
+        <v>-0.6016149333333335</v>
       </c>
       <c r="P83">
-        <v>-2.372504533333334</v>
+        <v>-2.406459733333334</v>
       </c>
       <c r="Q83">
-        <v>-2.366504533333334</v>
+        <v>-2.400459733333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3901668754765868</v>
+        <v>0.4092983685586195</v>
       </c>
       <c r="T83">
-        <v>5.327246041832415</v>
+        <v>5.62320415526755</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02747750315787677</v>
+        <v>0.02714241165595144</v>
       </c>
       <c r="W83">
-        <v>0.2293208047553727</v>
+        <v>0.2293998193315267</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1373875157893838</v>
+        <v>0.1357120582797572</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2617815581924033</v>
+        <v>0.2636815581924034</v>
       </c>
       <c r="C84">
-        <v>-9.179205667200844</v>
+        <v>-9.407601728436127</v>
       </c>
       <c r="D84">
-        <v>5.549794332799159</v>
+        <v>5.501398271563875</v>
       </c>
       <c r="E84">
-        <v>1.060000000000002</v>
+        <v>1.240000000000002</v>
       </c>
       <c r="F84">
-        <v>14.76</v>
+        <v>14.94</v>
       </c>
       <c r="G84">
         <v>0.031</v>
@@ -8124,37 +8124,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M84">
-        <v>3.480408000000001</v>
+        <v>3.522852</v>
       </c>
       <c r="N84">
-        <v>-3.008074666666667</v>
+        <v>-3.050518666666667</v>
       </c>
       <c r="O84">
-        <v>-0.6016149333333335</v>
+        <v>-0.6101037333333335</v>
       </c>
       <c r="P84">
-        <v>-2.406459733333334</v>
+        <v>-2.440414933333334</v>
       </c>
       <c r="Q84">
-        <v>-2.400459733333334</v>
+        <v>-2.434414933333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4092983685586195</v>
+        <v>0.4306806255326559</v>
       </c>
       <c r="T84">
-        <v>5.62320415526755</v>
+        <v>5.953980870283289</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02714241165595144</v>
+        <v>0.02681539464804841</v>
       </c>
       <c r="W84">
-        <v>0.2293998193315267</v>
+        <v>0.2294769299419902</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1357120582797572</v>
+        <v>0.134076973240242</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2636815581924034</v>
+        <v>0.2655815581924034</v>
       </c>
       <c r="C85">
-        <v>-9.407601728436127</v>
+        <v>-9.635161026868349</v>
       </c>
       <c r="D85">
-        <v>5.501398271563875</v>
+        <v>5.453838973131653</v>
       </c>
       <c r="E85">
-        <v>1.240000000000002</v>
+        <v>1.420000000000002</v>
       </c>
       <c r="F85">
-        <v>14.94</v>
+        <v>15.12</v>
       </c>
       <c r="G85">
         <v>0.031</v>
@@ -8206,37 +8206,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M85">
-        <v>3.522852</v>
+        <v>3.565296</v>
       </c>
       <c r="N85">
-        <v>-3.050518666666667</v>
+        <v>-3.092962666666667</v>
       </c>
       <c r="O85">
-        <v>-0.6101037333333335</v>
+        <v>-0.6185925333333335</v>
       </c>
       <c r="P85">
-        <v>-2.440414933333334</v>
+        <v>-2.474370133333334</v>
       </c>
       <c r="Q85">
-        <v>-2.434414933333334</v>
+        <v>-2.468370133333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4306806255326559</v>
+        <v>0.454735664628447</v>
       </c>
       <c r="T85">
-        <v>5.953980870283289</v>
+        <v>6.326104674675996</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02681539464804841</v>
+        <v>0.02649616375938117</v>
       </c>
       <c r="W85">
-        <v>0.2294769299419902</v>
+        <v>0.2295522045855379</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.134076973240242</v>
+        <v>0.1324808187969059</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2655815581924034</v>
+        <v>0.2674815581924033</v>
       </c>
       <c r="C86">
-        <v>-9.635161026868346</v>
+        <v>-9.861905077809904</v>
       </c>
       <c r="D86">
-        <v>5.453838973131653</v>
+        <v>5.407094922190094</v>
       </c>
       <c r="E86">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="F86">
-        <v>15.12</v>
+        <v>15.3</v>
       </c>
       <c r="G86">
         <v>0.031</v>
@@ -8288,37 +8288,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M86">
-        <v>3.565296</v>
+        <v>3.60774</v>
       </c>
       <c r="N86">
-        <v>-3.092962666666667</v>
+        <v>-3.135406666666666</v>
       </c>
       <c r="O86">
-        <v>-0.6185925333333334</v>
+        <v>-0.6270813333333334</v>
       </c>
       <c r="P86">
-        <v>-2.474370133333333</v>
+        <v>-2.508325333333333</v>
       </c>
       <c r="Q86">
-        <v>-2.468370133333333</v>
+        <v>-2.502325333333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4547356646284467</v>
+        <v>0.4819980422703432</v>
       </c>
       <c r="T86">
-        <v>6.326104674675991</v>
+        <v>6.747844986321057</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02649616375938118</v>
+        <v>0.0261844441857414</v>
       </c>
       <c r="W86">
-        <v>0.2295522045855379</v>
+        <v>0.2296257080610022</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1324808187969059</v>
+        <v>0.130922220928707</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2674815581924033</v>
+        <v>0.2693815581924034</v>
       </c>
       <c r="C87">
-        <v>-9.861905077809904</v>
+        <v>-10.0878546652232</v>
       </c>
       <c r="D87">
-        <v>5.407094922190094</v>
+        <v>5.361145334776804</v>
       </c>
       <c r="E87">
-        <v>1.6</v>
+        <v>1.780000000000001</v>
       </c>
       <c r="F87">
-        <v>15.3</v>
+        <v>15.48</v>
       </c>
       <c r="G87">
         <v>0.031</v>
@@ -8370,37 +8370,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M87">
-        <v>3.60774</v>
+        <v>3.650184</v>
       </c>
       <c r="N87">
-        <v>-3.135406666666666</v>
+        <v>-3.177850666666667</v>
       </c>
       <c r="O87">
-        <v>-0.6270813333333334</v>
+        <v>-0.6355701333333335</v>
       </c>
       <c r="P87">
-        <v>-2.508325333333333</v>
+        <v>-2.542280533333334</v>
       </c>
       <c r="Q87">
-        <v>-2.502325333333333</v>
+        <v>-2.536280533333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4819980422703432</v>
+        <v>0.5131550452896534</v>
       </c>
       <c r="T87">
-        <v>6.747844986321057</v>
+        <v>7.229833913915419</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0261844441857414</v>
+        <v>0.02587997390451184</v>
       </c>
       <c r="W87">
-        <v>0.2296257080610022</v>
+        <v>0.2296975021533161</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.130922220928707</v>
+        <v>0.1293998695225592</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2693815581924034</v>
+        <v>0.2712815581924033</v>
       </c>
       <c r="C88">
-        <v>-10.0878546652232</v>
+        <v>-10.31302987253387</v>
       </c>
       <c r="D88">
-        <v>5.361145334776804</v>
+        <v>5.315970127466128</v>
       </c>
       <c r="E88">
-        <v>1.780000000000001</v>
+        <v>1.960000000000001</v>
       </c>
       <c r="F88">
-        <v>15.48</v>
+        <v>15.66</v>
       </c>
       <c r="G88">
         <v>0.031</v>
@@ -8452,37 +8452,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M88">
-        <v>3.650184</v>
+        <v>3.692628</v>
       </c>
       <c r="N88">
-        <v>-3.177850666666667</v>
+        <v>-3.220294666666667</v>
       </c>
       <c r="O88">
-        <v>-0.6355701333333335</v>
+        <v>-0.6440589333333334</v>
       </c>
       <c r="P88">
-        <v>-2.542280533333334</v>
+        <v>-2.576235733333333</v>
       </c>
       <c r="Q88">
-        <v>-2.536280533333334</v>
+        <v>-2.570235733333333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5131550452896534</v>
+        <v>0.5491054333888574</v>
       </c>
       <c r="T88">
-        <v>7.229833913915419</v>
+        <v>7.785974984216605</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02587997390451184</v>
+        <v>0.02558250294009217</v>
       </c>
       <c r="W88">
-        <v>0.2296975021533161</v>
+        <v>0.2297676458067263</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1293998695225592</v>
+        <v>0.1279125147004608</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2712815581924033</v>
+        <v>0.2731815581924034</v>
       </c>
       <c r="C89">
-        <v>-10.31302987253387</v>
+        <v>-10.53745011189928</v>
       </c>
       <c r="D89">
-        <v>5.315970127466128</v>
+        <v>5.271549888100722</v>
       </c>
       <c r="E89">
-        <v>1.960000000000001</v>
+        <v>2.140000000000001</v>
       </c>
       <c r="F89">
-        <v>15.66</v>
+        <v>15.84</v>
       </c>
       <c r="G89">
         <v>0.031</v>
@@ -8534,37 +8534,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M89">
-        <v>3.692628</v>
+        <v>3.735072</v>
       </c>
       <c r="N89">
-        <v>-3.220294666666667</v>
+        <v>-3.262738666666667</v>
       </c>
       <c r="O89">
-        <v>-0.6440589333333334</v>
+        <v>-0.6525477333333334</v>
       </c>
       <c r="P89">
-        <v>-2.576235733333333</v>
+        <v>-2.610190933333334</v>
       </c>
       <c r="Q89">
-        <v>-2.570235733333333</v>
+        <v>-2.604190933333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5491054333888574</v>
+        <v>0.5910475528379291</v>
       </c>
       <c r="T89">
-        <v>7.785974984216605</v>
+        <v>8.434806232901325</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02558250294009217</v>
+        <v>0.0252917926794093</v>
       </c>
       <c r="W89">
-        <v>0.2297676458067263</v>
+        <v>0.2298361952861953</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1279125147004608</v>
+        <v>0.1264589633970465</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2731815581924034</v>
+        <v>0.2750815581924033</v>
       </c>
       <c r="C90">
-        <v>-10.53745011189928</v>
+        <v>-10.76113415202163</v>
       </c>
       <c r="D90">
-        <v>5.271549888100722</v>
+        <v>5.227865847978375</v>
       </c>
       <c r="E90">
-        <v>2.140000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="F90">
-        <v>15.84</v>
+        <v>16.02</v>
       </c>
       <c r="G90">
         <v>0.031</v>
@@ -8616,37 +8616,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M90">
-        <v>3.735072</v>
+        <v>3.777516</v>
       </c>
       <c r="N90">
-        <v>-3.262738666666667</v>
+        <v>-3.305182666666667</v>
       </c>
       <c r="O90">
-        <v>-0.6525477333333334</v>
+        <v>-0.6610365333333333</v>
       </c>
       <c r="P90">
-        <v>-2.610190933333334</v>
+        <v>-2.644146133333333</v>
       </c>
       <c r="Q90">
-        <v>-2.604190933333334</v>
+        <v>-2.638146133333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5910475528379291</v>
+        <v>0.6406155121868317</v>
       </c>
       <c r="T90">
-        <v>8.434806232901325</v>
+        <v>9.201606799528717</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0252917926794093</v>
+        <v>0.02500761523357324</v>
       </c>
       <c r="W90">
-        <v>0.2298361952861953</v>
+        <v>0.2299032043279234</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1264589633970465</v>
+        <v>0.1250380761678662</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2750815581924033</v>
+        <v>0.2769815581924033</v>
       </c>
       <c r="C91">
-        <v>-10.76113415202163</v>
+        <v>-10.98410014458965</v>
       </c>
       <c r="D91">
-        <v>5.227865847978375</v>
+        <v>5.184899855410352</v>
       </c>
       <c r="E91">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="F91">
-        <v>16.02</v>
+        <v>16.2</v>
       </c>
       <c r="G91">
         <v>0.031</v>
@@ -8698,37 +8698,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M91">
-        <v>3.777516</v>
+        <v>3.81996</v>
       </c>
       <c r="N91">
-        <v>-3.305182666666667</v>
+        <v>-3.347626666666667</v>
       </c>
       <c r="O91">
-        <v>-0.6610365333333333</v>
+        <v>-0.6695253333333334</v>
       </c>
       <c r="P91">
-        <v>-2.644146133333333</v>
+        <v>-2.678101333333333</v>
       </c>
       <c r="Q91">
-        <v>-2.638146133333334</v>
+        <v>-2.672101333333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6406155121868317</v>
+        <v>0.7000970634055148</v>
       </c>
       <c r="T91">
-        <v>9.201606799528717</v>
+        <v>10.12176747948159</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02500761523357324</v>
+        <v>0.0247297528420891</v>
       </c>
       <c r="W91">
-        <v>0.2299032043279234</v>
+        <v>0.2299687242798354</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1250380761678662</v>
+        <v>0.1236487642104455</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2769815581924033</v>
+        <v>0.2788815581924033</v>
       </c>
       <c r="C92">
-        <v>-10.98410014458965</v>
+        <v>-11.206365649427</v>
       </c>
       <c r="D92">
-        <v>5.184899855410352</v>
+        <v>5.142634350572995</v>
       </c>
       <c r="E92">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="F92">
-        <v>16.2</v>
+        <v>16.38</v>
       </c>
       <c r="G92">
         <v>0.031</v>
@@ -8780,37 +8780,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M92">
-        <v>3.81996</v>
+        <v>3.862404</v>
       </c>
       <c r="N92">
-        <v>-3.347626666666667</v>
+        <v>-3.390070666666666</v>
       </c>
       <c r="O92">
-        <v>-0.6695253333333334</v>
+        <v>-0.6780141333333334</v>
       </c>
       <c r="P92">
-        <v>-2.678101333333333</v>
+        <v>-2.712056533333333</v>
       </c>
       <c r="Q92">
-        <v>-2.672101333333333</v>
+        <v>-2.706056533333333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7000970634055148</v>
+        <v>0.7727967371172388</v>
       </c>
       <c r="T92">
-        <v>10.12176747948159</v>
+        <v>11.2464083105351</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0247297528420891</v>
+        <v>0.02445799731635186</v>
       </c>
       <c r="W92">
-        <v>0.2299687242798354</v>
+        <v>0.2300328042328042</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1236487642104455</v>
+        <v>0.1222899865817593</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2788815581924033</v>
+        <v>0.2807815581924034</v>
       </c>
       <c r="C93">
-        <v>-11.206365649427</v>
+        <v>-11.42794765842062</v>
       </c>
       <c r="D93">
-        <v>5.142634350572995</v>
+        <v>5.101052341579385</v>
       </c>
       <c r="E93">
-        <v>2.68</v>
+        <v>2.860000000000003</v>
       </c>
       <c r="F93">
-        <v>16.38</v>
+        <v>16.56</v>
       </c>
       <c r="G93">
         <v>0.031</v>
@@ -8862,37 +8862,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M93">
-        <v>3.862404</v>
+        <v>3.904848000000001</v>
       </c>
       <c r="N93">
-        <v>-3.390070666666666</v>
+        <v>-3.432514666666667</v>
       </c>
       <c r="O93">
-        <v>-0.6780141333333334</v>
+        <v>-0.6865029333333336</v>
       </c>
       <c r="P93">
-        <v>-2.712056533333333</v>
+        <v>-2.746011733333334</v>
       </c>
       <c r="Q93">
-        <v>-2.706056533333333</v>
+        <v>-2.740011733333334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7727967371172388</v>
+        <v>0.8636713292568939</v>
       </c>
       <c r="T93">
-        <v>11.2464083105351</v>
+        <v>12.65220934935199</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02445799731635186</v>
+        <v>0.02419214951943498</v>
       </c>
       <c r="W93">
-        <v>0.2300328042328042</v>
+        <v>0.2300954911433173</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1222899865817593</v>
+        <v>0.1209607475971749</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2807815581924034</v>
+        <v>0.2826815581924034</v>
       </c>
       <c r="C94">
-        <v>-11.42794765842062</v>
+        <v>-11.64886261829744</v>
       </c>
       <c r="D94">
-        <v>5.101052341579385</v>
+        <v>5.060137381702564</v>
       </c>
       <c r="E94">
-        <v>2.860000000000003</v>
+        <v>3.040000000000003</v>
       </c>
       <c r="F94">
-        <v>16.56</v>
+        <v>16.74</v>
       </c>
       <c r="G94">
         <v>0.031</v>
@@ -8944,37 +8944,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M94">
-        <v>3.904848000000001</v>
+        <v>3.947292</v>
       </c>
       <c r="N94">
-        <v>-3.432514666666667</v>
+        <v>-3.474958666666667</v>
       </c>
       <c r="O94">
-        <v>-0.6865029333333336</v>
+        <v>-0.6949917333333335</v>
       </c>
       <c r="P94">
-        <v>-2.746011733333334</v>
+        <v>-2.779966933333334</v>
       </c>
       <c r="Q94">
-        <v>-2.740011733333334</v>
+        <v>-2.773966933333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8636713292568939</v>
+        <v>0.9805100905793075</v>
       </c>
       <c r="T94">
-        <v>12.65220934935199</v>
+        <v>14.45966782783085</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02419214951943498</v>
+        <v>0.02393201887944106</v>
       </c>
       <c r="W94">
-        <v>0.2300954911433173</v>
+        <v>0.2301568299482278</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1209607475971749</v>
+        <v>0.1196600943972053</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2826815581924034</v>
+        <v>0.2845815581924034</v>
       </c>
       <c r="C95">
-        <v>-11.64886261829744</v>
+        <v>-11.86912645231383</v>
       </c>
       <c r="D95">
-        <v>5.060137381702564</v>
+        <v>5.019873547686172</v>
       </c>
       <c r="E95">
-        <v>3.040000000000003</v>
+        <v>3.220000000000002</v>
       </c>
       <c r="F95">
-        <v>16.74</v>
+        <v>16.92</v>
       </c>
       <c r="G95">
         <v>0.031</v>
@@ -9026,37 +9026,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M95">
-        <v>3.947292</v>
+        <v>3.989736000000001</v>
       </c>
       <c r="N95">
-        <v>-3.474958666666667</v>
+        <v>-3.517402666666667</v>
       </c>
       <c r="O95">
-        <v>-0.6949917333333335</v>
+        <v>-0.7034805333333335</v>
       </c>
       <c r="P95">
-        <v>-2.779966933333334</v>
+        <v>-2.813922133333334</v>
       </c>
       <c r="Q95">
-        <v>-2.773966933333334</v>
+        <v>-2.807922133333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9805100905793075</v>
+        <v>1.136295105675859</v>
       </c>
       <c r="T95">
-        <v>14.45966782783085</v>
+        <v>16.86961246580266</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02393201887944106</v>
+        <v>0.02367742293391509</v>
       </c>
       <c r="W95">
-        <v>0.2301568299482278</v>
+        <v>0.2302168636721828</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1196600943972053</v>
+        <v>0.1183871146695754</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2845815581924034</v>
+        <v>0.2864815581924034</v>
       </c>
       <c r="C96">
-        <v>-11.86912645231383</v>
+        <v>-12.0887545809176</v>
       </c>
       <c r="D96">
-        <v>5.019873547686172</v>
+        <v>4.980245419082403</v>
       </c>
       <c r="E96">
-        <v>3.220000000000002</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="F96">
-        <v>16.92</v>
+        <v>17.1</v>
       </c>
       <c r="G96">
         <v>0.031</v>
@@ -9108,37 +9108,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M96">
-        <v>3.989736000000001</v>
+        <v>4.03218</v>
       </c>
       <c r="N96">
-        <v>-3.517402666666667</v>
+        <v>-3.559846666666667</v>
       </c>
       <c r="O96">
-        <v>-0.7034805333333335</v>
+        <v>-0.7119693333333335</v>
       </c>
       <c r="P96">
-        <v>-2.813922133333334</v>
+        <v>-2.847877333333334</v>
       </c>
       <c r="Q96">
-        <v>-2.807922133333334</v>
+        <v>-2.841877333333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.136295105675859</v>
+        <v>1.354394126811032</v>
       </c>
       <c r="T96">
-        <v>16.86961246580266</v>
+        <v>20.24353495896321</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02367742293391509</v>
+        <v>0.02342818690303178</v>
       </c>
       <c r="W96">
-        <v>0.2302168636721828</v>
+        <v>0.2302756335282651</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1183871146695754</v>
+        <v>0.1171409345151588</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2864815581924034</v>
+        <v>0.2883815581924034</v>
       </c>
       <c r="C97">
-        <v>-12.0887545809176</v>
+        <v>-12.30776194143901</v>
       </c>
       <c r="D97">
-        <v>4.980245419082403</v>
+        <v>4.941238058560992</v>
       </c>
       <c r="E97">
-        <v>3.400000000000002</v>
+        <v>3.580000000000002</v>
       </c>
       <c r="F97">
-        <v>17.1</v>
+        <v>17.28</v>
       </c>
       <c r="G97">
         <v>0.031</v>
@@ -9190,37 +9190,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M97">
-        <v>4.03218</v>
+        <v>4.074624</v>
       </c>
       <c r="N97">
-        <v>-3.559846666666667</v>
+        <v>-3.602290666666667</v>
       </c>
       <c r="O97">
-        <v>-0.7119693333333335</v>
+        <v>-0.7204581333333334</v>
       </c>
       <c r="P97">
-        <v>-2.847877333333334</v>
+        <v>-2.881832533333333</v>
       </c>
       <c r="Q97">
-        <v>-2.841877333333334</v>
+        <v>-2.875832533333333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.354394126811032</v>
+        <v>1.68154265851379</v>
       </c>
       <c r="T97">
-        <v>20.24353495896321</v>
+        <v>25.30441869870401</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02342818690303178</v>
+        <v>0.02318414328945853</v>
       </c>
       <c r="W97">
-        <v>0.2302756335282651</v>
+        <v>0.2303331790123457</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1171409345151588</v>
+        <v>0.1159207164472926</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2883815581924034</v>
+        <v>0.2902815581924034</v>
       </c>
       <c r="C98">
-        <v>-12.30776194143901</v>
+        <v>-12.52616300686365</v>
       </c>
       <c r="D98">
-        <v>4.941238058560994</v>
+        <v>4.902836993136347</v>
       </c>
       <c r="E98">
-        <v>3.580000000000002</v>
+        <v>3.760000000000002</v>
       </c>
       <c r="F98">
-        <v>17.28</v>
+        <v>17.46</v>
       </c>
       <c r="G98">
         <v>0.031</v>
@@ -9272,37 +9272,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M98">
-        <v>4.074624</v>
+        <v>4.117068000000001</v>
       </c>
       <c r="N98">
-        <v>-3.602290666666667</v>
+        <v>-3.644734666666667</v>
       </c>
       <c r="O98">
-        <v>-0.7204581333333334</v>
+        <v>-0.7289469333333335</v>
       </c>
       <c r="P98">
-        <v>-2.881832533333333</v>
+        <v>-2.915787733333334</v>
       </c>
       <c r="Q98">
-        <v>-2.875832533333333</v>
+        <v>-2.909787733333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.681542658513786</v>
+        <v>2.226790211351714</v>
       </c>
       <c r="T98">
-        <v>25.30441869870395</v>
+        <v>33.73922493160526</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02318414328945853</v>
+        <v>0.02294513150296926</v>
       </c>
       <c r="W98">
-        <v>0.2303331790123457</v>
+        <v>0.2303895379915999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1159207164472926</v>
+        <v>0.1147256575148463</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2902815581924034</v>
+        <v>0.2921815581924033</v>
       </c>
       <c r="C99">
-        <v>-12.52616300686365</v>
+        <v>-12.74397180373669</v>
       </c>
       <c r="D99">
-        <v>4.902836993136347</v>
+        <v>4.86502819626331</v>
       </c>
       <c r="E99">
-        <v>3.760000000000002</v>
+        <v>3.940000000000001</v>
       </c>
       <c r="F99">
-        <v>17.46</v>
+        <v>17.64</v>
       </c>
       <c r="G99">
         <v>0.031</v>
@@ -9354,37 +9354,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M99">
-        <v>4.117068000000001</v>
+        <v>4.159512</v>
       </c>
       <c r="N99">
-        <v>-3.644734666666667</v>
+        <v>-3.687178666666667</v>
       </c>
       <c r="O99">
-        <v>-0.7289469333333335</v>
+        <v>-0.7374357333333335</v>
       </c>
       <c r="P99">
-        <v>-2.915787733333334</v>
+        <v>-2.949742933333334</v>
       </c>
       <c r="Q99">
-        <v>-2.909787733333334</v>
+        <v>-2.943742933333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.226790211351714</v>
+        <v>3.31728531702757</v>
       </c>
       <c r="T99">
-        <v>33.73922493160526</v>
+        <v>50.60883739740788</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02294513150296926</v>
+        <v>0.02271099750804101</v>
       </c>
       <c r="W99">
-        <v>0.2303895379915999</v>
+        <v>0.2304447467876039</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1147256575148463</v>
+        <v>0.113554987540205</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2921815581924033</v>
+        <v>0.2940815581924033</v>
       </c>
       <c r="C100">
-        <v>-12.74397180373669</v>
+        <v>-12.96120192924499</v>
       </c>
       <c r="D100">
-        <v>4.86502819626331</v>
+        <v>4.827798070755007</v>
       </c>
       <c r="E100">
-        <v>3.940000000000001</v>
+        <v>4.120000000000001</v>
       </c>
       <c r="F100">
-        <v>17.64</v>
+        <v>17.82</v>
       </c>
       <c r="G100">
         <v>0.031</v>
@@ -9436,37 +9436,37 @@
         <v>0.4723333333333333</v>
       </c>
       <c r="M100">
-        <v>4.159512</v>
+        <v>4.201956</v>
       </c>
       <c r="N100">
-        <v>-3.687178666666667</v>
+        <v>-3.729622666666667</v>
       </c>
       <c r="O100">
-        <v>-0.7374357333333335</v>
+        <v>-0.7459245333333334</v>
       </c>
       <c r="P100">
-        <v>-2.949742933333334</v>
+        <v>-2.983698133333333</v>
       </c>
       <c r="Q100">
-        <v>-2.943742933333334</v>
+        <v>-2.977698133333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.31728531702757</v>
+        <v>6.588770634055141</v>
       </c>
       <c r="T100">
-        <v>50.60883739740788</v>
+        <v>101.2176747948158</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02271099750804101</v>
+        <v>0.02248159349280827</v>
       </c>
       <c r="W100">
-        <v>0.2304447467876039</v>
+        <v>0.2304988402543958</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9474,91 +9474,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.113554987540205</v>
+        <v>0.1124079674640414</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2940815581924033</v>
-      </c>
-      <c r="C101">
-        <v>-12.96120192924499</v>
-      </c>
-      <c r="D101">
-        <v>4.827798070755007</v>
-      </c>
-      <c r="E101">
-        <v>4.120000000000001</v>
-      </c>
-      <c r="F101">
-        <v>17.82</v>
-      </c>
-      <c r="G101">
-        <v>0.031</v>
-      </c>
-      <c r="H101">
-        <v>4.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.4783333333333333</v>
-      </c>
-      <c r="K101">
-        <v>0.006</v>
-      </c>
-      <c r="L101">
-        <v>0.4723333333333333</v>
-      </c>
-      <c r="M101">
-        <v>4.201956</v>
-      </c>
-      <c r="N101">
-        <v>-3.729622666666667</v>
-      </c>
-      <c r="O101">
-        <v>-0.7459245333333334</v>
-      </c>
-      <c r="P101">
-        <v>-2.983698133333333</v>
-      </c>
-      <c r="Q101">
-        <v>-2.977698133333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.588770634055141</v>
-      </c>
-      <c r="T101">
-        <v>101.2176747948158</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02248159349280827</v>
-      </c>
-      <c r="W101">
-        <v>0.2304988402543958</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1124079674640414</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
